--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7c61efecd2434424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R448b774dbfcd4d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rb14d52f710be419b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R82076cf7eab245a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -82,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -146,6 +146,9 @@
     <x:xf numFmtId="200" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -154,9 +157,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BackroomsModRegister" displayName="BackroomsModRegister" ref="A1:K295" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:K295"/>
-  <x:tableColumns count="11">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BackroomsModRegister" displayName="BackroomsModRegister" ref="A1:Q295" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:Q295"/>
+  <x:tableColumns count="17">
     <x:tableColumn id="1" name="Load order"/>
     <x:tableColumn id="2" name="Mod"/>
     <x:tableColumn id="3" name="Workshop ID / package ID"/>
@@ -168,6 +171,12 @@
     <x:tableColumn id="9" name="Integration Approach"/>
     <x:tableColumn id="10" name="Compatibility Watch"/>
     <x:tableColumn id="11" name="Research Status"/>
+    <x:tableColumn id="12" name="FeatureTraceIDs"/>
+    <x:tableColumn id="13" name="ReviewRecord"/>
+    <x:tableColumn id="14" name="ReviewStatus"/>
+    <x:tableColumn id="15" name="FinalDisposition"/>
+    <x:tableColumn id="16" name="EvidenceBuild"/>
+    <x:tableColumn id="17" name="AcceptanceEvidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -469,7 +478,7 @@
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>All names and IDs come from the local profile. Row-level roles are design mappings; most per-mod dependencies and compatibility remain unverified.</x:v>
+        <x:v>Six per-row evidence/decision fields have been added to the register. Row-level reviews, feature assignments, and final dispositions remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1000,6 +1009,12 @@
     <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="66" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="38" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="30" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="28" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1036,6 +1051,24 @@
       <x:c r="K1" s="22" t="str">
         <x:v>Research Status</x:v>
       </x:c>
+      <x:c r="L1" s="27" t="str">
+        <x:v>FeatureTraceIDs</x:v>
+      </x:c>
+      <x:c r="M1" s="27" t="str">
+        <x:v>ReviewRecord</x:v>
+      </x:c>
+      <x:c r="N1" s="27" t="str">
+        <x:v>ReviewStatus</x:v>
+      </x:c>
+      <x:c r="O1" s="27" t="str">
+        <x:v>FinalDisposition</x:v>
+      </x:c>
+      <x:c r="P1" s="27" t="str">
+        <x:v>EvidenceBuild</x:v>
+      </x:c>
+      <x:c r="Q1" s="27" t="str">
+        <x:v>AcceptanceEvidence</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="45" customHeight="1">
       <x:c r="A2" s="26" t="str">
@@ -1070,6 +1103,24 @@
       </x:c>
       <x:c r="K2" s="24" t="str">
         <x:v>Required by the official RWT and VEF listings; exact local build still needs pinning.</x:v>
+      </x:c>
+      <x:c r="L2" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M2" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N2" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O2" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P2" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q2" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="45" customHeight="1">
@@ -1106,6 +1157,24 @@
       <x:c r="K3" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L3" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M3" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N3" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O3" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P3" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q3" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="45" customHeight="1">
       <x:c r="A4" s="26" t="str">
@@ -1141,6 +1210,24 @@
       <x:c r="K4" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L4" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M4" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N4" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O4" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P4" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q4" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="45" customHeight="1">
       <x:c r="A5" s="26" t="str">
@@ -1155,7 +1242,7 @@
       <x:c r="D5" s="24" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="24" t="str"/>
+      <x:c r="E5" s="24"/>
       <x:c r="F5" s="24" t="str">
         <x:v>RimWorld base game</x:v>
       </x:c>
@@ -1173,6 +1260,24 @@
       </x:c>
       <x:c r="K5" s="24" t="str">
         <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+      </x:c>
+      <x:c r="L5" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M5" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N5" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O5" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P5" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q5" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="45" customHeight="1">
@@ -1188,7 +1293,7 @@
       <x:c r="D6" s="24" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E6" s="24" t="str"/>
+      <x:c r="E6" s="24"/>
       <x:c r="F6" s="24" t="str">
         <x:v>DLC: Royalty</x:v>
       </x:c>
@@ -1206,6 +1311,24 @@
       </x:c>
       <x:c r="K6" s="24" t="str">
         <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+      </x:c>
+      <x:c r="L6" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M6" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N6" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O6" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P6" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q6" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="45" customHeight="1">
@@ -1221,7 +1344,7 @@
       <x:c r="D7" s="24" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E7" s="24" t="str"/>
+      <x:c r="E7" s="24"/>
       <x:c r="F7" s="24" t="str">
         <x:v>DLC: Ideology</x:v>
       </x:c>
@@ -1239,6 +1362,24 @@
       </x:c>
       <x:c r="K7" s="24" t="str">
         <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+      </x:c>
+      <x:c r="L7" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M7" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N7" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O7" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P7" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q7" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
@@ -1254,7 +1395,7 @@
       <x:c r="D8" s="24" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E8" s="24" t="str"/>
+      <x:c r="E8" s="24"/>
       <x:c r="F8" s="24" t="str">
         <x:v>DLC: Biotech</x:v>
       </x:c>
@@ -1272,6 +1413,24 @@
       </x:c>
       <x:c r="K8" s="24" t="str">
         <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+      </x:c>
+      <x:c r="L8" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M8" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N8" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O8" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P8" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q8" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="45" customHeight="1">
@@ -1287,7 +1446,7 @@
       <x:c r="D9" s="24" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E9" s="24" t="str"/>
+      <x:c r="E9" s="24"/>
       <x:c r="F9" s="24" t="str">
         <x:v>DLC: Anomaly</x:v>
       </x:c>
@@ -1305,6 +1464,24 @@
       </x:c>
       <x:c r="K9" s="24" t="str">
         <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+      </x:c>
+      <x:c r="L9" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M9" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N9" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O9" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P9" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q9" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="45" customHeight="1">
@@ -1320,7 +1497,7 @@
       <x:c r="D10" s="24" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E10" s="24" t="str"/>
+      <x:c r="E10" s="24"/>
       <x:c r="F10" s="24" t="str">
         <x:v>DLC: Odyssey</x:v>
       </x:c>
@@ -1338,6 +1515,24 @@
       </x:c>
       <x:c r="K10" s="24" t="str">
         <x:v>Local profile entry; required by both gravship chapter listings.</x:v>
+      </x:c>
+      <x:c r="L10" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M10" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N10" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O10" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P10" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q10" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="45" customHeight="1">
@@ -1374,6 +1569,24 @@
       <x:c r="K11" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L11" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M11" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N11" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O11" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P11" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q11" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="45" customHeight="1">
       <x:c r="A12" s="26" t="str">
@@ -1409,6 +1622,24 @@
       <x:c r="K12" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L12" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M12" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N12" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O12" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P12" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q12" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="45" customHeight="1">
       <x:c r="A13" s="26" t="str">
@@ -1444,6 +1675,24 @@
       <x:c r="K13" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L13" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M13" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N13" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O13" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P13" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q13" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
       <x:c r="A14" s="26" t="str">
@@ -1479,6 +1728,24 @@
       <x:c r="K14" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L14" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N14" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O14" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P14" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q14" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="45" customHeight="1">
       <x:c r="A15" s="26" t="str">
@@ -1514,6 +1781,24 @@
       <x:c r="K15" s="24" t="str">
         <x:v>Official Workshop description and dependency listing reviewed.</x:v>
       </x:c>
+      <x:c r="L15" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M15" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N15" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O15" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P15" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q15" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
       <x:c r="A16" s="26" t="str">
@@ -1549,6 +1834,24 @@
       <x:c r="K16" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L16" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M16" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N16" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O16" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P16" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q16" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
       <x:c r="A17" s="26" t="str">
@@ -1584,6 +1887,24 @@
       <x:c r="K17" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L17" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M17" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N17" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O17" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P17" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q17" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
       <x:c r="A18" s="26" t="str">
@@ -1619,6 +1940,24 @@
       <x:c r="K18" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L18" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M18" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N18" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O18" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P18" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q18" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="45" customHeight="1">
       <x:c r="A19" s="26" t="str">
@@ -1654,6 +1993,24 @@
       <x:c r="K19" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L19" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M19" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N19" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O19" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P19" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q19" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="45" customHeight="1">
       <x:c r="A20" s="26" t="str">
@@ -1689,6 +2046,24 @@
       <x:c r="K20" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L20" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M20" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N20" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O20" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P20" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q20" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="45" customHeight="1">
       <x:c r="A21" s="26" t="str">
@@ -1724,6 +2099,24 @@
       <x:c r="K21" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L21" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M21" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N21" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O21" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P21" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q21" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="45" customHeight="1">
       <x:c r="A22" s="26" t="str">
@@ -1759,6 +2152,24 @@
       <x:c r="K22" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L22" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M22" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N22" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O22" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P22" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q22" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="45" customHeight="1">
       <x:c r="A23" s="26" t="str">
@@ -1794,6 +2205,24 @@
       <x:c r="K23" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L23" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M23" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N23" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O23" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P23" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q23" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="45" customHeight="1">
       <x:c r="A24" s="26" t="str">
@@ -1829,6 +2258,24 @@
       <x:c r="K24" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L24" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M24" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N24" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O24" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P24" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q24" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="45" customHeight="1">
       <x:c r="A25" s="26" t="str">
@@ -1864,6 +2311,24 @@
       <x:c r="K25" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L25" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M25" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N25" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O25" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P25" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q25" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="45" customHeight="1">
       <x:c r="A26" s="26" t="str">
@@ -1899,6 +2364,24 @@
       <x:c r="K26" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L26" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M26" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N26" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O26" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P26" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q26" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="45" customHeight="1">
       <x:c r="A27" s="26" t="str">
@@ -1934,6 +2417,24 @@
       <x:c r="K27" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L27" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M27" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N27" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O27" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P27" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q27" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="45" customHeight="1">
       <x:c r="A28" s="26" t="str">
@@ -1969,6 +2470,24 @@
       <x:c r="K28" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L28" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M28" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N28" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O28" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P28" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q28" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="45" customHeight="1">
       <x:c r="A29" s="26" t="str">
@@ -2004,6 +2523,24 @@
       <x:c r="K29" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L29" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M29" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N29" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O29" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P29" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q29" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="45" customHeight="1">
       <x:c r="A30" s="26" t="str">
@@ -2039,6 +2576,24 @@
       <x:c r="K30" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L30" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M30" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N30" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O30" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P30" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q30" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="45" customHeight="1">
       <x:c r="A31" s="26" t="str">
@@ -2074,6 +2629,24 @@
       <x:c r="K31" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L31" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M31" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N31" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O31" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P31" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q31" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="45" customHeight="1">
       <x:c r="A32" s="26" t="str">
@@ -2109,6 +2682,24 @@
       <x:c r="K32" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L32" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M32" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N32" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O32" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P32" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q32" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="45" customHeight="1">
       <x:c r="A33" s="26" t="str">
@@ -2144,6 +2735,24 @@
       <x:c r="K33" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L33" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M33" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N33" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O33" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P33" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q33" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="45" customHeight="1">
       <x:c r="A34" s="26" t="str">
@@ -2179,6 +2788,24 @@
       <x:c r="K34" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L34" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M34" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N34" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O34" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P34" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q34" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="45" customHeight="1">
       <x:c r="A35" s="26" t="str">
@@ -2214,6 +2841,24 @@
       <x:c r="K35" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L35" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M35" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N35" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O35" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P35" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q35" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="45" customHeight="1">
       <x:c r="A36" s="26" t="str">
@@ -2249,6 +2894,24 @@
       <x:c r="K36" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L36" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M36" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N36" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O36" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P36" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q36" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="45" customHeight="1">
       <x:c r="A37" s="26" t="str">
@@ -2284,6 +2947,24 @@
       <x:c r="K37" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L37" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M37" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N37" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O37" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P37" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q37" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="45" customHeight="1">
       <x:c r="A38" s="26" t="str">
@@ -2319,6 +3000,24 @@
       <x:c r="K38" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L38" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M38" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N38" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O38" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P38" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q38" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="45" customHeight="1">
       <x:c r="A39" s="26" t="str">
@@ -2354,6 +3053,24 @@
       <x:c r="K39" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L39" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M39" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N39" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O39" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P39" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q39" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="45" customHeight="1">
       <x:c r="A40" s="26" t="str">
@@ -2389,6 +3106,24 @@
       <x:c r="K40" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L40" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M40" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N40" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O40" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P40" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q40" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="45" customHeight="1">
       <x:c r="A41" s="26" t="str">
@@ -2424,6 +3159,24 @@
       <x:c r="K41" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L41" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M41" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N41" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O41" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P41" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q41" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="45" customHeight="1">
       <x:c r="A42" s="26" t="str">
@@ -2459,6 +3212,24 @@
       <x:c r="K42" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L42" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M42" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N42" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O42" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P42" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q42" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="45" customHeight="1">
       <x:c r="A43" s="26" t="str">
@@ -2494,6 +3265,24 @@
       <x:c r="K43" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L43" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M43" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N43" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O43" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P43" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q43" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="45" customHeight="1">
       <x:c r="A44" s="26" t="str">
@@ -2529,6 +3318,24 @@
       <x:c r="K44" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L44" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M44" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N44" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O44" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P44" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q44" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="45" customHeight="1">
       <x:c r="A45" s="26" t="str">
@@ -2564,6 +3371,24 @@
       <x:c r="K45" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L45" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M45" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N45" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O45" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P45" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q45" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="45" customHeight="1">
       <x:c r="A46" s="26" t="str">
@@ -2599,6 +3424,24 @@
       <x:c r="K46" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L46" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M46" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N46" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O46" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P46" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q46" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="45" customHeight="1">
       <x:c r="A47" s="26" t="str">
@@ -2634,6 +3477,24 @@
       <x:c r="K47" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L47" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M47" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N47" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O47" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P47" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q47" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="45" customHeight="1">
       <x:c r="A48" s="26" t="str">
@@ -2669,6 +3530,24 @@
       <x:c r="K48" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L48" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M48" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N48" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O48" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P48" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q48" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="45" customHeight="1">
       <x:c r="A49" s="26" t="str">
@@ -2704,6 +3583,24 @@
       <x:c r="K49" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L49" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M49" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N49" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O49" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P49" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q49" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="45" customHeight="1">
       <x:c r="A50" s="26" t="str">
@@ -2739,6 +3636,24 @@
       <x:c r="K50" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L50" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M50" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N50" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O50" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P50" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q50" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="45" customHeight="1">
       <x:c r="A51" s="26" t="str">
@@ -2774,6 +3689,24 @@
       <x:c r="K51" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L51" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M51" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N51" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O51" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P51" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q51" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="45" customHeight="1">
       <x:c r="A52" s="26" t="str">
@@ -2809,6 +3742,24 @@
       <x:c r="K52" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L52" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M52" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N52" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O52" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P52" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q52" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="45" customHeight="1">
       <x:c r="A53" s="26" t="str">
@@ -2844,6 +3795,24 @@
       <x:c r="K53" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L53" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M53" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N53" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O53" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P53" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q53" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="45" customHeight="1">
       <x:c r="A54" s="26" t="str">
@@ -2879,6 +3848,24 @@
       <x:c r="K54" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L54" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M54" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N54" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O54" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P54" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q54" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="45" customHeight="1">
       <x:c r="A55" s="26" t="str">
@@ -2914,6 +3901,24 @@
       <x:c r="K55" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L55" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M55" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N55" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O55" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P55" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q55" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="45" customHeight="1">
       <x:c r="A56" s="26" t="str">
@@ -2949,6 +3954,24 @@
       <x:c r="K56" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L56" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M56" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N56" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O56" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P56" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q56" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="45" customHeight="1">
       <x:c r="A57" s="26" t="str">
@@ -2984,6 +4007,24 @@
       <x:c r="K57" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L57" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M57" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N57" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O57" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P57" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q57" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="45" customHeight="1">
       <x:c r="A58" s="26" t="str">
@@ -3019,6 +4060,24 @@
       <x:c r="K58" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L58" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M58" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N58" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O58" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P58" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q58" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="45" customHeight="1">
       <x:c r="A59" s="26" t="str">
@@ -3054,6 +4113,24 @@
       <x:c r="K59" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L59" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M59" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N59" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O59" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P59" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q59" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="45" customHeight="1">
       <x:c r="A60" s="26" t="str">
@@ -3089,6 +4166,24 @@
       <x:c r="K60" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L60" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M60" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N60" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O60" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P60" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q60" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="45" customHeight="1">
       <x:c r="A61" s="26" t="str">
@@ -3124,6 +4219,24 @@
       <x:c r="K61" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L61" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M61" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N61" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O61" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P61" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q61" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="45" customHeight="1">
       <x:c r="A62" s="26" t="str">
@@ -3159,6 +4272,24 @@
       <x:c r="K62" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L62" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M62" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N62" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O62" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P62" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q62" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="45" customHeight="1">
       <x:c r="A63" s="26" t="str">
@@ -3194,6 +4325,24 @@
       <x:c r="K63" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L63" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M63" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N63" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O63" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P63" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q63" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="45" customHeight="1">
       <x:c r="A64" s="26" t="str">
@@ -3229,6 +4378,24 @@
       <x:c r="K64" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L64" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M64" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N64" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O64" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P64" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q64" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="45" customHeight="1">
       <x:c r="A65" s="26" t="str">
@@ -3264,6 +4431,24 @@
       <x:c r="K65" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L65" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M65" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N65" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O65" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P65" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q65" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="45" customHeight="1">
       <x:c r="A66" s="26" t="str">
@@ -3299,6 +4484,24 @@
       <x:c r="K66" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L66" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M66" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N66" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O66" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P66" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q66" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="45" customHeight="1">
       <x:c r="A67" s="26" t="str">
@@ -3334,6 +4537,24 @@
       <x:c r="K67" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L67" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M67" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N67" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O67" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P67" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q67" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="45" customHeight="1">
       <x:c r="A68" s="26" t="str">
@@ -3369,6 +4590,24 @@
       <x:c r="K68" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L68" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M68" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N68" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O68" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P68" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q68" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="45" customHeight="1">
       <x:c r="A69" s="26" t="str">
@@ -3404,6 +4643,24 @@
       <x:c r="K69" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L69" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M69" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N69" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O69" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P69" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q69" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="45" customHeight="1">
       <x:c r="A70" s="26" t="str">
@@ -3439,6 +4696,24 @@
       <x:c r="K70" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L70" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M70" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N70" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O70" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P70" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q70" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="45" customHeight="1">
       <x:c r="A71" s="26" t="str">
@@ -3474,6 +4749,24 @@
       <x:c r="K71" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L71" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M71" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N71" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O71" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P71" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q71" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="45" customHeight="1">
       <x:c r="A72" s="26" t="str">
@@ -3509,6 +4802,24 @@
       <x:c r="K72" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L72" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M72" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N72" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O72" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P72" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q72" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="45" customHeight="1">
       <x:c r="A73" s="26" t="str">
@@ -3544,6 +4855,24 @@
       <x:c r="K73" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L73" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M73" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N73" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O73" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P73" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q73" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="45" customHeight="1">
       <x:c r="A74" s="26" t="str">
@@ -3579,6 +4908,24 @@
       <x:c r="K74" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L74" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M74" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N74" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O74" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P74" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q74" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="45" customHeight="1">
       <x:c r="A75" s="26" t="str">
@@ -3614,6 +4961,24 @@
       <x:c r="K75" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L75" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M75" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N75" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O75" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P75" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q75" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="45" customHeight="1">
       <x:c r="A76" s="26" t="str">
@@ -3649,6 +5014,24 @@
       <x:c r="K76" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L76" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M76" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N76" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O76" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P76" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q76" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="45" customHeight="1">
       <x:c r="A77" s="26" t="str">
@@ -3684,6 +5067,24 @@
       <x:c r="K77" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L77" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M77" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N77" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O77" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P77" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q77" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="45" customHeight="1">
       <x:c r="A78" s="26" t="str">
@@ -3719,6 +5120,24 @@
       <x:c r="K78" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L78" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M78" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N78" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O78" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P78" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q78" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="45" customHeight="1">
       <x:c r="A79" s="26" t="str">
@@ -3754,6 +5173,24 @@
       <x:c r="K79" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L79" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M79" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N79" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O79" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P79" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q79" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="45" customHeight="1">
       <x:c r="A80" s="26" t="str">
@@ -3789,6 +5226,24 @@
       <x:c r="K80" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L80" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M80" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N80" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O80" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P80" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q80" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" ht="45" customHeight="1">
       <x:c r="A81" s="26" t="str">
@@ -3824,6 +5279,24 @@
       <x:c r="K81" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L81" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M81" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N81" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O81" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P81" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q81" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" ht="45" customHeight="1">
       <x:c r="A82" s="26" t="str">
@@ -3859,6 +5332,24 @@
       <x:c r="K82" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L82" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M82" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N82" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O82" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P82" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q82" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="83" ht="45" customHeight="1">
       <x:c r="A83" s="26" t="str">
@@ -3894,6 +5385,24 @@
       <x:c r="K83" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L83" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M83" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N83" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O83" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P83" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q83" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="84" ht="45" customHeight="1">
       <x:c r="A84" s="26" t="str">
@@ -3929,6 +5438,24 @@
       <x:c r="K84" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L84" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M84" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N84" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O84" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P84" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q84" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" ht="45" customHeight="1">
       <x:c r="A85" s="26" t="str">
@@ -3964,6 +5491,24 @@
       <x:c r="K85" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L85" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M85" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N85" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O85" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P85" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q85" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="45" customHeight="1">
       <x:c r="A86" s="26" t="str">
@@ -3999,6 +5544,24 @@
       <x:c r="K86" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L86" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M86" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N86" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O86" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P86" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q86" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" ht="45" customHeight="1">
       <x:c r="A87" s="26" t="str">
@@ -4034,6 +5597,24 @@
       <x:c r="K87" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L87" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M87" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N87" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O87" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P87" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q87" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="45" customHeight="1">
       <x:c r="A88" s="26" t="str">
@@ -4069,6 +5650,24 @@
       <x:c r="K88" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L88" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M88" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N88" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O88" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P88" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q88" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="89" ht="45" customHeight="1">
       <x:c r="A89" s="26" t="str">
@@ -4104,6 +5703,24 @@
       <x:c r="K89" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L89" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M89" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N89" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O89" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P89" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q89" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="45" customHeight="1">
       <x:c r="A90" s="26" t="str">
@@ -4139,6 +5756,24 @@
       <x:c r="K90" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L90" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M90" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N90" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O90" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P90" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q90" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" ht="45" customHeight="1">
       <x:c r="A91" s="26" t="str">
@@ -4174,6 +5809,24 @@
       <x:c r="K91" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L91" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M91" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N91" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O91" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P91" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q91" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="45" customHeight="1">
       <x:c r="A92" s="26" t="str">
@@ -4209,6 +5862,24 @@
       <x:c r="K92" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L92" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M92" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N92" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O92" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P92" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q92" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="45" customHeight="1">
       <x:c r="A93" s="26" t="str">
@@ -4244,6 +5915,24 @@
       <x:c r="K93" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L93" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M93" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N93" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O93" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P93" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q93" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="94" ht="45" customHeight="1">
       <x:c r="A94" s="26" t="str">
@@ -4279,6 +5968,24 @@
       <x:c r="K94" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L94" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M94" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N94" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O94" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P94" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q94" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="95" ht="45" customHeight="1">
       <x:c r="A95" s="26" t="str">
@@ -4314,6 +6021,24 @@
       <x:c r="K95" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L95" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M95" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N95" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O95" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P95" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q95" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="96" ht="45" customHeight="1">
       <x:c r="A96" s="26" t="str">
@@ -4349,6 +6074,24 @@
       <x:c r="K96" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L96" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M96" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N96" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O96" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P96" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q96" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="97" ht="45" customHeight="1">
       <x:c r="A97" s="26" t="str">
@@ -4384,6 +6127,24 @@
       <x:c r="K97" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L97" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M97" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N97" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O97" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P97" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q97" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="98" ht="45" customHeight="1">
       <x:c r="A98" s="26" t="str">
@@ -4419,6 +6180,24 @@
       <x:c r="K98" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L98" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M98" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N98" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O98" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P98" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q98" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="99" ht="45" customHeight="1">
       <x:c r="A99" s="26" t="str">
@@ -4454,6 +6233,24 @@
       <x:c r="K99" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L99" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M99" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N99" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O99" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P99" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q99" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="100" ht="45" customHeight="1">
       <x:c r="A100" s="26" t="str">
@@ -4489,6 +6286,24 @@
       <x:c r="K100" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L100" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M100" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N100" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O100" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P100" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q100" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="101" ht="45" customHeight="1">
       <x:c r="A101" s="26" t="str">
@@ -4524,6 +6339,24 @@
       <x:c r="K101" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L101" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M101" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N101" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O101" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P101" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q101" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="102" ht="45" customHeight="1">
       <x:c r="A102" s="26" t="str">
@@ -4559,6 +6392,24 @@
       <x:c r="K102" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L102" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M102" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N102" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O102" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P102" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q102" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="103" ht="45" customHeight="1">
       <x:c r="A103" s="26" t="str">
@@ -4594,6 +6445,24 @@
       <x:c r="K103" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L103" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M103" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N103" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O103" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P103" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q103" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="104" ht="45" customHeight="1">
       <x:c r="A104" s="26" t="str">
@@ -4629,6 +6498,24 @@
       <x:c r="K104" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L104" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M104" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N104" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O104" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P104" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q104" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="105" ht="45" customHeight="1">
       <x:c r="A105" s="26" t="str">
@@ -4664,6 +6551,24 @@
       <x:c r="K105" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L105" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M105" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N105" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O105" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P105" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q105" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" ht="45" customHeight="1">
       <x:c r="A106" s="26" t="str">
@@ -4699,6 +6604,24 @@
       <x:c r="K106" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L106" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M106" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N106" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O106" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P106" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q106" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" ht="45" customHeight="1">
       <x:c r="A107" s="26" t="str">
@@ -4734,6 +6657,24 @@
       <x:c r="K107" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L107" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M107" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N107" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O107" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P107" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q107" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" ht="45" customHeight="1">
       <x:c r="A108" s="26" t="str">
@@ -4769,6 +6710,24 @@
       <x:c r="K108" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L108" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M108" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N108" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O108" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P108" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q108" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" ht="45" customHeight="1">
       <x:c r="A109" s="26" t="str">
@@ -4804,6 +6763,24 @@
       <x:c r="K109" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L109" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M109" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N109" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O109" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P109" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q109" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" ht="45" customHeight="1">
       <x:c r="A110" s="26" t="str">
@@ -4839,6 +6816,24 @@
       <x:c r="K110" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L110" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M110" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N110" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O110" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P110" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q110" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" ht="45" customHeight="1">
       <x:c r="A111" s="26" t="str">
@@ -4874,6 +6869,24 @@
       <x:c r="K111" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L111" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M111" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N111" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O111" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P111" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q111" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" ht="45" customHeight="1">
       <x:c r="A112" s="26" t="str">
@@ -4909,6 +6922,24 @@
       <x:c r="K112" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L112" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M112" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N112" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O112" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P112" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q112" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" ht="45" customHeight="1">
       <x:c r="A113" s="26" t="str">
@@ -4944,6 +6975,24 @@
       <x:c r="K113" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L113" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M113" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N113" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O113" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P113" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q113" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" ht="45" customHeight="1">
       <x:c r="A114" s="26" t="str">
@@ -4979,6 +7028,24 @@
       <x:c r="K114" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L114" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M114" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N114" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O114" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P114" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q114" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" ht="45" customHeight="1">
       <x:c r="A115" s="26" t="str">
@@ -5014,6 +7081,24 @@
       <x:c r="K115" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L115" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M115" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N115" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O115" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P115" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q115" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" ht="45" customHeight="1">
       <x:c r="A116" s="26" t="str">
@@ -5049,6 +7134,24 @@
       <x:c r="K116" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L116" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M116" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N116" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O116" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P116" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q116" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" ht="45" customHeight="1">
       <x:c r="A117" s="26" t="str">
@@ -5084,6 +7187,24 @@
       <x:c r="K117" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L117" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M117" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N117" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O117" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P117" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q117" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" ht="45" customHeight="1">
       <x:c r="A118" s="26" t="str">
@@ -5119,6 +7240,24 @@
       <x:c r="K118" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L118" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M118" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N118" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O118" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P118" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q118" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" ht="45" customHeight="1">
       <x:c r="A119" s="26" t="str">
@@ -5154,6 +7293,24 @@
       <x:c r="K119" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L119" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M119" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N119" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O119" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P119" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q119" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" ht="45" customHeight="1">
       <x:c r="A120" s="26" t="str">
@@ -5189,6 +7346,24 @@
       <x:c r="K120" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L120" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M120" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N120" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O120" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P120" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q120" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" ht="45" customHeight="1">
       <x:c r="A121" s="26" t="str">
@@ -5224,6 +7399,24 @@
       <x:c r="K121" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L121" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M121" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N121" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O121" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P121" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q121" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" ht="45" customHeight="1">
       <x:c r="A122" s="26" t="str">
@@ -5259,6 +7452,24 @@
       <x:c r="K122" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L122" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M122" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N122" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O122" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P122" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q122" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" ht="45" customHeight="1">
       <x:c r="A123" s="26" t="str">
@@ -5294,6 +7505,24 @@
       <x:c r="K123" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L123" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M123" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N123" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O123" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P123" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q123" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" ht="45" customHeight="1">
       <x:c r="A124" s="26" t="str">
@@ -5329,6 +7558,24 @@
       <x:c r="K124" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L124" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M124" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N124" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O124" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P124" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q124" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" ht="45" customHeight="1">
       <x:c r="A125" s="26" t="str">
@@ -5364,6 +7611,24 @@
       <x:c r="K125" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L125" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M125" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N125" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O125" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P125" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q125" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="45" customHeight="1">
       <x:c r="A126" s="26" t="str">
@@ -5399,6 +7664,24 @@
       <x:c r="K126" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L126" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M126" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N126" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O126" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P126" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q126" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="127" ht="45" customHeight="1">
       <x:c r="A127" s="26" t="str">
@@ -5434,6 +7717,24 @@
       <x:c r="K127" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L127" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M127" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N127" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O127" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P127" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q127" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" ht="45" customHeight="1">
       <x:c r="A128" s="26" t="str">
@@ -5469,6 +7770,24 @@
       <x:c r="K128" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L128" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M128" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N128" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O128" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P128" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q128" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="45" customHeight="1">
       <x:c r="A129" s="26" t="str">
@@ -5504,6 +7823,24 @@
       <x:c r="K129" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L129" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M129" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N129" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O129" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P129" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q129" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="45" customHeight="1">
       <x:c r="A130" s="26" t="str">
@@ -5539,6 +7876,24 @@
       <x:c r="K130" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L130" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M130" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N130" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O130" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P130" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q130" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="45" customHeight="1">
       <x:c r="A131" s="26" t="str">
@@ -5574,6 +7929,24 @@
       <x:c r="K131" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L131" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M131" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N131" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O131" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P131" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q131" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" ht="45" customHeight="1">
       <x:c r="A132" s="26" t="str">
@@ -5609,6 +7982,24 @@
       <x:c r="K132" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L132" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M132" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N132" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O132" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P132" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q132" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" ht="45" customHeight="1">
       <x:c r="A133" s="26" t="str">
@@ -5644,6 +8035,24 @@
       <x:c r="K133" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L133" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M133" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N133" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O133" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P133" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q133" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" ht="45" customHeight="1">
       <x:c r="A134" s="26" t="str">
@@ -5679,6 +8088,24 @@
       <x:c r="K134" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L134" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M134" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N134" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O134" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P134" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q134" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="135" ht="45" customHeight="1">
       <x:c r="A135" s="26" t="str">
@@ -5714,6 +8141,24 @@
       <x:c r="K135" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L135" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M135" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N135" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O135" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P135" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q135" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" ht="45" customHeight="1">
       <x:c r="A136" s="26" t="str">
@@ -5749,6 +8194,24 @@
       <x:c r="K136" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L136" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M136" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N136" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O136" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P136" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q136" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="45" customHeight="1">
       <x:c r="A137" s="26" t="str">
@@ -5784,6 +8247,24 @@
       <x:c r="K137" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L137" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M137" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N137" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O137" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P137" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q137" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="138" ht="45" customHeight="1">
       <x:c r="A138" s="26" t="str">
@@ -5819,6 +8300,24 @@
       <x:c r="K138" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L138" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M138" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N138" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O138" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P138" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q138" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" ht="45" customHeight="1">
       <x:c r="A139" s="26" t="str">
@@ -5854,6 +8353,24 @@
       <x:c r="K139" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L139" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M139" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N139" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O139" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P139" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q139" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="140" ht="45" customHeight="1">
       <x:c r="A140" s="26" t="str">
@@ -5889,6 +8406,24 @@
       <x:c r="K140" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L140" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M140" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N140" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O140" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P140" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q140" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="141" ht="45" customHeight="1">
       <x:c r="A141" s="26" t="str">
@@ -5924,6 +8459,24 @@
       <x:c r="K141" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L141" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M141" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N141" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O141" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P141" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q141" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="142" ht="45" customHeight="1">
       <x:c r="A142" s="26" t="str">
@@ -5959,6 +8512,24 @@
       <x:c r="K142" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L142" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M142" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N142" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O142" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P142" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q142" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="143" ht="45" customHeight="1">
       <x:c r="A143" s="26" t="str">
@@ -5994,6 +8565,24 @@
       <x:c r="K143" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L143" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M143" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N143" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O143" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P143" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q143" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" ht="45" customHeight="1">
       <x:c r="A144" s="26" t="str">
@@ -6029,6 +8618,24 @@
       <x:c r="K144" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L144" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M144" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N144" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O144" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P144" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q144" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" ht="45" customHeight="1">
       <x:c r="A145" s="26" t="str">
@@ -6064,6 +8671,24 @@
       <x:c r="K145" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L145" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M145" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N145" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O145" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P145" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q145" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="45" customHeight="1">
       <x:c r="A146" s="26" t="str">
@@ -6099,6 +8724,24 @@
       <x:c r="K146" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L146" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M146" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N146" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O146" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P146" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q146" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" ht="45" customHeight="1">
       <x:c r="A147" s="26" t="str">
@@ -6134,6 +8777,24 @@
       <x:c r="K147" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L147" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M147" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N147" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O147" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P147" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q147" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="148" ht="45" customHeight="1">
       <x:c r="A148" s="26" t="str">
@@ -6169,6 +8830,24 @@
       <x:c r="K148" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L148" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M148" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N148" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O148" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P148" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q148" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" ht="45" customHeight="1">
       <x:c r="A149" s="26" t="str">
@@ -6204,6 +8883,24 @@
       <x:c r="K149" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L149" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M149" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N149" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O149" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P149" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q149" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="45" customHeight="1">
       <x:c r="A150" s="26" t="str">
@@ -6239,6 +8936,24 @@
       <x:c r="K150" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L150" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M150" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N150" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O150" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P150" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q150" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" ht="45" customHeight="1">
       <x:c r="A151" s="26" t="str">
@@ -6274,6 +8989,24 @@
       <x:c r="K151" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L151" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M151" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N151" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O151" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P151" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q151" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" ht="45" customHeight="1">
       <x:c r="A152" s="26" t="str">
@@ -6309,6 +9042,24 @@
       <x:c r="K152" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L152" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M152" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N152" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O152" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P152" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q152" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" ht="45" customHeight="1">
       <x:c r="A153" s="26" t="str">
@@ -6344,6 +9095,24 @@
       <x:c r="K153" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L153" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M153" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N153" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O153" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P153" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q153" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" ht="45" customHeight="1">
       <x:c r="A154" s="26" t="str">
@@ -6379,6 +9148,24 @@
       <x:c r="K154" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L154" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M154" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N154" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O154" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P154" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q154" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="155" ht="45" customHeight="1">
       <x:c r="A155" s="26" t="str">
@@ -6414,6 +9201,24 @@
       <x:c r="K155" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L155" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M155" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N155" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O155" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P155" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q155" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="156" ht="45" customHeight="1">
       <x:c r="A156" s="26" t="str">
@@ -6449,6 +9254,24 @@
       <x:c r="K156" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L156" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M156" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N156" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O156" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P156" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q156" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="157" ht="45" customHeight="1">
       <x:c r="A157" s="26" t="str">
@@ -6484,6 +9307,24 @@
       <x:c r="K157" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L157" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M157" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N157" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O157" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P157" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q157" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="158" ht="45" customHeight="1">
       <x:c r="A158" s="26" t="str">
@@ -6519,6 +9360,24 @@
       <x:c r="K158" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L158" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M158" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N158" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O158" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P158" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q158" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="159" ht="45" customHeight="1">
       <x:c r="A159" s="26" t="str">
@@ -6554,6 +9413,24 @@
       <x:c r="K159" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L159" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M159" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N159" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O159" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P159" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q159" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" ht="45" customHeight="1">
       <x:c r="A160" s="26" t="str">
@@ -6589,6 +9466,24 @@
       <x:c r="K160" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L160" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M160" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N160" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O160" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P160" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q160" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="161" ht="45" customHeight="1">
       <x:c r="A161" s="26" t="str">
@@ -6624,6 +9519,24 @@
       <x:c r="K161" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L161" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M161" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N161" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O161" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P161" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q161" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="162" ht="45" customHeight="1">
       <x:c r="A162" s="26" t="str">
@@ -6659,6 +9572,24 @@
       <x:c r="K162" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L162" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M162" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N162" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O162" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P162" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q162" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="163" ht="45" customHeight="1">
       <x:c r="A163" s="26" t="str">
@@ -6694,6 +9625,24 @@
       <x:c r="K163" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L163" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M163" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N163" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O163" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P163" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q163" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" ht="45" customHeight="1">
       <x:c r="A164" s="26" t="str">
@@ -6729,6 +9678,24 @@
       <x:c r="K164" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L164" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M164" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N164" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O164" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P164" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q164" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="165" ht="45" customHeight="1">
       <x:c r="A165" s="26" t="str">
@@ -6764,6 +9731,24 @@
       <x:c r="K165" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L165" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M165" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N165" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O165" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P165" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q165" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="166" ht="45" customHeight="1">
       <x:c r="A166" s="26" t="str">
@@ -6799,6 +9784,24 @@
       <x:c r="K166" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L166" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M166" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N166" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O166" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P166" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q166" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="167" ht="45" customHeight="1">
       <x:c r="A167" s="26" t="str">
@@ -6834,6 +9837,24 @@
       <x:c r="K167" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L167" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M167" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N167" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O167" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P167" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q167" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="168" ht="45" customHeight="1">
       <x:c r="A168" s="26" t="str">
@@ -6869,6 +9890,24 @@
       <x:c r="K168" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L168" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M168" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N168" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O168" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P168" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q168" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="169" ht="45" customHeight="1">
       <x:c r="A169" s="26" t="str">
@@ -6904,6 +9943,24 @@
       <x:c r="K169" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L169" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M169" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N169" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O169" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P169" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q169" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="170" ht="45" customHeight="1">
       <x:c r="A170" s="26" t="str">
@@ -6939,6 +9996,24 @@
       <x:c r="K170" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L170" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M170" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N170" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O170" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P170" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q170" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="171" ht="45" customHeight="1">
       <x:c r="A171" s="26" t="str">
@@ -6974,6 +10049,24 @@
       <x:c r="K171" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L171" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M171" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N171" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O171" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P171" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q171" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="172" ht="45" customHeight="1">
       <x:c r="A172" s="26" t="str">
@@ -7009,6 +10102,24 @@
       <x:c r="K172" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L172" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M172" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N172" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O172" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P172" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q172" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" ht="45" customHeight="1">
       <x:c r="A173" s="26" t="str">
@@ -7044,6 +10155,24 @@
       <x:c r="K173" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L173" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M173" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N173" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O173" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P173" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q173" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" ht="45" customHeight="1">
       <x:c r="A174" s="26" t="str">
@@ -7079,6 +10208,24 @@
       <x:c r="K174" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L174" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M174" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N174" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O174" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P174" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q174" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="175" ht="45" customHeight="1">
       <x:c r="A175" s="26" t="str">
@@ -7114,6 +10261,24 @@
       <x:c r="K175" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L175" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M175" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N175" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O175" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P175" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q175" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="176" ht="45" customHeight="1">
       <x:c r="A176" s="26" t="str">
@@ -7149,6 +10314,24 @@
       <x:c r="K176" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L176" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M176" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N176" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O176" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P176" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q176" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="177" ht="45" customHeight="1">
       <x:c r="A177" s="26" t="str">
@@ -7184,6 +10367,24 @@
       <x:c r="K177" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L177" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M177" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N177" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O177" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P177" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q177" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="178" ht="45" customHeight="1">
       <x:c r="A178" s="26" t="str">
@@ -7219,6 +10420,24 @@
       <x:c r="K178" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L178" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M178" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N178" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O178" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P178" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q178" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="179" ht="45" customHeight="1">
       <x:c r="A179" s="26" t="str">
@@ -7254,6 +10473,24 @@
       <x:c r="K179" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L179" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M179" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N179" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O179" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P179" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q179" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="180" ht="45" customHeight="1">
       <x:c r="A180" s="26" t="str">
@@ -7289,6 +10526,24 @@
       <x:c r="K180" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L180" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M180" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N180" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O180" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P180" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q180" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="181" ht="45" customHeight="1">
       <x:c r="A181" s="26" t="str">
@@ -7324,6 +10579,24 @@
       <x:c r="K181" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L181" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M181" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N181" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O181" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P181" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q181" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="182" ht="45" customHeight="1">
       <x:c r="A182" s="26" t="str">
@@ -7359,6 +10632,24 @@
       <x:c r="K182" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L182" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M182" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N182" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O182" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P182" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q182" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="183" ht="45" customHeight="1">
       <x:c r="A183" s="26" t="str">
@@ -7394,6 +10685,24 @@
       <x:c r="K183" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L183" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M183" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N183" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O183" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P183" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q183" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="184" ht="45" customHeight="1">
       <x:c r="A184" s="26" t="str">
@@ -7429,6 +10738,24 @@
       <x:c r="K184" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L184" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M184" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N184" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O184" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P184" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q184" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="185" ht="45" customHeight="1">
       <x:c r="A185" s="26" t="str">
@@ -7464,6 +10791,24 @@
       <x:c r="K185" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L185" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M185" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N185" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O185" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P185" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q185" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="186" ht="45" customHeight="1">
       <x:c r="A186" s="26" t="str">
@@ -7499,6 +10844,24 @@
       <x:c r="K186" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L186" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M186" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N186" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O186" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P186" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q186" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="187" ht="45" customHeight="1">
       <x:c r="A187" s="26" t="str">
@@ -7534,6 +10897,24 @@
       <x:c r="K187" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L187" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M187" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N187" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O187" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P187" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q187" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="188" ht="45" customHeight="1">
       <x:c r="A188" s="26" t="str">
@@ -7569,6 +10950,24 @@
       <x:c r="K188" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L188" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M188" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N188" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O188" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P188" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q188" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="189" ht="45" customHeight="1">
       <x:c r="A189" s="26" t="str">
@@ -7604,6 +11003,24 @@
       <x:c r="K189" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L189" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M189" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N189" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O189" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P189" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q189" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="190" ht="45" customHeight="1">
       <x:c r="A190" s="26" t="str">
@@ -7639,6 +11056,24 @@
       <x:c r="K190" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L190" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M190" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N190" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O190" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P190" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q190" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="191" ht="45" customHeight="1">
       <x:c r="A191" s="26" t="str">
@@ -7674,6 +11109,24 @@
       <x:c r="K191" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L191" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M191" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N191" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O191" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P191" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q191" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="192" ht="45" customHeight="1">
       <x:c r="A192" s="26" t="str">
@@ -7709,6 +11162,24 @@
       <x:c r="K192" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L192" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M192" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N192" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O192" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P192" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q192" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="193" ht="45" customHeight="1">
       <x:c r="A193" s="26" t="str">
@@ -7744,6 +11215,24 @@
       <x:c r="K193" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L193" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M193" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N193" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O193" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P193" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q193" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="194" ht="45" customHeight="1">
       <x:c r="A194" s="26" t="str">
@@ -7779,6 +11268,24 @@
       <x:c r="K194" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L194" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M194" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N194" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O194" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P194" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q194" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="195" ht="45" customHeight="1">
       <x:c r="A195" s="26" t="str">
@@ -7814,6 +11321,24 @@
       <x:c r="K195" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L195" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M195" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N195" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O195" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P195" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q195" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" ht="45" customHeight="1">
       <x:c r="A196" s="26" t="str">
@@ -7849,6 +11374,24 @@
       <x:c r="K196" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L196" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M196" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N196" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O196" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P196" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q196" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="197" ht="45" customHeight="1">
       <x:c r="A197" s="26" t="str">
@@ -7884,6 +11427,24 @@
       <x:c r="K197" s="24" t="str">
         <x:v>Official Workshop/release pages and local profile snapshot reviewed. RWT wiki returned HTTP 403; local server release identity, exact activity semantics, runtime behavior, and Backrooms adapters remain pending.</x:v>
       </x:c>
+      <x:c r="L197" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M197" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N197" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O197" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P197" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q197" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="198" ht="45" customHeight="1">
       <x:c r="A198" s="26" t="str">
@@ -7919,6 +11480,24 @@
       <x:c r="K198" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L198" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M198" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N198" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O198" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P198" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q198" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="199" ht="45" customHeight="1">
       <x:c r="A199" s="26" t="str">
@@ -7954,6 +11533,24 @@
       <x:c r="K199" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L199" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M199" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N199" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O199" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P199" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q199" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="200" ht="45" customHeight="1">
       <x:c r="A200" s="26" t="str">
@@ -7989,6 +11586,24 @@
       <x:c r="K200" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L200" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M200" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N200" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O200" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P200" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q200" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="201" ht="45" customHeight="1">
       <x:c r="A201" s="26" t="str">
@@ -8024,6 +11639,24 @@
       <x:c r="K201" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L201" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M201" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N201" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O201" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P201" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q201" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="202" ht="45" customHeight="1">
       <x:c r="A202" s="26" t="str">
@@ -8059,6 +11692,24 @@
       <x:c r="K202" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L202" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M202" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N202" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O202" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P202" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q202" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="203" ht="45" customHeight="1">
       <x:c r="A203" s="26" t="str">
@@ -8094,6 +11745,24 @@
       <x:c r="K203" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L203" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M203" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N203" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O203" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P203" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q203" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="204" ht="45" customHeight="1">
       <x:c r="A204" s="26" t="str">
@@ -8129,6 +11798,24 @@
       <x:c r="K204" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L204" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M204" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N204" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O204" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P204" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q204" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="205" ht="45" customHeight="1">
       <x:c r="A205" s="26" t="str">
@@ -8164,6 +11851,24 @@
       <x:c r="K205" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L205" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M205" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N205" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O205" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P205" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q205" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="206" ht="45" customHeight="1">
       <x:c r="A206" s="26" t="str">
@@ -8199,6 +11904,24 @@
       <x:c r="K206" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L206" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M206" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N206" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O206" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P206" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q206" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="207" ht="45" customHeight="1">
       <x:c r="A207" s="26" t="str">
@@ -8234,6 +11957,24 @@
       <x:c r="K207" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L207" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M207" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N207" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O207" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P207" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q207" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" ht="45" customHeight="1">
       <x:c r="A208" s="26" t="str">
@@ -8269,6 +12010,24 @@
       <x:c r="K208" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L208" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M208" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N208" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O208" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P208" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q208" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="209" ht="45" customHeight="1">
       <x:c r="A209" s="26" t="str">
@@ -8304,6 +12063,24 @@
       <x:c r="K209" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L209" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M209" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N209" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O209" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P209" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q209" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" ht="45" customHeight="1">
       <x:c r="A210" s="26" t="str">
@@ -8339,6 +12116,24 @@
       <x:c r="K210" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L210" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M210" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N210" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O210" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P210" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q210" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="211" ht="45" customHeight="1">
       <x:c r="A211" s="26" t="str">
@@ -8374,6 +12169,24 @@
       <x:c r="K211" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L211" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M211" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N211" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O211" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P211" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q211" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="212" ht="45" customHeight="1">
       <x:c r="A212" s="26" t="str">
@@ -8409,6 +12222,24 @@
       <x:c r="K212" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L212" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M212" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N212" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O212" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P212" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q212" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" ht="45" customHeight="1">
       <x:c r="A213" s="26" t="str">
@@ -8444,6 +12275,24 @@
       <x:c r="K213" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L213" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M213" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N213" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O213" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P213" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q213" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" ht="45" customHeight="1">
       <x:c r="A214" s="26" t="str">
@@ -8479,6 +12328,24 @@
       <x:c r="K214" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L214" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M214" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N214" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O214" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P214" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q214" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="215" ht="45" customHeight="1">
       <x:c r="A215" s="26" t="str">
@@ -8514,6 +12381,24 @@
       <x:c r="K215" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L215" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M215" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N215" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O215" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P215" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q215" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="216" ht="45" customHeight="1">
       <x:c r="A216" s="26" t="str">
@@ -8549,6 +12434,24 @@
       <x:c r="K216" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L216" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M216" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N216" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O216" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P216" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q216" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" ht="45" customHeight="1">
       <x:c r="A217" s="26" t="str">
@@ -8584,6 +12487,24 @@
       <x:c r="K217" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L217" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M217" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N217" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O217" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P217" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q217" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" ht="45" customHeight="1">
       <x:c r="A218" s="26" t="str">
@@ -8619,6 +12540,24 @@
       <x:c r="K218" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L218" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M218" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N218" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O218" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P218" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q218" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="219" ht="45" customHeight="1">
       <x:c r="A219" s="26" t="str">
@@ -8654,6 +12593,24 @@
       <x:c r="K219" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L219" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M219" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N219" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O219" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P219" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q219" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="45" customHeight="1">
       <x:c r="A220" s="26" t="str">
@@ -8689,6 +12646,24 @@
       <x:c r="K220" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L220" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M220" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N220" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O220" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P220" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q220" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="45" customHeight="1">
       <x:c r="A221" s="26" t="str">
@@ -8724,6 +12699,24 @@
       <x:c r="K221" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L221" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M221" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N221" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O221" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P221" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q221" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" ht="45" customHeight="1">
       <x:c r="A222" s="26" t="str">
@@ -8759,6 +12752,24 @@
       <x:c r="K222" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L222" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M222" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N222" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O222" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P222" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q222" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="223" ht="45" customHeight="1">
       <x:c r="A223" s="26" t="str">
@@ -8794,6 +12805,24 @@
       <x:c r="K223" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L223" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M223" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N223" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O223" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P223" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q223" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="224" ht="45" customHeight="1">
       <x:c r="A224" s="26" t="str">
@@ -8829,6 +12858,24 @@
       <x:c r="K224" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L224" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M224" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N224" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O224" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P224" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q224" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="225" ht="45" customHeight="1">
       <x:c r="A225" s="26" t="str">
@@ -8864,6 +12911,24 @@
       <x:c r="K225" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L225" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M225" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N225" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O225" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P225" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q225" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="226" ht="45" customHeight="1">
       <x:c r="A226" s="26" t="str">
@@ -8899,6 +12964,24 @@
       <x:c r="K226" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L226" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M226" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N226" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O226" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P226" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q226" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="227" ht="45" customHeight="1">
       <x:c r="A227" s="26" t="str">
@@ -8934,6 +13017,24 @@
       <x:c r="K227" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L227" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M227" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N227" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O227" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P227" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q227" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="228" ht="45" customHeight="1">
       <x:c r="A228" s="26" t="str">
@@ -8969,6 +13070,24 @@
       <x:c r="K228" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L228" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M228" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N228" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O228" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P228" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q228" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="229" ht="45" customHeight="1">
       <x:c r="A229" s="26" t="str">
@@ -9004,6 +13123,24 @@
       <x:c r="K229" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L229" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M229" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N229" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O229" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P229" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q229" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="230" ht="45" customHeight="1">
       <x:c r="A230" s="26" t="str">
@@ -9039,6 +13176,24 @@
       <x:c r="K230" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L230" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M230" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N230" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O230" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P230" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q230" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="231" ht="45" customHeight="1">
       <x:c r="A231" s="26" t="str">
@@ -9074,6 +13229,24 @@
       <x:c r="K231" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L231" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M231" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N231" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O231" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P231" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q231" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="232" ht="45" customHeight="1">
       <x:c r="A232" s="26" t="str">
@@ -9109,6 +13282,24 @@
       <x:c r="K232" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L232" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M232" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N232" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O232" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P232" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q232" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="233" ht="45" customHeight="1">
       <x:c r="A233" s="26" t="str">
@@ -9144,6 +13335,24 @@
       <x:c r="K233" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L233" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M233" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N233" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O233" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P233" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q233" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="234" ht="45" customHeight="1">
       <x:c r="A234" s="26" t="str">
@@ -9179,6 +13388,24 @@
       <x:c r="K234" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L234" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M234" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N234" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O234" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P234" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q234" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="235" ht="45" customHeight="1">
       <x:c r="A235" s="26" t="str">
@@ -9214,6 +13441,24 @@
       <x:c r="K235" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L235" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M235" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N235" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O235" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P235" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q235" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="236" ht="45" customHeight="1">
       <x:c r="A236" s="26" t="str">
@@ -9249,6 +13494,24 @@
       <x:c r="K236" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L236" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M236" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N236" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O236" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P236" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q236" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="237" ht="45" customHeight="1">
       <x:c r="A237" s="26" t="str">
@@ -9284,6 +13547,24 @@
       <x:c r="K237" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L237" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M237" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N237" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O237" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P237" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q237" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="238" ht="45" customHeight="1">
       <x:c r="A238" s="26" t="str">
@@ -9319,6 +13600,24 @@
       <x:c r="K238" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L238" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M238" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N238" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O238" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P238" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q238" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="239" ht="45" customHeight="1">
       <x:c r="A239" s="26" t="str">
@@ -9354,6 +13653,24 @@
       <x:c r="K239" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L239" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M239" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N239" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O239" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P239" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q239" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="240" ht="45" customHeight="1">
       <x:c r="A240" s="26" t="str">
@@ -9389,6 +13706,24 @@
       <x:c r="K240" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L240" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M240" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N240" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O240" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P240" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q240" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="241" ht="45" customHeight="1">
       <x:c r="A241" s="26" t="str">
@@ -9424,6 +13759,24 @@
       <x:c r="K241" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L241" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M241" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N241" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O241" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P241" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q241" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="242" ht="45" customHeight="1">
       <x:c r="A242" s="26" t="str">
@@ -9459,6 +13812,24 @@
       <x:c r="K242" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L242" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M242" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N242" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O242" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P242" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q242" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="243" ht="45" customHeight="1">
       <x:c r="A243" s="26" t="str">
@@ -9494,6 +13865,24 @@
       <x:c r="K243" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L243" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M243" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N243" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O243" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P243" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q243" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="244" ht="45" customHeight="1">
       <x:c r="A244" s="26" t="str">
@@ -9529,6 +13918,24 @@
       <x:c r="K244" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L244" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M244" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N244" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O244" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P244" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q244" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="245" ht="45" customHeight="1">
       <x:c r="A245" s="26" t="str">
@@ -9564,6 +13971,24 @@
       <x:c r="K245" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L245" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M245" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N245" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O245" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P245" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q245" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="246" ht="45" customHeight="1">
       <x:c r="A246" s="26" t="str">
@@ -9599,6 +14024,24 @@
       <x:c r="K246" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L246" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M246" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N246" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O246" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P246" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q246" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="247" ht="45" customHeight="1">
       <x:c r="A247" s="26" t="str">
@@ -9634,6 +14077,24 @@
       <x:c r="K247" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L247" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M247" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N247" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O247" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P247" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q247" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="248" ht="45" customHeight="1">
       <x:c r="A248" s="26" t="str">
@@ -9669,6 +14130,24 @@
       <x:c r="K248" s="24" t="str">
         <x:v>Official Workshop description and dependency listing reviewed.</x:v>
       </x:c>
+      <x:c r="L248" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M248" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N248" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O248" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P248" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q248" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="249" ht="45" customHeight="1">
       <x:c r="A249" s="26" t="str">
@@ -9704,6 +14183,24 @@
       <x:c r="K249" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L249" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M249" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N249" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O249" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P249" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q249" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="250" ht="45" customHeight="1">
       <x:c r="A250" s="26" t="str">
@@ -9739,6 +14236,24 @@
       <x:c r="K250" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L250" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M250" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N250" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O250" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P250" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q250" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="251" ht="45" customHeight="1">
       <x:c r="A251" s="26" t="str">
@@ -9774,6 +14289,24 @@
       <x:c r="K251" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L251" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M251" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N251" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O251" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P251" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q251" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="252" ht="45" customHeight="1">
       <x:c r="A252" s="26" t="str">
@@ -9809,6 +14342,24 @@
       <x:c r="K252" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L252" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M252" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N252" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O252" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P252" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q252" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="253" ht="45" customHeight="1">
       <x:c r="A253" s="26" t="str">
@@ -9844,6 +14395,24 @@
       <x:c r="K253" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L253" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M253" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N253" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O253" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P253" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q253" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="254" ht="45" customHeight="1">
       <x:c r="A254" s="26" t="str">
@@ -9879,6 +14448,24 @@
       <x:c r="K254" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L254" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M254" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N254" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O254" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P254" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q254" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="255" ht="45" customHeight="1">
       <x:c r="A255" s="26" t="str">
@@ -9914,6 +14501,24 @@
       <x:c r="K255" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L255" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M255" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N255" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O255" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P255" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q255" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="256" ht="45" customHeight="1">
       <x:c r="A256" s="26" t="str">
@@ -9949,6 +14554,24 @@
       <x:c r="K256" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L256" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M256" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N256" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O256" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P256" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q256" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="257" ht="45" customHeight="1">
       <x:c r="A257" s="26" t="str">
@@ -9984,6 +14607,24 @@
       <x:c r="K257" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L257" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M257" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N257" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O257" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P257" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q257" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="258" ht="45" customHeight="1">
       <x:c r="A258" s="26" t="str">
@@ -10019,6 +14660,24 @@
       <x:c r="K258" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L258" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M258" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N258" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O258" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P258" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q258" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="259" ht="45" customHeight="1">
       <x:c r="A259" s="26" t="str">
@@ -10054,6 +14713,24 @@
       <x:c r="K259" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L259" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M259" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N259" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O259" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P259" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q259" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="260" ht="45" customHeight="1">
       <x:c r="A260" s="26" t="str">
@@ -10089,6 +14766,24 @@
       <x:c r="K260" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L260" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M260" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N260" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O260" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P260" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q260" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="261" ht="45" customHeight="1">
       <x:c r="A261" s="26" t="str">
@@ -10124,6 +14819,24 @@
       <x:c r="K261" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L261" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M261" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N261" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O261" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P261" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q261" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="262" ht="45" customHeight="1">
       <x:c r="A262" s="26" t="str">
@@ -10159,6 +14872,24 @@
       <x:c r="K262" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L262" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M262" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N262" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O262" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P262" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q262" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="263" ht="45" customHeight="1">
       <x:c r="A263" s="26" t="str">
@@ -10194,6 +14925,24 @@
       <x:c r="K263" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L263" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M263" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N263" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O263" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P263" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q263" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="264" ht="45" customHeight="1">
       <x:c r="A264" s="26" t="str">
@@ -10229,6 +14978,24 @@
       <x:c r="K264" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L264" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M264" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N264" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O264" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P264" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q264" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="265" ht="45" customHeight="1">
       <x:c r="A265" s="26" t="str">
@@ -10264,6 +15031,24 @@
       <x:c r="K265" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L265" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M265" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N265" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O265" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P265" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q265" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="266" ht="45" customHeight="1">
       <x:c r="A266" s="26" t="str">
@@ -10299,6 +15084,24 @@
       <x:c r="K266" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L266" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M266" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N266" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O266" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P266" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q266" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="267" ht="45" customHeight="1">
       <x:c r="A267" s="26" t="str">
@@ -10334,6 +15137,24 @@
       <x:c r="K267" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L267" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M267" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N267" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O267" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P267" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q267" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="268" ht="45" customHeight="1">
       <x:c r="A268" s="26" t="str">
@@ -10369,6 +15190,24 @@
       <x:c r="K268" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L268" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M268" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N268" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O268" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P268" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q268" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="269" ht="45" customHeight="1">
       <x:c r="A269" s="26" t="str">
@@ -10404,6 +15243,24 @@
       <x:c r="K269" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L269" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M269" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N269" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O269" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P269" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q269" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="270" ht="45" customHeight="1">
       <x:c r="A270" s="26" t="str">
@@ -10439,6 +15296,24 @@
       <x:c r="K270" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L270" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M270" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N270" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O270" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P270" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q270" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="271" ht="45" customHeight="1">
       <x:c r="A271" s="26" t="str">
@@ -10474,6 +15349,24 @@
       <x:c r="K271" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L271" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M271" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N271" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O271" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P271" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q271" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="272" ht="45" customHeight="1">
       <x:c r="A272" s="26" t="str">
@@ -10509,6 +15402,24 @@
       <x:c r="K272" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L272" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M272" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N272" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O272" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P272" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q272" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="273" ht="45" customHeight="1">
       <x:c r="A273" s="26" t="str">
@@ -10544,6 +15455,24 @@
       <x:c r="K273" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L273" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M273" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N273" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O273" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P273" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q273" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="274" ht="45" customHeight="1">
       <x:c r="A274" s="26" t="str">
@@ -10579,6 +15508,24 @@
       <x:c r="K274" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L274" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M274" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N274" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O274" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P274" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q274" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="275" ht="45" customHeight="1">
       <x:c r="A275" s="26" t="str">
@@ -10614,6 +15561,24 @@
       <x:c r="K275" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L275" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M275" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N275" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O275" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P275" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q275" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="276" ht="45" customHeight="1">
       <x:c r="A276" s="26" t="str">
@@ -10649,6 +15614,24 @@
       <x:c r="K276" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L276" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M276" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N276" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O276" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P276" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q276" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="277" ht="45" customHeight="1">
       <x:c r="A277" s="26" t="str">
@@ -10684,6 +15667,24 @@
       <x:c r="K277" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L277" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M277" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N277" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O277" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P277" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q277" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="278" ht="45" customHeight="1">
       <x:c r="A278" s="26" t="str">
@@ -10719,6 +15720,24 @@
       <x:c r="K278" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L278" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M278" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N278" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O278" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P278" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q278" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="279" ht="45" customHeight="1">
       <x:c r="A279" s="26" t="str">
@@ -10754,6 +15773,24 @@
       <x:c r="K279" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L279" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M279" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N279" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O279" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P279" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q279" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="280" ht="45" customHeight="1">
       <x:c r="A280" s="26" t="str">
@@ -10789,6 +15826,24 @@
       <x:c r="K280" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L280" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M280" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N280" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O280" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P280" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q280" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="281" ht="45" customHeight="1">
       <x:c r="A281" s="26" t="str">
@@ -10824,6 +15879,24 @@
       <x:c r="K281" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L281" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M281" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N281" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O281" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P281" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q281" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="282" ht="45" customHeight="1">
       <x:c r="A282" s="26" t="str">
@@ -10859,6 +15932,24 @@
       <x:c r="K282" s="24" t="str">
         <x:v>Official Workshop description and dependency listing reviewed.</x:v>
       </x:c>
+      <x:c r="L282" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M282" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N282" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O282" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P282" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q282" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="283" ht="45" customHeight="1">
       <x:c r="A283" s="26" t="str">
@@ -10894,6 +15985,24 @@
       <x:c r="K283" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L283" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M283" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N283" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O283" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P283" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q283" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="284" ht="45" customHeight="1">
       <x:c r="A284" s="26" t="str">
@@ -10929,6 +16038,24 @@
       <x:c r="K284" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L284" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M284" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N284" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O284" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P284" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q284" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="285" ht="45" customHeight="1">
       <x:c r="A285" s="26" t="str">
@@ -10964,6 +16091,24 @@
       <x:c r="K285" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L285" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M285" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N285" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O285" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P285" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q285" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="286" ht="45" customHeight="1">
       <x:c r="A286" s="26" t="str">
@@ -10999,6 +16144,24 @@
       <x:c r="K286" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L286" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M286" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N286" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O286" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P286" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q286" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="287" ht="45" customHeight="1">
       <x:c r="A287" s="26" t="str">
@@ -11034,6 +16197,24 @@
       <x:c r="K287" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L287" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M287" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N287" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O287" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P287" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q287" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="288" ht="45" customHeight="1">
       <x:c r="A288" s="26" t="str">
@@ -11069,6 +16250,24 @@
       <x:c r="K288" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L288" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M288" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N288" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O288" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P288" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q288" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="289" ht="45" customHeight="1">
       <x:c r="A289" s="26" t="str">
@@ -11104,6 +16303,24 @@
       <x:c r="K289" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L289" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M289" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N289" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O289" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P289" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q289" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="290" ht="45" customHeight="1">
       <x:c r="A290" s="26" t="str">
@@ -11139,6 +16356,24 @@
       <x:c r="K290" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L290" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M290" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N290" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O290" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P290" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q290" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="291" ht="45" customHeight="1">
       <x:c r="A291" s="26" t="str">
@@ -11174,6 +16409,24 @@
       <x:c r="K291" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L291" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M291" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N291" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O291" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P291" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q291" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="292" ht="45" customHeight="1">
       <x:c r="A292" s="26" t="str">
@@ -11209,6 +16462,24 @@
       <x:c r="K292" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L292" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M292" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N292" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O292" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P292" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q292" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="293" ht="45" customHeight="1">
       <x:c r="A293" s="26" t="str">
@@ -11244,6 +16515,24 @@
       <x:c r="K293" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L293" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M293" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N293" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O293" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P293" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q293" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="294" ht="45" customHeight="1">
       <x:c r="A294" s="26" t="str">
@@ -11279,6 +16568,24 @@
       <x:c r="K294" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L294" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M294" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N294" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O294" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P294" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q294" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
     <x:row r="295" ht="45" customHeight="1">
       <x:c r="A295" s="26" t="str">
@@ -11314,11 +16621,29 @@
       <x:c r="K295" s="24" t="str">
         <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
       </x:c>
+      <x:c r="L295" s="27" t="str">
+        <x:v>Pending mapping</x:v>
+      </x:c>
+      <x:c r="M295" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="N295" s="27" t="str">
+        <x:v>Pending</x:v>
+      </x:c>
+      <x:c r="O295" s="27" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="P295" s="27" t="str">
+        <x:v>Not pinned</x:v>
+      </x:c>
+      <x:c r="Q295" s="27" t="str">
+        <x:v>Not runtime tested</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R501556a5ed8a4d3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02fc116f69be48fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rb14d52f710be419b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R82076cf7eab245a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R57c7d5f6c12c45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R325a6d1b41b247f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -478,7 +478,7 @@
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Six per-row evidence/decision fields have been added to the register. Row-level reviews, feature assignments, and final dispositions remain pending.</x:v>
+        <x:v>The first six framework entries have source/metadata notes and provisional use boundaries; deeper API/runtime checks remain open, and the other 288 entries still need source review.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -502,7 +502,7 @@
         <x:v>Current RWT boundary</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>The local client/server package IDs and order match in this snapshot, but server enforcement is disabled and its build hash is unresolved. Official release notes are not proof that this local server runs that release. Custom transfers and scenario joining remain untested.</x:v>
+        <x:v>The 294 local client/server IDs and order match, but the server does not enforce them. The Windows server archive matches the published RWT 26.8.31.1 asset; the client DLL is pinned separately. Custom transfers, visits, and scenario joining remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1090,37 +1090,37 @@
         <x:v>Mod framework</x:v>
       </x:c>
       <x:c r="G2" s="24" t="str">
-        <x:v>Required by RimWorld Together and Vanilla Expanded Framework in their published listings.</x:v>
+        <x:v>Listed as a dependency by RWT and several selected frameworks. Rimrooms requires it only for the selected co-op path, not solo Core play.</x:v>
       </x:c>
       <x:c r="H2" s="24" t="str">
-        <x:v>Keep the framework available for the profile's dependent mods. Reuse public APIs only when a specific Backrooms integration needs them; the company mod must not duplicate framework services.</x:v>
+        <x:v>Keep the shared library available for dependent co-op/profile mods. Add a Rimrooms patch only if a specific feature needs one.</x:v>
       </x:c>
       <x:c r="I2" s="24" t="str">
-        <x:v>Load before consuming mods. Verify the exact 1.6 package version and transitive dependencies; avoid making a framework a Backrooms core requirement without a concrete integration.</x:v>
+        <x:v>Preserve the required load-before-Core order; record both local metadata and active assembly identities because their version strings differ.</x:v>
       </x:c>
       <x:c r="J2" s="24" t="str">
-        <x:v>Low to medium: pin the exact 1.6 build and dependency order; consume public APIs only when an integration needs them.</x:v>
+        <x:v>Retest the dependency order if Harmony or a dependent RWT build changes.</x:v>
       </x:c>
       <x:c r="K2" s="24" t="str">
-        <x:v>Required by the official RWT and VEF listings; exact local build still needs pinning.</x:v>
+        <x:v>Workshop description and installed metadata reviewed; source/API and runtime checks pending.</x:v>
       </x:c>
       <x:c r="L2" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M2" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2009463077-brrainz.harmony.md</x:v>
       </x:c>
       <x:c r="N2" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Workshop and installed metadata reviewed; Rimrooms compatibility pending</x:v>
       </x:c>
       <x:c r="O2" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: required only for the selected RWT co-op path; optional for solo Core play.</x:v>
       </x:c>
       <x:c r="P2" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; metadata 2.4.2.0; active DLL 2.4.1.0+789df191bbaf6610232d50e7ef7dddc0d2812549</x:v>
       </x:c>
       <x:c r="Q2" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; pinned co-op profile check pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="45" customHeight="1">
@@ -1555,37 +1555,37 @@
         <x:v>Mod framework</x:v>
       </x:c>
       <x:c r="G11" s="24" t="str">
-        <x:v>Selected profile framework; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; optional storage framework in this profile, not a Rimrooms core dependency.</x:v>
       </x:c>
       <x:c r="H11" s="24" t="str">
-        <x:v>Keep the framework available for the profile's dependent mods. Reuse public APIs only when a specific Backrooms integration needs them; the company mod must not duplicate framework services.</x:v>
+        <x:v>Consider standard interoperability for facility stock and recovered evidence only if it improves the player's existing storage workflow.</x:v>
       </x:c>
       <x:c r="I11" s="24" t="str">
-        <x:v>Load before consuming mods. Verify the exact 1.6 package version and transitive dependencies; avoid making a framework a Backrooms core requirement without a concrete integration.</x:v>
+        <x:v>Use a narrow bridge only for a reproduced storage need; keep vanilla stockpiles useful when ASF is absent.</x:v>
       </x:c>
       <x:c r="J11" s="24" t="str">
-        <x:v>Low to medium: pin the exact 1.6 build and dependency order; consume public APIs only when an integration needs them.</x:v>
+        <x:v>Test item filters, display, and temperature only if an integration is selected.</x:v>
       </x:c>
       <x:c r="K11" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Workshop description/change notes and local About.xml reviewed; exact API and runtime interactions pending.</x:v>
       </x:c>
       <x:c r="L11" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M11" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3033901359-adaptive.storage.framework.md</x:v>
       </x:c>
       <x:c r="N11" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Workshop, change notes, and installed metadata reviewed; compatibility pending</x:v>
       </x:c>
       <x:c r="O11" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional storage interoperability; no Rimrooms core dependency planned.</x:v>
       </x:c>
       <x:c r="P11" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support; no modVersion stated</x:v>
       </x:c>
       <x:c r="Q11" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; custom storage/evidence behavior pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="45" customHeight="1">
@@ -1608,37 +1608,37 @@
         <x:v>Mod framework</x:v>
       </x:c>
       <x:c r="G12" s="24" t="str">
-        <x:v>Selected profile framework; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; the framework adds no vehicles by itself and is not a Rimrooms core dependency.</x:v>
       </x:c>
       <x:c r="H12" s="24" t="str">
-        <x:v>Keep the framework available for the profile's dependent mods. Reuse public APIs only when a specific Backrooms integration needs them; the company mod must not duplicate framework services.</x:v>
+        <x:v>Consider future vehicle-based expedition or outpost support only if it fits Odyssey/Gravship Expanded and verified RWT travel.</x:v>
       </x:c>
       <x:c r="I12" s="24" t="str">
-        <x:v>Load before consuming mods. Verify the exact 1.6 package version and transitive dependencies; avoid making a framework a Backrooms core requirement without a concrete integration.</x:v>
+        <x:v>Keep the machine gate as the Backrooms entry point and preserve native gravship behavior; do not add vehicles solely because the framework is installed.</x:v>
       </x:c>
       <x:c r="J12" s="24" t="str">
-        <x:v>Low to medium: pin the exact 1.6 build and dependency order; consume public APIs only when an integration needs them.</x:v>
+        <x:v>Local metadata lists RimThreaded as incompatible; vehicle, save, and multiplayer interactions are untested.</x:v>
       </x:c>
       <x:c r="K12" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Workshop description and local About.xml reviewed; vehicle, save, and multiplayer interactions pending.</x:v>
       </x:c>
       <x:c r="L12" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M12" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3014915404-SmashPhil.VehicleFramework.md</x:v>
       </x:c>
       <x:c r="N12" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Workshop and installed metadata reviewed; compatibility pending</x:v>
       </x:c>
       <x:c r="O12" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional vehicle interoperability only if it fits expeditions/outposts and the gravship plan.</x:v>
       </x:c>
       <x:c r="P12" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; Vehicle Framework 1.6.2144</x:v>
       </x:c>
       <x:c r="Q12" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; vehicle/RWT travel behavior pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="45" customHeight="1">
@@ -1661,37 +1661,37 @@
         <x:v>Mod framework</x:v>
       </x:c>
       <x:c r="G13" s="24" t="str">
-        <x:v>Selected profile framework; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; optional profile XML tool and not a Rimrooms core dependency.</x:v>
       </x:c>
       <x:c r="H13" s="24" t="str">
-        <x:v>Keep the framework available for the profile's dependent mods. Reuse public APIs only when a specific Backrooms integration needs them; the company mod must not duplicate framework services.</x:v>
+        <x:v>Revisit only if a real feature needs a documented XML patch or settings operation.</x:v>
       </x:c>
       <x:c r="I13" s="24" t="str">
-        <x:v>Load before consuming mods. Verify the exact 1.6 package version and transitive dependencies; avoid making a framework a Backrooms core requirement without a concrete integration.</x:v>
+        <x:v>Keep core definitions and settings independent; no custom XML Extensions operation selected.</x:v>
       </x:c>
       <x:c r="J13" s="24" t="str">
-        <x:v>Low to medium: pin the exact 1.6 build and dependency order; consume public APIs only when an integration needs them.</x:v>
+        <x:v>Check load order and patches only if Rimrooms adopts a documented operation.</x:v>
       </x:c>
       <x:c r="K13" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Workshop description and local About.xml reviewed; operation/API and runtime checks pending.</x:v>
       </x:c>
       <x:c r="L13" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-COMPAT</x:v>
       </x:c>
       <x:c r="M13" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2574315206-imranfish.xmlextensions.md</x:v>
       </x:c>
       <x:c r="N13" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Workshop and installed metadata reviewed; specific API use pending</x:v>
       </x:c>
       <x:c r="O13" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional profile tool; no Rimrooms dependency planned.</x:v>
       </x:c>
       <x:c r="P13" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support; no modVersion stated</x:v>
       </x:c>
       <x:c r="Q13" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; no custom XML Extensions use selected.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
@@ -1714,37 +1714,37 @@
         <x:v>Mod framework</x:v>
       </x:c>
       <x:c r="G14" s="24" t="str">
-        <x:v>Selected profile framework; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; optional shared library used by profile mods, not a Rimrooms core dependency.</x:v>
       </x:c>
       <x:c r="H14" s="24" t="str">
-        <x:v>Keep the framework available for the profile's dependent mods. Reuse public APIs only when a specific Backrooms integration needs them; the company mod must not duplicate framework services.</x:v>
+        <x:v>Leave existing HugsLib-dependent mods usable; treat shared logs as support evidence when supplied by a player.</x:v>
       </x:c>
       <x:c r="I14" s="24" t="str">
-        <x:v>Load before consuming mods. Verify the exact 1.6 package version and transitive dependencies; avoid making a framework a Backrooms core requirement without a concrete integration.</x:v>
+        <x:v>Do not require HugsLib services or log upload for campaign play; preserve the local after-Core load order.</x:v>
       </x:c>
       <x:c r="J14" s="24" t="str">
-        <x:v>Low to medium: pin the exact 1.6 build and dependency order; consume public APIs only when an integration needs them.</x:v>
+        <x:v>Confirm startup and support-log flow on the eventual clean and selected mod profiles.</x:v>
       </x:c>
       <x:c r="K14" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Workshop description and local About.xml reviewed; Rimrooms service and runtime interactions pending.</x:v>
       </x:c>
       <x:c r="L14" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-COMPAT</x:v>
       </x:c>
       <x:c r="M14" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/818773962-UnlimitedHugs.HugsLib.md</x:v>
       </x:c>
       <x:c r="N14" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Workshop and installed metadata reviewed; compatibility pending</x:v>
       </x:c>
       <x:c r="O14" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional profile library; no direct Rimrooms dependency planned.</x:v>
       </x:c>
       <x:c r="P14" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local description version 12.0.0</x:v>
       </x:c>
       <x:c r="Q14" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; no direct Rimrooms service use selected.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="45" customHeight="1">
@@ -1767,37 +1767,37 @@
         <x:v>Mod framework</x:v>
       </x:c>
       <x:c r="G15" s="24" t="str">
-        <x:v>Required when either selected Vanilla Gravship Expanded chapter is enabled.</x:v>
+        <x:v>Harmony required; dependency of the selected Gravship Expanded chapters and optional to the Core-only campaign.</x:v>
       </x:c>
       <x:c r="H15" s="24" t="str">
-        <x:v>Keep the framework available for the profile's dependent mods. Reuse public APIs only when a specific Backrooms integration needs them; the company mod must not duplicate framework services.</x:v>
+        <x:v>Retain it for the chosen late-game gravship chain; use its services only through a selected, documented dependency.</x:v>
       </x:c>
       <x:c r="I15" s="24" t="str">
-        <x:v>Load before consuming mods. Verify the exact 1.6 package version and transitive dependencies; avoid making a framework a Backrooms core requirement without a concrete integration.</x:v>
+        <x:v>Keep gravship content behind the DLC/mod boundary; preserve a complete gate campaign without VEF or Odyssey.</x:v>
       </x:c>
       <x:c r="J15" s="24" t="str">
-        <x:v>Low to medium: pin the exact 1.6 build and dependency order; consume public APIs only when an integration needs them.</x:v>
+        <x:v>Local metadata lists RangeAnimalFramework as incompatible; check it against the final 294 profile and VGE warnings.</x:v>
       </x:c>
       <x:c r="K15" s="24" t="str">
-        <x:v>Official Workshop description and dependency listing reviewed.</x:v>
+        <x:v>Workshop description and local About.xml reviewed; specific API, gravship conflicts, and combined-profile behavior pending.</x:v>
       </x:c>
       <x:c r="L15" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M15" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2023507013-OskarPotocki.VanillaFactionsExpanded.Core.md</x:v>
       </x:c>
       <x:c r="N15" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Workshop and installed metadata reviewed; VGE runtime checks pending</x:v>
       </x:c>
       <x:c r="O15" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: required by the selected Gravship Expanded chain; optional to the Core-only Rimrooms campaign.</x:v>
       </x:c>
       <x:c r="P15" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support; no modVersion stated</x:v>
       </x:c>
       <x:c r="Q15" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; clean VGE and combined-profile checks pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="45" customHeight="1">
@@ -16643,7 +16643,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02fc116f69be48fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b108bc1453f48af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R57c7d5f6c12c45c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R325a6d1b41b247f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R33055fb13a884bd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R15bfcc9aaae54e2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -478,7 +478,7 @@
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>The first six framework entries have source/metadata notes and provisional use boundaries; deeper API/runtime checks remain open, and the other 288 entries still need source review.</x:v>
+        <x:v>Twelve profile rows have source/metadata notes and provisional use boundaries; API/runtime checks remain open, and the other 282 entries need their first source review.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -690,7 +690,7 @@
         <x:v>Materials, cargo, and recovered resources</x:v>
       </x:c>
       <x:c r="B41" s="17" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -834,7 +834,7 @@
         <x:v>Staff work-flow quality of life</x:v>
       </x:c>
       <x:c r="B59" s="17" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -1111,13 +1111,13 @@
         <x:v>docs/research/reviews/mods/2009463077-brrainz.harmony.md</x:v>
       </x:c>
       <x:c r="N2" s="27" t="str">
-        <x:v>Workshop and installed metadata reviewed; Rimrooms compatibility pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O2" s="27" t="str">
         <x:v>Provisional: required only for the selected RWT co-op path; optional for solo Core play.</x:v>
       </x:c>
       <x:c r="P2" s="27" t="str">
-        <x:v>RimWorld 1.6.4871 rev590; metadata 2.4.2.0; active DLL 2.4.1.0+789df191bbaf6610232d50e7ef7dddc0d2812549</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; Harmony About.xml 2.4.2.0; active DLL product 2.4.1.0+789df191bbaf6610232d50e7ef7dddc0d2812549</x:v>
       </x:c>
       <x:c r="Q2" s="27" t="str">
         <x:v>Not runtime tested; pinned co-op profile check pending.</x:v>
@@ -1143,37 +1143,37 @@
         <x:v>Staff psychology, relationships, and faction standing</x:v>
       </x:c>
       <x:c r="G3" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Selected profile entry; changes pawn mood/opinion rules but is not a Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="H3" s="24" t="str">
-        <x:v>Use the active trait, memory, social-fight, relationship, conversion, and faction-reaction rules when generating applicants, workplace incidents, and crew histories. Keep the company's evaluation based on actual pawn traits, skills, and relationships.</x:v>
+        <x:v>Let staff keep the profile's own reactions. Avoid making Rimrooms progression depend on its specific mood balance.</x:v>
       </x:c>
       <x:c r="I3" s="24" t="str">
-        <x:v>Medium: these mods change the staff and visitor experience. Avoid replacing their thought, relation, or faction logic; check how hostility and guest incidents affect company reputation.</x:v>
+        <x:v>Keep any future company thoughts isolated and additive; do not overwrite its thought definitions.</x:v>
       </x:c>
       <x:c r="J3" s="24" t="str">
-        <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
+        <x:v>Local and Workshop metadata stop at RimWorld 1.4; its page warns about ThoughtDef overrides and load order.</x:v>
       </x:c>
       <x:c r="K3" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Workshop page and installed metadata reviewed; declared support stops at 1.4; 1.6 compatibility pending.</x:v>
       </x:c>
       <x:c r="L3" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M3" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1543063349-SF.Grim.Reality.md</x:v>
       </x:c>
       <x:c r="N3" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O3" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: retain as a selected-profile compatibility case; do not depend on its thought balance until 1.6 support is demonstrated.</x:v>
       </x:c>
       <x:c r="P3" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata lists RimWorld 1.0-1.4</x:v>
       </x:c>
       <x:c r="Q3" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; mood/thought and social behavior with five DLC and profile mods pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="45" customHeight="1">
@@ -1196,37 +1196,37 @@
         <x:v>Interface, scenario setup, and quality of life</x:v>
       </x:c>
       <x:c r="G4" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; optional startup/support utility and not a Rimrooms gameplay dependency.</x:v>
       </x:c>
       <x:c r="H4" s="24" t="str">
-        <x:v>Preserve the mod's interface or scenario convenience. The Backrooms Operations board should add a focused company view and link to existing vanilla/mod tabs instead of replacing unrelated menus.</x:v>
+        <x:v>Preserve its existing progress display for startup, map generation, and save loading.</x:v>
       </x:c>
       <x:c r="I4" s="24" t="str">
-        <x:v>Low: avoid patching visual-only or convenience features. Scenario editors may be useful for development but must not become a runtime dependency or a campaign progression requirement.</x:v>
+        <x:v>No Rimrooms screen or startup patch planned.</x:v>
       </x:c>
       <x:c r="J4" s="24" t="str">
-        <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
+        <x:v>Harmony/load order; page lists conflicts with RimThemes and Startup Impact Continued. Neither appears in current inventory names/IDs.</x:v>
       </x:c>
       <x:c r="K4" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Official Workshop page and installed metadata reviewed; startup compatibility pending.</x:v>
       </x:c>
       <x:c r="L4" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-COMPAT</x:v>
       </x:c>
       <x:c r="M4" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3535481557-ilyvion.LoadingProgress.md</x:v>
       </x:c>
       <x:c r="N4" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O4" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional support utility; no Rimrooms runtime dependency.</x:v>
       </x:c>
       <x:c r="P4" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; Loading Progress 0.16.0</x:v>
       </x:c>
       <x:c r="Q4" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; exact profile startup and named conflicts pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="45" customHeight="1">
@@ -1576,13 +1576,13 @@
         <x:v>docs/research/reviews/mods/3033901359-adaptive.storage.framework.md</x:v>
       </x:c>
       <x:c r="N11" s="27" t="str">
-        <x:v>Workshop, change notes, and installed metadata reviewed; compatibility pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O11" s="27" t="str">
         <x:v>Provisional: optional storage interoperability; no Rimrooms core dependency planned.</x:v>
       </x:c>
       <x:c r="P11" s="27" t="str">
-        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support; no modVersion stated</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support and no modVersion</x:v>
       </x:c>
       <x:c r="Q11" s="27" t="str">
         <x:v>Not runtime tested; custom storage/evidence behavior pending.</x:v>
@@ -1629,7 +1629,7 @@
         <x:v>docs/research/reviews/mods/3014915404-SmashPhil.VehicleFramework.md</x:v>
       </x:c>
       <x:c r="N12" s="27" t="str">
-        <x:v>Workshop and installed metadata reviewed; compatibility pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O12" s="27" t="str">
         <x:v>Provisional: optional vehicle interoperability only if it fits expeditions/outposts and the gravship plan.</x:v>
@@ -1682,16 +1682,16 @@
         <x:v>docs/research/reviews/mods/2574315206-imranfish.xmlextensions.md</x:v>
       </x:c>
       <x:c r="N13" s="27" t="str">
-        <x:v>Workshop and installed metadata reviewed; specific API use pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O13" s="27" t="str">
         <x:v>Provisional: optional profile tool; no Rimrooms dependency planned.</x:v>
       </x:c>
       <x:c r="P13" s="27" t="str">
-        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support; no modVersion stated</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support and no modVersion</x:v>
       </x:c>
       <x:c r="Q13" s="27" t="str">
-        <x:v>Not runtime tested; no custom XML Extensions use selected.</x:v>
+        <x:v>Not runtime tested; no custom XML Extension use selected.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="45" customHeight="1">
@@ -1735,10 +1735,10 @@
         <x:v>docs/research/reviews/mods/818773962-UnlimitedHugs.HugsLib.md</x:v>
       </x:c>
       <x:c r="N14" s="27" t="str">
-        <x:v>Workshop and installed metadata reviewed; compatibility pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O14" s="27" t="str">
-        <x:v>Provisional: optional profile library; no direct Rimrooms dependency planned.</x:v>
+        <x:v>Provisional: optional library for profile mods; no direct Rimrooms dependency planned.</x:v>
       </x:c>
       <x:c r="P14" s="27" t="str">
         <x:v>RimWorld 1.6.4871 rev590; local description version 12.0.0</x:v>
@@ -1788,13 +1788,13 @@
         <x:v>docs/research/reviews/mods/2023507013-OskarPotocki.VanillaFactionsExpanded.Core.md</x:v>
       </x:c>
       <x:c r="N15" s="27" t="str">
-        <x:v>Workshop and installed metadata reviewed; VGE runtime checks pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O15" s="27" t="str">
         <x:v>Provisional: required by the selected Gravship Expanded chain; optional to the Core-only Rimrooms campaign.</x:v>
       </x:c>
       <x:c r="P15" s="27" t="str">
-        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support; no modVersion stated</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists 1.6 support and no modVersion</x:v>
       </x:c>
       <x:c r="Q15" s="27" t="str">
         <x:v>Not runtime tested; clean VGE and combined-profile checks pending.</x:v>
@@ -1817,40 +1817,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3357749890</x:v>
       </x:c>
       <x:c r="F16" s="24" t="str">
-        <x:v>Materials, cargo, and recovered resources</x:v>
+        <x:v>Staff work-flow quality of life</x:v>
       </x:c>
       <x:c r="G16" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; selected work convenience, not a Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="H16" s="24" t="str">
-        <x:v>Use carrying, item handling, harvest, and salvage rules to shape expedition kit limits and recovered-cargo value. Preserve each mod's normal material and weight behavior; add only a Backrooms cargo manifest and appraisal layer.</x:v>
+        <x:v>Let players use its stump, blight, and mature-plant orders when managing facility or outpost grounds.</x:v>
       </x:c>
       <x:c r="I16" s="24" t="str">
-        <x:v>Medium: weight, stack, yield, and destruction rules affect mission capacity and valuation. Reconcile cargo accounting with item transfers and avoid duplicate salvage or recipe patches.</x:v>
+        <x:v>Keep Rimrooms roles on native work orders and avoid reassigning its designations.</x:v>
       </x:c>
       <x:c r="J16" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Verify queued cutting/harvest jobs and overlapping plant-management mods on the selected DLC/profile.</x:v>
       </x:c>
       <x:c r="K16" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Workshop description/change notes and installed metadata reviewed; work-queue interaction pending.</x:v>
       </x:c>
       <x:c r="L16" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M16" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3357749890-Arylice.Rimworld.AutomaticStumpChopping.md</x:v>
       </x:c>
       <x:c r="N16" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O16" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional job convenience; preserve existing orders and do not add a Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P16" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; Automatic Stump Chopping 1.0</x:v>
       </x:c>
       <x:c r="Q16" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; job queue and DLC plant interactions pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="45" customHeight="1">
@@ -1873,37 +1873,37 @@
         <x:v>Animals and field support</x:v>
       </x:c>
       <x:c r="G17" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; optional animal/outpost behavior, not a Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="H17" s="24" t="str">
-        <x:v>Use animals for company security, cargo, food, breeding, and field support when the installed content allows it. Keep staff hiring and mission completion viable without a particular animal species or animal mod.</x:v>
+        <x:v>Leave animal grazing and plant regrowth to the existing profile rules.</x:v>
       </x:c>
       <x:c r="I17" s="24" t="str">
-        <x:v>Low to medium: respect each mod's animal, pen, medical, and apparel definitions. Check load order and travel/ownership when animals accompany expedition teams.</x:v>
+        <x:v>Do not create a second grazing system; keep outpost and facility support independent of it.</x:v>
       </x:c>
       <x:c r="J17" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>The page warns that other plant-ingestion changes may conflict; exact animal/plant rows still need review.</x:v>
       </x:c>
       <x:c r="K17" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Official Workshop page and installed metadata reviewed; plant/animal overlap pending.</x:v>
       </x:c>
       <x:c r="L17" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-OUT;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M17" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2302739121-kittahkhan.grazeup.md</x:v>
       </x:c>
       <x:c r="N17" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O17" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal/outpost behavior; no Rimrooms dependency planned.</x:v>
       </x:c>
       <x:c r="P17" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml lists support through 1.6; no modVersion stated</x:v>
       </x:c>
       <x:c r="Q17" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; plant-ingestion and animal-profile interactions pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="45" customHeight="1">
@@ -1926,37 +1926,37 @@
         <x:v>World operations, contracts, and commerce</x:v>
       </x:c>
       <x:c r="G18" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Harmony required; profile also has Trade Ships Drop Spot and Trade Ships No Matter What.</x:v>
       </x:c>
       <x:c r="H18" s="24" t="str">
-        <x:v>Use world events, factions, comms, traders, and saleable goods to support company contracts, procurement, outposts, and revenue. Add company jobs through a dedicated Operations interface while honoring the profile's comms and quest settings.</x:v>
+        <x:v>May help players arrange purchases; Rimrooms contracts must not assume an orbital ship can be called.</x:v>
       </x:c>
       <x:c r="I18" s="24" t="str">
-        <x:v>Medium to high: world objects, quests, traders, and site creation require exact RimWorld Together synchronization review. Keep the company ledger distinct from vanilla silver and other mods' transaction state.</x:v>
+        <x:v>Leave calls and trader options on the existing Comms Console; no Rimrooms trade-ship override planned.</x:v>
       </x:c>
       <x:c r="J18" s="24" t="str">
-        <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
+        <x:v>Direct Steam page fetch was rate-limited. Combined trader type, landing spot, goods, price, cooldown, and modded-item behavior are unknown.</x:v>
       </x:c>
       <x:c r="K18" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Installed metadata and indexed official listing reviewed; full page/API/runtime evidence pending.</x:v>
       </x:c>
       <x:c r="L18" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M18" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3722921543-zal.calltradeships.md</x:v>
       </x:c>
       <x:c r="N18" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O18" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional trade convenience; no Rimrooms dependency and no contract guarantee of a called ship.</x:v>
       </x:c>
       <x:c r="P18" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; Call Trade Ships (Continued) 1.0.1</x:v>
       </x:c>
       <x:c r="Q18" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify with Trade Ships Drop Spot and Trade Ships No Matter What.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="45" customHeight="1">
@@ -1979,37 +1979,37 @@
         <x:v>Power and industrial infrastructure</x:v>
       </x:c>
       <x:c r="G19" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>No dependency; optional map setup utility, not a Rimrooms power feature.</x:v>
       </x:c>
       <x:c r="H19" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Keep generated facility/outpost maps usable without moving natural geothermal sites.</x:v>
       </x:c>
       <x:c r="I19" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>No Rimrooms adapter or map-generation dependency planned.</x:v>
       </x:c>
       <x:c r="J19" s="24" t="str">
-        <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
+        <x:v>Publisher says it is intended for a new map; existing-map use needs God Mode.</x:v>
       </x:c>
       <x:c r="K19" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Official Workshop page and installed metadata reviewed; map behavior pending.</x:v>
       </x:c>
       <x:c r="L19" s="27" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M19" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1547361568-LingLuo.MoveSteamGeyser.md</x:v>
       </x:c>
       <x:c r="N19" s="27" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O19" s="27" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional map setup utility; no Rimrooms dependency or generated-terrain reliance.</x:v>
       </x:c>
       <x:c r="P19" s="27" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata lists 1.0-1.6 support; no modVersion stated</x:v>
       </x:c>
       <x:c r="Q19" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; new-map and existing-save behavior pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="45" customHeight="1">
@@ -16643,7 +16643,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b108bc1453f48af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab2820c6ecdd448f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R33055fb13a884bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R15bfcc9aaae54e2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R74a09034959942c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R11cfac814cf7453b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -82,7 +82,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -148,6 +148,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -446,7 +449,7 @@
         <x:v>Selected multiplayer model</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>Separate company branches; enable only activities verified on the pinned RWT client/server build. No live shared-map control or global company research contract.</x:v>
+        <x:v>Separate company branches; favor offline visits, supply/aid exchange, and shared investigation stories if confirmed. No shared-map control or automatic global research.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -478,7 +481,7 @@
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Twelve profile rows have source/metadata notes and provisional use boundaries; API/runtime checks remain open, and the other 282 entries need their first source review.</x:v>
+        <x:v>Thirteen profile rows now have source/metadata notes and provisional use boundaries; 281 remain pending. No combined-profile runtime compatibility is established.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -486,7 +489,7 @@
         <x:v>Technology exchange</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>Design a transferable Backrooms research dossier; each receiving branch studies it locally. RWT does not document built-in shared research. Confirm modded-item transfer support before enabling this feature.</x:v>
+        <x:v>Trade a Backrooms research dossier as cargo; the receiving company studies it locally. Custom-item transfer is untested; research does not unlock automatically for both branches.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -494,7 +497,7 @@
         <x:v>Facility visits</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>The Workshop description advertises visits. Exact online/offline behavior, server settings, and activity semantics are unverified; validate against the pinned release before designing features around visits.</x:v>
+        <x:v>Official RWT guidance lists offline visits and raids. Exact activity options and the visit experience remain untested on the pinned build.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -502,7 +505,7 @@
         <x:v>Current RWT boundary</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>The 294 local client/server IDs and order match, but the server does not enforce them. The Windows server archive matches the published RWT 26.8.31.1 asset; the client DLL is pinned separately. Custom transfers, visits, and scenario joining remain untested.</x:v>
+        <x:v>Local client/server IDs and order match, but the server does not enforce them. The server release and client artifact are pinned; separate starts, offline visits, supply/aid transfer, and reconnect checks remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -11393,7 +11396,7 @@
         <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="45" customHeight="1">
+    <x:row r="197" ht="66" hidden="0" customHeight="1">
       <x:c r="A197" s="26" t="str">
         <x:v>196</x:v>
       </x:c>
@@ -11410,40 +11413,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3005289691</x:v>
       </x:c>
       <x:c r="F197" s="24" t="str">
-        <x:v>Multiplayer: guild and world exchange</x:v>
+        <x:v>Multiplayer: separate colonies and shared-world exchange</x:v>
       </x:c>
       <x:c r="G197" s="24" t="str">
-        <x:v>Selected co-op target; optional to a solo Backrooms install. Official Workshop description advertises separate colonies and several co-op/world activities; exact runtime and transfer behavior must be verified against the pinned build.</x:v>
+        <x:v>Selected co-op target; optional to solo play. Local metadata supports RimWorld 1.5/1.6 and requires Harmony.</x:v>
       </x:c>
       <x:c r="H197" s="24" t="str">
-        <x:v>Use RWT's advertised separate-colony model for cooperative company branches. The Workshop description lists activities such as visiting, raiding, spying, trading, factions/guilds, roads, and sites. Keep company research local; enable item/pawn exchange and other actions only after testing the exact client/server build and settings.</x:v>
+        <x:v>Players run separate companies; visits, supplies, aid, and case reports can link their stories if the pinned build supports them.</x:v>
       </x:c>
       <x:c r="I197" s="24" t="str">
-        <x:v>Keep integration behind one optional adapter. Inspect the pinned release's supported APIs and settings; preserve local branch ownership, detect disabled features, and use transaction receipts only for exchanges proven to work. Do not patch server internals or assume online/offline visit behavior.</x:v>
+        <x:v>Use supported RWT activities where they fit. Keep each company's facility, gate, discoveries, research, and ledger on its own branch. Do not assume custom dossier or gear transfers.</x:v>
       </x:c>
       <x:c r="J197" s="24" t="str">
-        <x:v>High: local client/server package IDs and order match in the 2026-09-27 snapshot, but the server has AllowAllMods=true, EnforceSettings=false, ModOrder=null, and an unresolved product hash. Wiki details could not be retrieved (HTTP 403). Do not assume live control, transfer, visit, or scenario-join semantics; validate them in the pinned release.</x:v>
+        <x:v>Official docs list offline visits/raids and item/pawn exchange. The local activity settings and exact results remain untested; the server does not enforce mod order/settings.</x:v>
       </x:c>
       <x:c r="K197" s="24" t="str">
-        <x:v>Official Workshop/release pages and local profile snapshot reviewed. RWT wiki returned HTTP 403; local server release identity, exact activity semantics, runtime behavior, and Backrooms adapters remain pending.</x:v>
-      </x:c>
-      <x:c r="L197" s="27" t="str">
-        <x:v>Pending mapping</x:v>
-      </x:c>
-      <x:c r="M197" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="N197" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="O197" s="27" t="str">
-        <x:v>Pending review</x:v>
-      </x:c>
-      <x:c r="P197" s="27" t="str">
-        <x:v>Not pinned</x:v>
-      </x:c>
-      <x:c r="Q197" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Workshop/wiki/release info, local metadata, profile config, and release tree reviewed; two-player compatibility and any client extension remain unconfirmed.</x:v>
+      </x:c>
+      <x:c r="L197" s="28" t="str">
+        <x:v>RR-MP;RR-ECO;RR-COMPAT</x:v>
+      </x:c>
+      <x:c r="M197" s="28" t="str">
+        <x:v>docs/research/reviews/mods/3005289691-nova.rimworldtogether.md</x:v>
+      </x:c>
+      <x:c r="N197" s="28" t="str">
+        <x:v>Reviewed—source facts recorded</x:v>
+      </x:c>
+      <x:c r="O197" s="28" t="str">
+        <x:v>Provisional: async co-op layer for separate facilities; use offline visits/supply exchange only after pinned-build checks. No live shared-map or shared research.</x:v>
+      </x:c>
+      <x:c r="P197" s="28" t="str">
+        <x:v>RimWorld 1.6.4871 rev590; local RWT server archive matches release 26.8.31.1 asset; local client DLL hash in feasibility audit</x:v>
+      </x:c>
+      <x:c r="Q197" s="28" t="str">
+        <x:v>Not runtime tested; separate starts, offline visit, supply/aid exchange, reconnect, and custom dossier transfer pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="45" customHeight="1">
@@ -16643,7 +16646,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab2820c6ecdd448f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb24c9fb31d4110"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R74a09034959942c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R11cfac814cf7453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rdf4c9c1e666d4718"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R5ff16a5122bc4a69"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -476,12 +476,12 @@
         <x:v>Chapter 2 requires Odyssey, Vanilla Expanded Framework, and Chapter 1.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="24" hidden="0" customHeight="1">
       <x:c r="A14" s="14" t="str">
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Thirteen profile rows now have source/metadata notes and provisional use boundaries; 281 remain pending. No combined-profile runtime compatibility is established.</x:v>
+        <x:v>Seventeen profile rows have source/metadata notes; 277 remain pending. Four reviewed power/storage pages currently report Steam Community removal; no combined-profile runtime compatibility is established.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2015,7 +2015,7 @@
         <x:v>Not runtime tested; new-map and existing-save behavior pending.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="45" customHeight="1">
+    <x:row r="20" ht="66" hidden="0" customHeight="1">
       <x:c r="A20" s="26" t="str">
         <x:v>19</x:v>
       </x:c>
@@ -2035,37 +2035,37 @@
         <x:v>Power and industrial infrastructure</x:v>
       </x:c>
       <x:c r="G20" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Selected profile utility; optional to Rimrooms Core. Local metadata lists RimWorld 1.6 support.</x:v>
       </x:c>
       <x:c r="H20" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Potential control-room model for switching facility power zones; keep the gate usable without it.</x:v>
       </x:c>
       <x:c r="I20" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>Preserve the mod's own remote toggle, if verified. Do not replace vanilla switches or assume automatic control.</x:v>
       </x:c>
       <x:c r="J20" s="24" t="str">
-        <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
+        <x:v>Workshop page currently reports removal; local copy is installed. Publisher notes a soft conflict with Auto Flicker, absent from this profile.</x:v>
       </x:c>
       <x:c r="K20" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
-      </x:c>
-      <x:c r="L20" s="27" t="str">
-        <x:v>Pending mapping</x:v>
-      </x:c>
-      <x:c r="M20" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="N20" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="O20" s="27" t="str">
-        <x:v>Pending review</x:v>
-      </x:c>
-      <x:c r="P20" s="27" t="str">
-        <x:v>Not pinned</x:v>
-      </x:c>
-      <x:c r="Q20" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Workshop page and local About.xml reviewed; both list RimWorld 1.4–1.6 support; no runtime test.</x:v>
+      </x:c>
+      <x:c r="L20" s="28" t="str">
+        <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
+      </x:c>
+      <x:c r="M20" s="28" t="str">
+        <x:v>docs/research/reviews/mods/3031634496-Og.AutomaticPowerSwitch.md</x:v>
+      </x:c>
+      <x:c r="N20" s="28" t="str">
+        <x:v>Reviewed—source facts recorded</x:v>
+      </x:c>
+      <x:c r="O20" s="28" t="str">
+        <x:v>Provisional: optional facility power-control convenience; do not require or repackage it. Steam page currently reports removal; local profile copy is installed.</x:v>
+      </x:c>
+      <x:c r="P20" s="28" t="str">
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4, 1.5, and 1.6; Workshop page advertises same</x:v>
+      </x:c>
+      <x:c r="Q20" s="28" t="str">
+        <x:v>Not runtime tested; remote switch, Microelectronics unlock, save/reload, and named Auto Flicker conflict checks pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="45" customHeight="1">
@@ -2280,7 +2280,7 @@
         <x:v>Not runtime tested</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="45" customHeight="1">
+    <x:row r="25" ht="66" hidden="0" customHeight="1">
       <x:c r="A25" s="26" t="str">
         <x:v>24</x:v>
       </x:c>
@@ -2300,40 +2300,40 @@
         <x:v>Storage and recovered-material logistics</x:v>
       </x:c>
       <x:c r="G25" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Selected profile entry; optional to Core. Requires Ideology DLC and Adaptive Storage Framework.</x:v>
       </x:c>
       <x:c r="H25" s="24" t="str">
-        <x:v>Use existing storage, hauling, and refrigeration for expedition kits, sample quarantine, evidence archives, food, and sale stock. Add Backrooms labels and custody rules through separate definitions rather than global storage rewrites.</x:v>
+        <x:v>Optional ideology-themed storage furniture for archive, relic, or ceremonial rooms.</x:v>
       </x:c>
       <x:c r="I25" s="24" t="str">
-        <x:v>Medium: confirm filters and stack rules can distinguish quarantined samples, ordinary stock, and mission cargo. Avoid patches that overwrite other storage mods' categories.</x:v>
+        <x:v>Use only when both Ideology and Adaptive Storage Framework are present; keep ordinary Core storage available.</x:v>
       </x:c>
       <x:c r="J25" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Workshop page currently reports removal. Publisher names third-party art/content; do not copy the module's files.</x:v>
       </x:c>
       <x:c r="K25" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
-      </x:c>
-      <x:c r="L25" s="27" t="str">
-        <x:v>Pending mapping</x:v>
-      </x:c>
-      <x:c r="M25" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="N25" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="O25" s="27" t="str">
-        <x:v>Pending review</x:v>
-      </x:c>
-      <x:c r="P25" s="27" t="str">
-        <x:v>Not pinned</x:v>
-      </x:c>
-      <x:c r="Q25" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="45" customHeight="1">
+        <x:v>Workshop page and local About.xml reviewed; supports RimWorld 1.4–1.6; requires Ideology and Adaptive Storage Framework.</x:v>
+      </x:c>
+      <x:c r="L25" s="28" t="str">
+        <x:v>RR-FAC;RR-EVD;RR-DLC;RR-COMPAT</x:v>
+      </x:c>
+      <x:c r="M25" s="28" t="str">
+        <x:v>docs/research/reviews/mods/3301337278-Adaptive.Ideology.Storage.md</x:v>
+      </x:c>
+      <x:c r="N25" s="28" t="str">
+        <x:v>Reviewed—source facts recorded</x:v>
+      </x:c>
+      <x:c r="O25" s="28" t="str">
+        <x:v>Provisional: optional Ideology and Adaptive Storage Framework furniture storage; keep archive/evidence storage available on Core. Steam page currently reports removal.</x:v>
+      </x:c>
+      <x:c r="P25" s="28" t="str">
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4, 1.5, and 1.6; requires Ideology and Adaptive Storage Framework</x:v>
+      </x:c>
+      <x:c r="Q25" s="28" t="str">
+        <x:v>Not runtime tested; DLC-absent safety, storage filters, trade visibility, and selected-profile behavior pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A26" s="26" t="str">
         <x:v>25</x:v>
       </x:c>
@@ -2353,40 +2353,40 @@
         <x:v>Storage and recovered-material logistics</x:v>
       </x:c>
       <x:c r="G26" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Selected profile entry; optional to Core. Requires Adaptive Storage Framework; local metadata also lists Harmony.</x:v>
       </x:c>
       <x:c r="H26" s="24" t="str">
-        <x:v>Use existing storage, hauling, and refrigeration for expedition kits, sample quarantine, evidence archives, food, and sale stock. Add Backrooms labels and custody rules through separate definitions rather than global storage rewrites.</x:v>
+        <x:v>Optional rough racks, piles, and cellars for stores, kitchens, field kits, and outposts.</x:v>
       </x:c>
       <x:c r="I26" s="24" t="str">
-        <x:v>Medium: confirm filters and stack rules can distinguish quarantined samples, ordinary stock, and mission cargo. Avoid patches that overwrite other storage mods' categories.</x:v>
+        <x:v>Keep sample and food records separate from furniture. Test cellar food-preservation claims before relying on them.</x:v>
       </x:c>
       <x:c r="J26" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Workshop page currently reports removal. Publisher notes cellar temperature limits; do not copy the module's art or code.</x:v>
       </x:c>
       <x:c r="K26" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
-      </x:c>
-      <x:c r="L26" s="27" t="str">
-        <x:v>Pending mapping</x:v>
-      </x:c>
-      <x:c r="M26" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="N26" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="O26" s="27" t="str">
-        <x:v>Pending review</x:v>
-      </x:c>
-      <x:c r="P26" s="27" t="str">
-        <x:v>Not pinned</x:v>
-      </x:c>
-      <x:c r="Q26" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="45" customHeight="1">
+        <x:v>Workshop page and local About.xml reviewed; page supports RimWorld 1.5/1.6; local metadata lists Harmony and Adaptive Storage Framework.</x:v>
+      </x:c>
+      <x:c r="L26" s="28" t="str">
+        <x:v>RR-FAC;RR-EVD;RR-OUT;RR-COMPAT</x:v>
+      </x:c>
+      <x:c r="M26" s="28" t="str">
+        <x:v>docs/research/reviews/mods/3400037215-Adaptive.PrimitiveStorage.md</x:v>
+      </x:c>
+      <x:c r="N26" s="28" t="str">
+        <x:v>Reviewed—source facts recorded</x:v>
+      </x:c>
+      <x:c r="O26" s="28" t="str">
+        <x:v>Provisional: optional field, food, and rough-outpost storage; treat cellar preservation as unverified. Steam page currently reports removal.</x:v>
+      </x:c>
+      <x:c r="P26" s="28" t="str">
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.5/1.6 and lists Harmony plus Adaptive Storage Framework</x:v>
+      </x:c>
+      <x:c r="Q26" s="28" t="str">
+        <x:v>Not runtime tested; cellar temperatures/food decay, storage filters, trade visibility, and save/reload pending.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A27" s="26" t="str">
         <x:v>26</x:v>
       </x:c>
@@ -2406,37 +2406,37 @@
         <x:v>Storage and recovered-material logistics</x:v>
       </x:c>
       <x:c r="G27" s="24" t="str">
-        <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
+        <x:v>Selected profile entry; optional to Core. Requires Adaptive Storage Framework.</x:v>
       </x:c>
       <x:c r="H27" s="24" t="str">
-        <x:v>Use existing storage, hauling, and refrigeration for expedition kits, sample quarantine, evidence archives, food, and sale stock. Add Backrooms labels and custody rules through separate definitions rather than global storage rewrites.</x:v>
+        <x:v>Optional crates, racks, and cabinets for equipment stores, evidence archives, and shipping rooms.</x:v>
       </x:c>
       <x:c r="I27" s="24" t="str">
-        <x:v>Medium: confirm filters and stack rules can distinguish quarantined samples, ordinary stock, and mission cargo. Avoid patches that overwrite other storage mods' categories.</x:v>
+        <x:v>Keep custody and evidence records separate from the containers; preserve ordinary storage if the module is absent.</x:v>
       </x:c>
       <x:c r="J27" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Workshop page currently reports removal. Publisher documents an older update that could hide containers; stored items were reported safe.</x:v>
       </x:c>
       <x:c r="K27" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
-      </x:c>
-      <x:c r="L27" s="27" t="str">
-        <x:v>Pending mapping</x:v>
-      </x:c>
-      <x:c r="M27" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="N27" s="27" t="str">
-        <x:v>Pending</x:v>
-      </x:c>
-      <x:c r="O27" s="27" t="str">
-        <x:v>Pending review</x:v>
-      </x:c>
-      <x:c r="P27" s="27" t="str">
-        <x:v>Not pinned</x:v>
-      </x:c>
-      <x:c r="Q27" s="27" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Workshop page and local About.xml reviewed; supports RimWorld 1.4–1.6; requires Adaptive Storage Framework.</x:v>
+      </x:c>
+      <x:c r="L27" s="28" t="str">
+        <x:v>RR-FAC;RR-EVD;RR-COMPAT</x:v>
+      </x:c>
+      <x:c r="M27" s="28" t="str">
+        <x:v>docs/research/reviews/mods/3297307747-Adaptive.SimpleStorage.md</x:v>
+      </x:c>
+      <x:c r="N27" s="28" t="str">
+        <x:v>Reviewed—source facts recorded</x:v>
+      </x:c>
+      <x:c r="O27" s="28" t="str">
+        <x:v>Provisional: optional crate, rack, and cabinet storage for facility rooms; preserve ordinary storage if absent. Steam page currently reports removal.</x:v>
+      </x:c>
+      <x:c r="P27" s="28" t="str">
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4, 1.5, and 1.6; requires Adaptive Storage Framework</x:v>
+      </x:c>
+      <x:c r="Q27" s="28" t="str">
+        <x:v>Not runtime tested; construction, hauling/bills, trade visibility, and save/reload with the installed module remain pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="45" customHeight="1">
@@ -16646,7 +16646,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb24c9fb31d4110"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R010e5cc9450e4595"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R7fc34841be834307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R88ea647bf5eb4603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R4d15b45f42b84f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="Rc4587ff3a2054ef9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -481,7 +481,7 @@
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Twenty-one profile rows have source/metadata notes; 273 remain pending. Four reviewed power/storage pages currently report Steam Community removal; no combined-profile runtime compatibility is established.</x:v>
+        <x:v>291 of 294 rows have accepted source-fact records; 3 remain pending. Partial source notes: rows 96, 237, and 278. No combined-profile compatibility is established by source review.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -933,7 +933,7 @@
         <x:v>Evidence/review folder and templates</x:v>
       </x:c>
       <x:c r="B72" s="15" t="str">
-        <x:v>docs/research/reviews/README.md</x:v>
+        <x:v>docs/research/reviews/README.md; docs/research/reviews/templates/; docs/research/MOD_REVIEW_AGENT_ROADMAP.md</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -1105,7 +1105,7 @@
         <x:v>Retest the dependency order if Harmony or a dependent RWT build changes.</x:v>
       </x:c>
       <x:c r="K2" s="24" t="str">
-        <x:v>Workshop description and installed metadata reviewed; source/API and runtime checks pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L2" s="28" t="str">
         <x:v>RR-MP;RR-COMPAT</x:v>
@@ -1158,7 +1158,7 @@
         <x:v>Local and Workshop metadata stop at RimWorld 1.4; its page warns about ThoughtDef overrides and load order.</x:v>
       </x:c>
       <x:c r="K3" s="24" t="str">
-        <x:v>Workshop page and installed metadata reviewed; declared support stops at 1.4; 1.6 compatibility pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L3" s="28" t="str">
         <x:v>RR-STA;RR-COMPAT</x:v>
@@ -1211,7 +1211,7 @@
         <x:v>Harmony/load order; page lists conflicts with RimThemes and Startup Impact Continued. Neither appears in current inventory names/IDs.</x:v>
       </x:c>
       <x:c r="K4" s="24" t="str">
-        <x:v>Official Workshop page and installed metadata reviewed; startup compatibility pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L4" s="28" t="str">
         <x:v>RR-COMPAT</x:v>
@@ -1262,25 +1262,25 @@
         <x:v>Medium: verify definitions with this DLC present and absent; base progression must keep a safe fallback.</x:v>
       </x:c>
       <x:c r="K5" s="24" t="str">
-        <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L5" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-SCEN;RR-FAC;RR-STA;RR-GATE;RR-EXP;RR-SPACE;RR-EVD;RR-THREAT;RR-MSN;RR-ECO;RR-OUT;RR-DLC;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M5" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/official-4-Ludeon.RimWorld.md</x:v>
       </x:c>
       <x:c r="N5" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O5" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: required solo gameplay baseline; the full Core-only campaign is a design requirement.</x:v>
       </x:c>
       <x:c r="P5" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; official Ludeon sources and local package snapshot checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q5" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Official source note recorded. Core-only campaign implementation, DLC-absent behavior, and all multiplayer behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="45" customHeight="1">
@@ -1313,25 +1313,25 @@
         <x:v>Medium: verify definitions with this DLC present and absent; base progression must keep a safe fallback.</x:v>
       </x:c>
       <x:c r="K6" s="24" t="str">
-        <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L6" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-MSN;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M6" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/official-5-Ludeon.RimWorld.Royalty.md</x:v>
       </x:c>
       <x:c r="N6" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O6" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Royalty advancement/quest hooks; preserve a complete Core fallback.</x:v>
       </x:c>
       <x:c r="P6" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; official Ludeon source and local package snapshot checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q6" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Official source note recorded. Optional-only gating, absent-DLC load, and paired-DLC behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="45" customHeight="1">
@@ -1364,25 +1364,25 @@
         <x:v>Medium: verify definitions with this DLC present and absent; base progression must keep a safe fallback.</x:v>
       </x:c>
       <x:c r="K7" s="24" t="str">
-        <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L7" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M7" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/official-6-Ludeon.RimWorld.Ideology.md</x:v>
       </x:c>
       <x:c r="N7" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O7" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional company culture and role flavor; do not require Ideology systems.</x:v>
       </x:c>
       <x:c r="P7" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; official Ludeon source and local package snapshot checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q7" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Official source note recorded. Optional-only gating, absent-DLC load, and profile interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
@@ -1415,25 +1415,25 @@
         <x:v>Medium: verify definitions with this DLC present and absent; base progression must keep a safe fallback.</x:v>
       </x:c>
       <x:c r="K8" s="24" t="str">
-        <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L8" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M8" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/official-7-Ludeon.RimWorld.Biotech.md</x:v>
       </x:c>
       <x:c r="N8" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O8" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional biology, mech labor, and staff hooks; Core pawn labor remains sufficient.</x:v>
       </x:c>
       <x:c r="P8" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; official Ludeon source and local package snapshot checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q8" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Official source note recorded. Optional-only gating, absent-DLC load, and profile interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="45" customHeight="1">
@@ -1466,25 +1466,25 @@
         <x:v>Medium: verify definitions with this DLC present and absent; base progression must keep a safe fallback.</x:v>
       </x:c>
       <x:c r="K9" s="24" t="str">
-        <x:v>Local profile entry; exact game/DLC build still needs recording.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L9" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-EVD;RR-EXP;RR-MSN;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M9" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/official-8-Ludeon.RimWorld.Anomaly.md</x:v>
       </x:c>
       <x:c r="N9" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O9" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native anomaly touchpoints; Rimrooms supplies its own Core threat, evidence, and containment loops.</x:v>
       </x:c>
       <x:c r="P9" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; official Ludeon source and local package snapshot checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q9" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Official source note recorded. Optional-only gating, absent-DLC load, and profile interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="45" customHeight="1">
@@ -1517,25 +1517,25 @@
         <x:v>Medium: verify definitions with this DLC present and absent; base progression must keep a safe fallback.</x:v>
       </x:c>
       <x:c r="K10" s="24" t="str">
-        <x:v>Local profile entry; required by both gravship chapter listings.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L10" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-SPACEFLIGHT;RR-OUT;RR-EXP;RR-MSN;RR-ECO;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M10" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/official-9-Ludeon.RimWorld.Odyssey.md</x:v>
       </x:c>
       <x:c r="N10" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O10" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional gravship/space logistics; the Rimrooms gate and Core coordinate route remain primary.</x:v>
       </x:c>
       <x:c r="P10" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; official Ludeon source and local package snapshot checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q10" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Official source note recorded. Optional-only gating, absent-DLC load, and gravship integration remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="78" customHeight="1">
@@ -1570,7 +1570,7 @@
         <x:v>Test item filters, display, and temperature only if an integration is selected.</x:v>
       </x:c>
       <x:c r="K11" s="24" t="str">
-        <x:v>Workshop description/change notes and local About.xml reviewed; exact API and runtime interactions pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L11" s="28" t="str">
         <x:v>RR-FAC;RR-EVD;RR-COMPAT</x:v>
@@ -1623,7 +1623,7 @@
         <x:v>Local metadata lists RimThreaded as incompatible; vehicle, save, and multiplayer interactions are untested.</x:v>
       </x:c>
       <x:c r="K12" s="24" t="str">
-        <x:v>Workshop description and local About.xml reviewed; vehicle, save, and multiplayer interactions pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L12" s="28" t="str">
         <x:v>RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
@@ -1676,7 +1676,7 @@
         <x:v>Check load order and patches only if Rimrooms adopts a documented operation.</x:v>
       </x:c>
       <x:c r="K13" s="24" t="str">
-        <x:v>Workshop description and local About.xml reviewed; operation/API and runtime checks pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L13" s="28" t="str">
         <x:v>RR-COMPAT</x:v>
@@ -1729,7 +1729,7 @@
         <x:v>Confirm startup and support-log flow on the eventual clean and selected mod profiles.</x:v>
       </x:c>
       <x:c r="K14" s="24" t="str">
-        <x:v>Workshop description and local About.xml reviewed; Rimrooms service and runtime interactions pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L14" s="28" t="str">
         <x:v>RR-COMPAT</x:v>
@@ -1782,7 +1782,7 @@
         <x:v>Local metadata lists RangeAnimalFramework as incompatible; check it against the final 294 profile and VGE warnings.</x:v>
       </x:c>
       <x:c r="K15" s="24" t="str">
-        <x:v>Workshop description and local About.xml reviewed; specific API, gravship conflicts, and combined-profile behavior pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L15" s="28" t="str">
         <x:v>RR-SPACEFLIGHT;RR-COMPAT</x:v>
@@ -1835,7 +1835,7 @@
         <x:v>Verify queued cutting/harvest jobs and overlapping plant-management mods on the selected DLC/profile.</x:v>
       </x:c>
       <x:c r="K16" s="24" t="str">
-        <x:v>Workshop description/change notes and installed metadata reviewed; work-queue interaction pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L16" s="28" t="str">
         <x:v>RR-FAC;RR-OUT;RR-COMPAT</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>The page warns that other plant-ingestion changes may conflict; exact animal/plant rows still need review.</x:v>
       </x:c>
       <x:c r="K17" s="24" t="str">
-        <x:v>Official Workshop page and installed metadata reviewed; plant/animal overlap pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L17" s="28" t="str">
         <x:v>RR-OUT;RR-FAC;RR-COMPAT</x:v>
@@ -1941,7 +1941,7 @@
         <x:v>Direct Steam page fetch was rate-limited. Combined trader type, landing spot, goods, price, cooldown, and modded-item behavior are unknown.</x:v>
       </x:c>
       <x:c r="K18" s="24" t="str">
-        <x:v>Installed metadata and indexed official listing reviewed; full page/API/runtime evidence pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L18" s="28" t="str">
         <x:v>RR-ECO;RR-COMPAT</x:v>
@@ -1994,7 +1994,7 @@
         <x:v>Publisher says it is intended for a new map; existing-map use needs God Mode.</x:v>
       </x:c>
       <x:c r="K19" s="24" t="str">
-        <x:v>Official Workshop page and installed metadata reviewed; map behavior pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L19" s="28" t="str">
         <x:v>RR-FAC;RR-OUT;RR-COMPAT</x:v>
@@ -2047,7 +2047,7 @@
         <x:v>Workshop page currently reports removal; local copy is installed. Publisher notes a soft conflict with Auto Flicker, absent from this profile.</x:v>
       </x:c>
       <x:c r="K20" s="24" t="str">
-        <x:v>Workshop page and local About.xml reviewed; both list RimWorld 1.4–1.6 support; no runtime test.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L20" s="28" t="str">
         <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
@@ -2100,25 +2100,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K21" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L21" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-MSN;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M21" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3423264477-SR.ModRimworld.FactionalWarContinued.md</x:v>
       </x:c>
       <x:c r="N21" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O21" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional native faction incidents; use only as an example of optional world activity.</x:v>
       </x:c>
       <x:c r="P21" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 813B576389A3182BE8680F43F100C98FF8280DF43B345FD4399E68D99EA513D0</x:v>
       </x:c>
       <x:c r="Q21" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify each incident, faction consequences, cleanup, mod-absent path, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="45" customHeight="1">
@@ -2153,25 +2153,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K22" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L22" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M22" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2269697598-Mlie.XNDProfitableWeapons.md</x:v>
       </x:c>
       <x:c r="N22" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O22" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional economy configuration; do not double-credit vanilla sales in the company ledger.</x:v>
       </x:c>
       <x:c r="P22" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.0'; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 016426080BE1FEDF25DD3F4E08BC1F7280D61DC2611AC65956D9CCB43E35FC28</x:v>
       </x:c>
       <x:c r="Q22" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare produced/looted pricing, tags, filters, smelting, save/load, and any future ledger bridge.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="45" customHeight="1">
@@ -2206,25 +2206,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K23" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L23" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STYLE;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M23" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2264108215-XeoNovaDan.VisiblePants.md</x:v>
       </x:c>
       <x:c r="N23" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O23" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional appearance companion; no adapter and no art bundled.</x:v>
       </x:c>
       <x:c r="P23" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop/linked-source pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q23" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT linked repository is not tied to exact installed fork/assets. Rendering and selected apparel interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="45" customHeight="1">
@@ -2259,25 +2259,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K24" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L24" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M24" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3238353862-SamBucher.ADogSaidAnimalProsthetics2.md</x:v>
       </x:c>
       <x:c r="N24" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O24" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional animal medical/technology content; no Rimrooms dependency; keep animal care and case records functional without it.</x:v>
       </x:c>
       <x:c r="P24" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package SamBucher.ADogSaidAnimalProsthetics2; version 1.3.7; support 1.4-1.6; About.xml SHA-256 1961D14413EA36E86E6FF63147D995358F6B20607961BF13DF0B4CD5A2B7534E</x:v>
       </x:c>
       <x:c r="Q24" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check research/bills, selected animals, animal medical bed/IV interaction, Health-tab issue and safe removal.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="78" hidden="0" customHeight="1">
@@ -2312,7 +2312,7 @@
         <x:v>Workshop page currently reports removal. Publisher names third-party art/content; do not copy the module's files.</x:v>
       </x:c>
       <x:c r="K25" s="24" t="str">
-        <x:v>Workshop page and local About.xml reviewed; supports RimWorld 1.4–1.6; requires Ideology and Adaptive Storage Framework.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L25" s="28" t="str">
         <x:v>RR-FAC;RR-EVD;RR-DLC;RR-COMPAT</x:v>
@@ -2365,7 +2365,7 @@
         <x:v>Workshop page currently reports removal. Publisher notes cellar temperature limits; do not copy the module's art or code.</x:v>
       </x:c>
       <x:c r="K26" s="24" t="str">
-        <x:v>Workshop page and local About.xml reviewed; page supports RimWorld 1.5/1.6; local metadata lists Harmony and Adaptive Storage Framework.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L26" s="28" t="str">
         <x:v>RR-FAC;RR-EVD;RR-OUT;RR-COMPAT</x:v>
@@ -2418,7 +2418,7 @@
         <x:v>Workshop page currently reports removal. Publisher documents an older update that could hide containers; stored items were reported safe.</x:v>
       </x:c>
       <x:c r="K27" s="24" t="str">
-        <x:v>Workshop page and local About.xml reviewed; supports RimWorld 1.4–1.6; requires Adaptive Storage Framework.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L27" s="28" t="str">
         <x:v>RR-FAC;RR-EVD;RR-COMPAT</x:v>
@@ -2471,25 +2471,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K28" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L28" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M28" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1826684801-LegendaryMinuteman.AgeRMechSerum.md</x:v>
       </x:c>
       <x:c r="N28" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O28" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional rare life-extension reward; not required for staff retention or company currency.</x:v>
       </x:c>
       <x:c r="P28" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package LegendaryMinuteman.AgeRMechSerum; support tags 1.0-1.6; About.xml SHA-256 C402400C52AF46D264A89AD90B008229267DF74A74A34DFDC9EB34429A07AEDB</x:v>
       </x:c>
       <x:c r="Q28" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify age floor, chronic conditions and normal reward availability.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="45" customHeight="1">
@@ -2524,25 +2524,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K29" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L29" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M29" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2800155563-Mlie.AllMemoriesFade.md</x:v>
       </x:c>
       <x:c r="N29" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O29" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional mood-memory duration behavior; keep Rimrooms records in Rimrooms-owned saved data.</x:v>
       </x:c>
       <x:c r="P29" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Mlie.AllMemoriesFade; version 1.6.0; support 1.3-1.6; About.xml SHA-256 BDA65E7663A180995C84A6B5EB4989352FDC138024B9267E355FAFB27E5FB868</x:v>
       </x:c>
       <x:c r="Q29" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check modded/Ideology memories, exclusions, save/load and performance.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="45" customHeight="1">
@@ -2577,25 +2577,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K30" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L30" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-GATE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M30" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3256513109-Mlie.AllTurretsCanSetForcedTarget.md</x:v>
       </x:c>
       <x:c r="N30" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O30" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration-only; no Rimrooms turret patch or dependency planned.</x:v>
       </x:c>
       <x:c r="P30" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.0; About SHA-256 1C1D1C415C5409481ABDA3BFF5F10B6F9BC85F55A770F166F51E392B29FBB88B</x:v>
       </x:c>
       <x:c r="Q30" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify selected turret classes, forced targeting, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="45" customHeight="1">
@@ -2630,25 +2630,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K31" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L31" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EXP;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M31" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/761421485-UnlimitedHugs.AllowTool.md</x:v>
       </x:c>
       <x:c r="N31" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O31" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional command/haul QoL; keep Rimrooms work usable without its map-wide tools.</x:v>
       </x:c>
       <x:c r="P31" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package UnlimitedHugs.AllowTool; support 1.0-1.6; HugsLib required; About.xml SHA-256 0054DAF3B8466D87D2D6C3EE02F0345B240E92F2CC8656FC4DEB7665F984357B</x:v>
       </x:c>
       <x:c r="Q31" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check facility/expedition orders, selection, forbid and RWT command ownership.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="45" customHeight="1">
@@ -2683,25 +2683,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K32" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L32" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M32" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3513825850-Ingendum.AnimalApparelFramework.md</x:v>
       </x:c>
       <x:c r="N32" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O32" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional animal-equipment framework; check known overlap with row160 before any supported-profile claim.</x:v>
       </x:c>
       <x:c r="P32" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Ingendum.AnimalApparelFramework; support 1.6 only; Harmony; About.xml SHA-256 52C01BD5DDAB9710C95935373CABBAD20A6655635DF14F1C0B98DAF9718A36FD</x:v>
       </x:c>
       <x:c r="Q32" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; inspect animal equipment/rendering, row160 and row267 interactions, and saved gear.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="45" customHeight="1">
@@ -2736,25 +2736,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K33" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L33" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-DLC;RR-SPACEFLIGHT;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M33" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3525740284-Ingendum.AnimalArmorVacBelt.md</x:v>
       </x:c>
       <x:c r="N33" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O33" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional Odyssey-gated animal vacuum gear; never a Core-only or gate dependency.</x:v>
       </x:c>
       <x:c r="P33" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Ingendum.AnimalArmorVacBelt; support 1.6; requires Ingendum.AnimalApparelFramework; publisher requires Odyssey; About.xml SHA-256 A95F844E764D66085C4AE72E56C6CF14D9643CD7A66F7ECF7F8ED284A0AA3BCE</x:v>
       </x:c>
       <x:c r="Q33" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check DLC presence, research/crafting, vacuum, gear slots and RWT equipment state.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="45" customHeight="1">
@@ -2789,25 +2789,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K34" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L34" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-EXP;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M34" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2426119067-avilmask.AnimalControls.md</x:v>
       </x:c>
       <x:c r="N34" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O34" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional animal food/logistics settings; do not duplicate or require this policy for company logistics.</x:v>
       </x:c>
       <x:c r="P34" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package avilmask.AnimalControls; support 1.2-1.6; Harmony; About.xml SHA-256 3898DFF7CAE17FE2B2C652482F899587CA0E07293F7D1915BFA01DB03A8D78FF</x:v>
       </x:c>
       <x:c r="Q34" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check species/category food rules, handlers, row36 UI, save/remove, and absent Replimat/Meal Printer interaction.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="45" customHeight="1">
@@ -2842,25 +2842,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K35" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L35" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M35" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3221610549-GodlyAnnihilator.AnimalMedicalBed.md</x:v>
       </x:c>
       <x:c r="N35" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O35" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional native animal-care furnishing; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P35" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 41C392CEE3CDF07883A2DF9A4E36204D28656786EE03589979B2872967FE6434</x:v>
       </x:c>
       <x:c r="Q35" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify animal treatment, monitor link, IV/bed behavior, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="45" customHeight="1">
@@ -2895,25 +2895,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K36" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L36" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M36" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2876565401-overpl.AnimalSarcophagus.md</x:v>
       </x:c>
       <x:c r="N36" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O36" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional animal memorial furniture; not monster evidence storage.</x:v>
       </x:c>
       <x:c r="P36" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package overpl.AnimalSarcophagus; support 1.3-1.6; About.xml SHA-256 6FF214815FFF83575EA54014E59C68060A807340512D54AA5D77EE5FEA6E2CFA</x:v>
       </x:c>
       <x:c r="Q36" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; direct page fetch rate-limited; verify filters, hauling, Epitaph behavior and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="45" customHeight="1">
@@ -2948,25 +2948,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K37" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L37" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M37" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3575480305-Fluffy.AnimalTab.md</x:v>
       </x:c>
       <x:c r="N37" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O37" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional animal-management UI continuation; use standard animal controls when absent.</x:v>
       </x:c>
       <x:c r="P37" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Fluffy.AnimalTab; support 1.4-1.6; Harmony; About.xml SHA-256 3670C6AB3A7EF6046EC320F5B0464F02B530B1A71C66ACE7B3393805A6B15BF6</x:v>
       </x:c>
       <x:c r="Q37" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify tab, row33 and animal-gear interactions, duplicate package absence, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="45" customHeight="1">
@@ -3001,25 +3001,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K38" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L38" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M38" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3245454244-ColossalFossil.AnimalsAreFunContinued.md</x:v>
       </x:c>
       <x:c r="N38" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O38" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional pet/recreation feature; guests here are not asynchronous RWT facility visitors.</x:v>
       </x:c>
       <x:c r="P38" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package ColossalFossil.AnimalsAreFunContinued; version 1.6.5; support 1.1-1.6; About.xml SHA-256 933EBFC31972E6703985A21B284F0824AE66755692C7CC990E477257BBC064AF</x:v>
       </x:c>
       <x:c r="Q38" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; LGPL declared but exact version not verified; check recreation, guests, job cancellation, save/removal.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="45" customHeight="1">
@@ -3054,25 +3054,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K39" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L39" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M39" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1098354593-Oblitus.AnimalsLogic.md</x:v>
       </x:c>
       <x:c r="N39" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O39" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional animal behavior; if row 234 is retained, follow its documented setting path and test the pair.</x:v>
       </x:c>
       <x:c r="P39" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 0.19, 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 76874C400ABFC37E9CD68F68E27B830DB769956564EB705978AA1EE0A4B02C80</x:v>
       </x:c>
       <x:c r="Q39" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare predator hostility alone and with row 234 toggle on/off.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="45" customHeight="1">
@@ -3098,34 +3098,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H40" s="24" t="str">
-        <x:v>Use available vehicles, animals, wrecks, and transport items to stage teams, move supplies, evacuate casualties, and establish remote company posts. Keep the machine gate as the primary Backrooms route.</x:v>
+        <x:v>Treat the asteroid as an optional off-site anomaly research opportunity discovered through an orbital scanner or ancient uplink. Keep the Core gate campaign playable without it.</x:v>
       </x:c>
       <x:c r="I40" s="24" t="str">
-        <x:v>Medium: preserve each vehicle's travel and storage behavior. If a mod touches gravships or Odyssey world objects, validate it separately against both gravship chapters and RWT.</x:v>
+        <x:v>Leave the asteroid discovery, site exploration, and loot loop native. Keep Rimrooms coordinate generation and machine destinations separate.</x:v>
       </x:c>
       <x:c r="J40" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Anomaly and Odyssey are required by the mod. Test both discovery routes, site entry/return, item ownership, save/load, and the no-DLC campaign path.</x:v>
       </x:c>
       <x:c r="K40" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L40" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-SPACEFLIGHT;RR-THREAT;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M40" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3527726648-zoarak.anomalyplat.md</x:v>
       </x:c>
       <x:c r="N40" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O40" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native expedition content; no Rimrooms adapter planned.</x:v>
       </x:c>
       <x:c r="P40" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.6; no modVersion; About SHA-256 3B75B6CD10B178E2221842E8C98052AA0E2FB91C4C43CDD1AB61328A585A483E</x:v>
       </x:c>
       <x:c r="Q40" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify asteroid discovery routes, entry/exit, loot, save/load, and DLC-absent path.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="45" customHeight="1">
@@ -3160,25 +3160,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K41" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L41" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M41" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1195427067-com.bymarcin.ArchitectIcons.md</x:v>
       </x:c>
       <x:c r="N41" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O41" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional UI aid; use only separately created Rimrooms icons and preserve provenance.</x:v>
       </x:c>
       <x:c r="P41" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package com.bymarcin.ArchitectIcons; support 1.0-1.6; Harmony; About.xml SHA-256 D8C77467117FBECFCDE91CFF31780334BEA3A7A5B70A72907DD9E2D226B55E5A</x:v>
       </x:c>
       <x:c r="Q41" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check icon path/discovery, placeholders and intended UI scale.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="45" customHeight="1">
@@ -3213,25 +3213,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K42" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L42" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M42" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3550817577-Mlie.AreaUnlocker.md</x:v>
       </x:c>
       <x:c r="N42" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O42" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional zoning/UI extension; no Rimrooms dependency; do not reuse restricted third-party icons/assets.</x:v>
       </x:c>
       <x:c r="P42" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Mlie.AreaUnlocker; version 1.6.2; support 1.0-1.6; Harmony; About.xml SHA-256 B17A72CDC3037D2AA28F86D294594347F64C092640CDF5C67C08B1445FE4D7DF</x:v>
       </x:c>
       <x:c r="Q42" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify &gt;5 zones, Hospitality guest assignment, UI scale and map-local zones.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="45" customHeight="1">
@@ -3266,25 +3266,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K43" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L43" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-SPACEFLIGHT;RR-EXP;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M43" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3536585361-Broms.AsteroidMineralScanner.md</x:v>
       </x:c>
       <x:c r="N43" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O43" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional Odyssey orbital mining content; keep extraction available without it.</x:v>
       </x:c>
       <x:c r="P43" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.6; About.xml SHA-256 058B95A9EC69A06086B71E3CEE5705CA34103BF48A13271D05DC73F5AF352861</x:v>
       </x:c>
       <x:c r="Q43" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify resources, maps, yields, cost, roof setting, modded mineables, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="45" customHeight="1">
@@ -3319,25 +3319,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K44" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L44" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-FAC;RR-GATE;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M44" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2059389912-automatic.autolinks.md</x:v>
       </x:c>
       <x:c r="N44" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O44" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional generated navigation links; Rimrooms navigation works independently.</x:v>
       </x:c>
       <x:c r="P44" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package automatic.autolinks; support 1.1-1.6; no declared dependency; About.xml SHA-256 90CA2B65BE9F2560439E92E8A6064ADC60277BBF701B718905DC7FFAF6439CBA</x:v>
       </x:c>
       <x:c r="Q44" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check links for Rimrooms and optional definitions.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="45" customHeight="1">
@@ -3372,25 +3372,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K45" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L45" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M45" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3520167264-Defi.AutoCutBlight.md</x:v>
       </x:c>
       <x:c r="N45" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O45" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional agriculture QoL; food/outposts must not depend on it.</x:v>
       </x:c>
       <x:c r="P45" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 0DC74FABB0292047D30EF1D60590087A29D81B1B1D9DE5A70FEB24C107376632</x:v>
       </x:c>
       <x:c r="Q45" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify blight designation, allowed areas, worker assignment, save/load, and safe add/remove.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="45" customHeight="1">
@@ -3425,25 +3425,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K46" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L46" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M46" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2889440091-Mlie.BadCanBeGood.md</x:v>
       </x:c>
       <x:c r="N46" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O46" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional pawn-balance changes; keep recruitment, staff value, and work roles independent.</x:v>
       </x:c>
       <x:c r="P46" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.0 and publisher/repository sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q46" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT source noted. Trait, pawn value, recruitment, and RWT branch-local behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="45" customHeight="1">
@@ -3478,25 +3478,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K47" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L47" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M47" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1497792975-BinarySpark.CaravanDogs.md</x:v>
       </x:c>
       <x:c r="N47" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O47" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional caravan behavior; no Rimrooms patch.</x:v>
       </x:c>
       <x:c r="P47" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 BCE464D19B864D55C4090EB5D3B35E08A42DA277F04E42D15A0061604F157EE9</x:v>
       </x:c>
       <x:c r="Q47" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify pack cargo, embark/return, and safe add/remove on disposable save.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="45" customHeight="1">
@@ -3531,25 +3531,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K48" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L48" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACE;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M48" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2011794898-Meltup.BeautifulOutdoors.md</x:v>
       </x:c>
       <x:c r="N48" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O48" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional landscaping/beauty changes; keep Rimrooms mood rules independent.</x:v>
       </x:c>
       <x:c r="P48" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 8F9943B65C108CAB8B61DEBB01035EFEE39E2083125D47E46E91B1CCA947B6CC</x:v>
       </x:c>
       <x:c r="Q48" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check beauty/mood overlays across selected terrain/flora and RWT if included.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="45" customHeight="1">
@@ -3584,25 +3584,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K49" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L49" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M49" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2567901366-bedrestforfoodpoisoning.1trickPonyta.md</x:v>
       </x:c>
       <x:c r="N49" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O49" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional food-poisoning bed-rest behavior; keep vanilla medical recovery path available.</x:v>
       </x:c>
       <x:c r="P49" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package bedrestforfoodpoisoning.1trickPonyta; version 1.1.0; support 1.3-1.6; Harmony; About.xml SHA-256 BD8B7AD8B3A37A7C15257A975502197ECEDE51A0E99A651E69637EBEE391A45D</x:v>
       </x:c>
       <x:c r="Q49" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check thresholds, bed-rest priorities, expedition recovery, localization and RWT jobs.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="45" customHeight="1">
@@ -3628,34 +3628,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H50" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Use its incident-suppression settings as an optional way to tune ordinary base power reliability; keep Backrooms machine states and pressure events in Rimrooms-owned logic.</x:v>
       </x:c>
       <x:c r="I50" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>Do not patch its vanilla incident definitions. The machine and gate must have their own readable operating and failure states.</x:v>
       </x:c>
       <x:c r="J50" s="24" t="str">
-        <x:v>Medium: use as optional power/industry sources; price gate operating cost consistently and do not require one source for basic gate operation.</x:v>
+        <x:v>Test settings that suppress breakdowns, shorts, or solar flares; verify gate progression and recovery do not rely on incidents the player disabled.</x:v>
       </x:c>
       <x:c r="K50" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L50" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M50" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1555743957-AdamBucior.BetterElectronics.md</x:v>
       </x:c>
       <x:c r="N50" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O50" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration-only; electrical gate operation cannot require incidents this mod suppresses.</x:v>
       </x:c>
       <x:c r="P50" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 D7979912C1B03C667BA9D322E8C546441305AFC5419EFD0AD9F3DAD6C34D8ED5</x:v>
       </x:c>
       <x:c r="Q50" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify settings and gate power path with incidents enabled/disabled.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="45" customHeight="1">
@@ -3690,25 +3690,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K51" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L51" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M51" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2572683272-nephlite.advexplosions.md</x:v>
       </x:c>
       <x:c r="N51" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O51" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional visual-only explosion effects; keep damage and threat rules Rimrooms-owned.</x:v>
       </x:c>
       <x:c r="P51" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package nephlite.advexplosions; support 1.3-1.6; About.xml SHA-256 8FE537EA208A92B94A804B66436E9CFE63D5C5602DEB25FC4BCBCD1B73506D17</x:v>
       </x:c>
       <x:c r="Q51" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare damage separately from visuals and check Blood Animations/Muzzle Flash overlap.</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="45" customHeight="1">
@@ -3743,25 +3743,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K52" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L52" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M52" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3046776238-RedMattis.BetterGeneInheritance.md</x:v>
       </x:c>
       <x:c r="N52" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O52" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech offspring genetics; no staffing/recruitment dependency.</x:v>
       </x:c>
       <x:c r="P52" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop/source repo checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q52" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>No reuse license verified. Inheritance, pawn saves, gene-pack interactions, and RWT transfer remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="45" customHeight="1">
@@ -3796,25 +3796,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K53" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L53" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M53" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2221387317-ArchieV.BetterWeight.md</x:v>
       </x:c>
       <x:c r="N53" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O53" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional logistics/balance companion; no gate or expedition dependency.</x:v>
       </x:c>
       <x:c r="P53" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/repository sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q53" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>GPL-3.0 repository noted. Mass/minify/cargo/gravship behavior and DLC coverage remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="45" customHeight="1">
@@ -3834,40 +3834,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2710382569</x:v>
       </x:c>
       <x:c r="F54" s="24" t="str">
-        <x:v>Cross-mod fixes and balance patches</x:v>
+        <x:v>Furniture/workbench patch bundle</x:v>
       </x:c>
       <x:c r="G54" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H54" s="24" t="str">
-        <x:v>Retain as part of the chosen profile. Treat its patches as dependencies of the source mods it repairs; add Backrooms patches only for a confirmed conflict and only after identifying which Def or code path is already altered.</x:v>
+        <x:v>Let the selected patch handle only its documented supported linkables; avoid duplicate Rimrooms patches.</x:v>
       </x:c>
       <x:c r="I54" s="24" t="str">
-        <x:v>High: broad patches can overlap with Backrooms or other profile patches. Record exact covered mods and patch order before altering shared Defs.</x:v>
+        <x:v>No Rimrooms adapter; add a patch only after a reproduced conflict and exact shared-definition review.</x:v>
       </x:c>
       <x:c r="J54" s="24" t="str">
-        <x:v>High: verify patch order and source mods covered before adding any Backrooms patch.</x:v>
+        <x:v>Steam removal notice has no stated compatibility meaning; verify target packages, patch coverage and order.</x:v>
       </x:c>
       <x:c r="K54" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L54" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M54" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2710382569-Daria40K.BigLittleModPatch.md</x:v>
       </x:c>
       <x:c r="N54" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O54" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional cross-mod patch behavior; no Rimrooms dependency or duplicate adapter.</x:v>
       </x:c>
       <x:c r="P54" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q54" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; removal notice noted; no runtime test or profile compatibility claim. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="45" customHeight="1">
@@ -3902,25 +3902,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K55" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L55" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M55" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3228047321-Fuu.BloodAnimations.md</x:v>
       </x:c>
       <x:c r="N55" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O55" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional visual effects; publisher multiplayer statement is not RWT support clearance.</x:v>
       </x:c>
       <x:c r="P55" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Fuu.BloodAnimations; support 1.4-1.6; About.xml SHA-256 B8A995DB563778767D9ED3AB60136E648A58E14C3CE9199069CB6B7403122469</x:v>
       </x:c>
       <x:c r="Q55" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; inspect two-client RWT effects, wounds, casings, filth settings, and performance.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="45" customHeight="1">
@@ -3955,25 +3955,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K56" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L56" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-UI;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M56" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3525001145-Defi.Blueprints.fork.md</x:v>
       </x:c>
       <x:c r="N56" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O56" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional construction aid; current fork license and direct-page details remain unverified; do not copy code/assets.</x:v>
       </x:c>
       <x:c r="P56" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Defi.Blueprints.fork; support 1.4-1.6; Harmony; About.xml SHA-256 4F6520E72571CE2F87D7228B0B7B07A538907793479713EC9D818307593015B1; exact-ID Workshop index reviewed, direct fetch HTTP 429</x:v>
       </x:c>
       <x:c r="Q56" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; direct source page follow-up, blueprint import/export, Dubs Mint, and RWT placement checks pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="78" customHeight="1">
@@ -4008,7 +4008,7 @@
         <x:v>Local metadata omits 1.6; the publisher says it still works in 1.6, but runtime/full-profile evidence is missing. Page says patch-based and recommends low load order; test animal definitions and save/load.</x:v>
       </x:c>
       <x:c r="K57" s="24" t="str">
-        <x:v>Workshop page, publisher comment, and local About.xml reviewed; runtime pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L57" s="28" t="str">
         <x:v>RR-COMPAT</x:v>
@@ -4061,25 +4061,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K58" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L58" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EXP;RR-OUT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M58" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3534185281-Memegoddess.BuildFromInventory.md</x:v>
       </x:c>
       <x:c r="N58" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O58" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional construction aid; make material ownership and consumption explicit.</x:v>
       </x:c>
       <x:c r="P58" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Memegoddess.BuildFromInventory; support 1.1-1.6; Harmony; About.xml SHA-256 BAB42E55485ECFC3A9A665580201D9EFEE702A05864BF63AF77BACF41AF702AC</x:v>
       </x:c>
       <x:c r="Q58" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check inventory sources, partial builds, interruption, caravans, blueprints and RWT transfers.</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="45" customHeight="1">
@@ -4114,25 +4114,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K59" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L59" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACE;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M59" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1420979918-Buildable.Terrain.md</x:v>
       </x:c>
       <x:c r="N59" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O59" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional/configuration-only terrain tool; no Rimrooms adapter planned.</x:v>
       </x:c>
       <x:c r="P59" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion or dependency; About SHA-256 6A9063CAEDEECE9081A72FB55C9526497782EAC227B6B08D1D54AA0E7BCD295A</x:v>
       </x:c>
       <x:c r="Q59" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify generated terrain, wealth, route/room identity, terrain mods, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="45" customHeight="1">
@@ -4167,25 +4167,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K60" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L60" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M60" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2784149999-arakos.callatrader.acat.md</x:v>
       </x:c>
       <x:c r="N60" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O60" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: use as optional native trader-call feature; keep contracts/ledger independent.</x:v>
       </x:c>
       <x:c r="P60" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.1; About SHA-256 7292D7905D43B95A418AFDF01B88CFE215C895A949E393D5D143BF72555F940B</x:v>
       </x:c>
       <x:c r="Q60" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify trader calls, fees, cooldown, competing trade mods, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="45" customHeight="1">
@@ -4220,25 +4220,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K61" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L61" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M61" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3255137581-Mlie.CaptureThem.md</x:v>
       </x:c>
       <x:c r="N61" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O61" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native capture-work convenience; preserve vanilla custody paths.</x:v>
       </x:c>
       <x:c r="P61" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.0; About SHA-256 E7084CC1805CB3F0E31AE64F99B210A237B4C2FA4FD474C17AFB6D9B6EA6D076</x:v>
       </x:c>
       <x:c r="Q61" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify designated capture, prisoner bed, Prison Labor interaction, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="45" customHeight="1">
@@ -4273,25 +4273,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K62" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L62" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M62" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3642349335-Mlie.CarryallsIntercontinentalTransport.md</x:v>
       </x:c>
       <x:c r="N62" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O62" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional transport vehicle only; not the gate or Backrooms access route.</x:v>
       </x:c>
       <x:c r="P62" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.1'; local support 1.4, 1.5, 1.6; About.xml SHA-256 136DE75E56C7B8F5C54D01C762CE2F29746FC99ADF0374F827994E076DD6AF9B</x:v>
       </x:c>
       <x:c r="Q62" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify loading, capacity, landing, fuel reserve, round trip, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="45" customHeight="1">
@@ -4326,25 +4326,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K63" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L63" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M63" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3509487668-Orion.CashRegister.md</x:v>
       </x:c>
       <x:c r="N63" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O63" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: use native optional store/cafeteria features; do not merge its register into company ledger.</x:v>
       </x:c>
       <x:c r="P63" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.0.2; About SHA-256 0AC49AD6A323DEC98D430A62E5AB62618BAC79636144D56BED44D36754B3880A</x:v>
       </x:c>
       <x:c r="Q63" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Gastronomy and Hospitality: Storefront dependencies and intended Odyssey placement.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="45" customHeight="1">
@@ -4379,25 +4379,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K64" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L64" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M64" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1546494565-kapitanoczywisty.changemapedge.md</x:v>
       </x:c>
       <x:c r="N64" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O64" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional placement convenience; no Rimrooms adapter or perimeter-defense dependency.</x:v>
       </x:c>
       <x:c r="P64" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml 1.6; Harmony required; upstream v1.0.9; About SHA-256 8A7500D57E39F05A3F0832C4C8320E83A6AE9536054E5261560B46A782CE4DC2</x:v>
       </x:c>
       <x:c r="Q64" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify edge placement, visitors, raids, caravans, pods, save/load, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="45" customHeight="1">
@@ -4432,25 +4432,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K65" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L65" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-SCEN;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M65" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1874644848-void.charactereditor.md</x:v>
       </x:c>
       <x:c r="N65" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O65" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional admin/debug tool; do not incorporate pawn editing into normal hiring or missions.</x:v>
       </x:c>
       <x:c r="P65" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package void.charactereditor; installed 1.6.1; support tags 1.0-1.6; Harmony; About.xml SHA-256 24436D3DB24EF85CC7329430ACD5CB4389A735701E51E5002209DEFC77EC0D13; exact-ID page index reviewed, direct fetch HTTP 429</x:v>
       </x:c>
       <x:c r="Q65" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; resolve Workshop/local version mismatch; verify starts, DLC, branch-owned pawns and co-op mutation limits.</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="45" customHeight="1">
@@ -4485,25 +4485,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K66" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L66" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M66" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2006605356-CrashM.ColorCodedMoodBar.11.md</x:v>
       </x:c>
       <x:c r="N66" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O66" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional visual aid; color cannot be the only status signal; exact continuation license unresolved.</x:v>
       </x:c>
       <x:c r="P66" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package CrashM.ColorCodedMoodBar.11; support 1.1-1.6; Harmony; About.xml SHA-256 4332D2E11E6D1F7B17EA849541E346AF7CF8EA896C9F9E4E672F8705930F7AF4; exact-ID page index reviewed, direct fetch HTTP 429</x:v>
       </x:c>
       <x:c r="Q66" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check pawn states, scaling, bar layouts and each RWT client.</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="45" customHeight="1">
@@ -4538,25 +4538,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K67" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L67" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-EXP;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M67" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1561769193-avilmask.CommonSense.md</x:v>
       </x:c>
       <x:c r="N67" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O67" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional configurable behaviors; keep progression independent and test publisher-stated trade option overlap with row116.</x:v>
       </x:c>
       <x:c r="P67" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package avilmask.CommonSense; support 1.0-1.6; Harmony; About.xml SHA-256 7D88D50091E0EBE694EB1C2118CF9B7496942352B1A11D8856B8A080F1D3220C; exact-ID page index reviewed, direct fetch HTTP 429</x:v>
       </x:c>
       <x:c r="Q67" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check work/food/custody/trade jobs, row116 trade option, row75 recreation, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="45" customHeight="1">
@@ -4591,25 +4591,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K68" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L68" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M68" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3250322299-Mlie.CompactWorkTab.md</x:v>
       </x:c>
       <x:c r="N68" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O68" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional work-tab presentation only; no work logic integration.</x:v>
       </x:c>
       <x:c r="P68" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.0'; local support 1.4, 1.5, 1.6; About.xml SHA-256 F54DF1876CD8E6FA25030BC62491A45B0803FB12BA91631EA97D3179E21D01DA</x:v>
       </x:c>
       <x:c r="Q68" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Rimrooms job visibility, controls, Numbers interaction, and saved priorities.</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="45" customHeight="1">
@@ -4644,25 +4644,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K69" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L69" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M69" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2913588675-arl85.CorpseInfo.md</x:v>
       </x:c>
       <x:c r="N69" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O69" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional corpse-record UI; not Rimrooms forensics or evidence custody.</x:v>
       </x:c>
       <x:c r="P69" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID publisher/source pages checked 2026-09-27; direct page errored; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q69" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>License not found. Record/grave views and corpse-processing/dissection interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="45" customHeight="1">
@@ -4697,25 +4697,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K70" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L70" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M70" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2906276423-GwinnBleidd.CraftableMountains.md</x:v>
       </x:c>
       <x:c r="N70" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O70" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional construction content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P70" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q70" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher and existing source note reviewed; limited 1.6/Vacstone caveats recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="45" customHeight="1">
@@ -4750,25 +4750,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K71" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L71" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-EXP;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M71" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2016331497-CaesarV6.DamageIndicators.md</x:v>
       </x:c>
       <x:c r="N71" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O71" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional combat readability aid; no threat-state integration.</x:v>
       </x:c>
       <x:c r="P71" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID publisher/source pages checked 2026-09-27; direct page errored; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q71" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Linked source states MIT; complete asset provenance/performance and overlay interactions remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="45" customHeight="1">
@@ -4803,25 +4803,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K72" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L72" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M72" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2896207870-Troopersmith1.DeathRattle.md</x:v>
       </x:c>
       <x:c r="N72" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O72" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional injury-severity rule; no expedition survival dependency.</x:v>
       </x:c>
       <x:c r="P72" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/linked-fork source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q72" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Current page/local tags start at 1.3 despite title 1.2+; fork license unresolved. Life Support row272 pair and injury behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="45" customHeight="1">
@@ -4856,25 +4856,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K73" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L73" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M73" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3421951605-TheCafFiend.OverdoseDependencyFix.md</x:v>
       </x:c>
       <x:c r="N73" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O73" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech-only drug-balance feature; keep it outside Core-only play.</x:v>
       </x:c>
       <x:c r="P73" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID Workshop text checked 2026-09-27; direct page errored; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q73" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher says Biotech required DLC while local metadata lists Harmony only as hard dependency. Preserve mismatch; exact DLC and drug behavior untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="45" customHeight="1">
@@ -4894,40 +4894,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2423311270</x:v>
       </x:c>
       <x:c r="F74" s="24" t="str">
-        <x:v>Materials, cargo, and recovered resources</x:v>
+        <x:v>Item disposal and waste handling</x:v>
       </x:c>
       <x:c r="G74" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H74" s="24" t="str">
-        <x:v>Use carrying, item handling, harvest, and salvage rules to shape expedition kit limits and recovered-cargo value. Preserve each mod's normal material and weight behavior; add only a Backrooms cargo manifest and appraisal layer.</x:v>
+        <x:v>Keep disposal player-directed; require explicit evidence/sample custody before Rimrooms-owned items can be destroyed.</x:v>
       </x:c>
       <x:c r="I74" s="24" t="str">
-        <x:v>Medium: weight, stack, yield, and destruction rules affect mission capacity and valuation. Reconcile cargo accounting with item transfers and avoid duplicate salvage or recipe patches.</x:v>
+        <x:v>No adapter; track Rimrooms custody and audit outcomes separately from item destruction.</x:v>
       </x:c>
       <x:c r="J74" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Check irreversible loss, zero-HP items, wastepacks, jobs and RWT branch state.</x:v>
       </x:c>
       <x:c r="K74" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L74" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-EVD;RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M74" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2423311270-Garwel.DestroyItem.md</x:v>
       </x:c>
       <x:c r="N74" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O74" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional disposal behavior; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P74" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q74" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher repository/page and local metadata facts recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="45" customHeight="1">
@@ -4962,25 +4962,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K75" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L75" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>None—verified unrelated</x:v>
       </x:c>
       <x:c r="M75" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2425530959-Mlie.DingOnGameLoaded.md</x:v>
       </x:c>
       <x:c r="N75" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O75" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>None—verified unrelated to Rimrooms systems; optional client audio utility only.</x:v>
       </x:c>
       <x:c r="P75" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local Mlie.DingOnGameLoaded 1.6.1 / support 1.1–1.6; exact-ID indexed Workshop text checked 2026-09-27; direct Steam fetch rate-limited; no runtime test.</x:v>
       </x:c>
       <x:c r="Q75" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Linked note records the indexed publisher claims and local metadata. Direct page, client audio timing, and compatibility were not tested.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="45" customHeight="1">
@@ -5015,25 +5015,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K76" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L76" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M76" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3368214339-Xercaine.DoRecreationWhenIdle.md</x:v>
       </x:c>
       <x:c r="N76" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O76" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional recreation behavior; do not rely on it for staff needs or progression.</x:v>
       </x:c>
       <x:c r="P76" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Xercaine.DoRecreationWhenIdle; support 1.4-1.6; Harmony; About.xml SHA-256 A33EC2140DCAB9A5CF21BAF67D0C72E6D4A3779041ACFE572E4E0F5C39BFD2E8</x:v>
       </x:c>
       <x:c r="Q76" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check recreation loops with row142 and Common Sense settings.</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="45" customHeight="1">
@@ -5068,25 +5068,25 @@
         <x:v>Medium: the profile changes research presentation or flow. Keep company milestones on a stable separate research chain and avoid replacing the selected research interface blindly.</x:v>
       </x:c>
       <x:c r="K77" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L77" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M77" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3523205869-MD.PrioritizeResearch.md</x:v>
       </x:c>
       <x:c r="N77" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O77" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration-only; preserve its earlier-than-Rimatomics order and do not depend on its UI.</x:v>
       </x:c>
       <x:c r="P77" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml has no modVersion; About SHA-256 2FECF758A032661283E200387D5E08A560B185468942C67593FE43100A034DBB</x:v>
       </x:c>
       <x:c r="Q77" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify vanilla/DLC benches and Rimatomics research priority, completion, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="45" customHeight="1">
@@ -5121,25 +5121,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K78" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L78" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M78" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3532342422-jecrell.doorsexpanded.md</x:v>
       </x:c>
       <x:c r="N78" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O78" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional architecture/security-door reference; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P78" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 05A074F39F75C154E9DA609EDF84887EDCBD1D3E483E8392A6E8E111A5D67184</x:v>
       </x:c>
       <x:c r="Q78" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify door sizes, remote operation, power, pathing, containment, and rows 185/187.</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="45" customHeight="1">
@@ -5174,25 +5174,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K79" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L79" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M79" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3534629428-Wolfcub05.DraftableAnimals.md</x:v>
       </x:c>
       <x:c r="N79" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O79" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal expedition/combat control; no required staff or threat feature.</x:v>
       </x:c>
       <x:c r="P79" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID publisher text checked 2026-09-27; direct page errored; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q79" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Permission to update is not a license grant. Animal Weapon wording and full-profile command behavior remain uncertain.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="45" customHeight="1">
@@ -5227,25 +5227,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K80" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L80" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-ECO;RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M80" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2599942235-telardo.DragSelect.md</x:v>
       </x:c>
       <x:c r="N80" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O80" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional UI convenience; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P80" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q80" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; removal notice has no stated compatibility meaning; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="45" customHeight="1">
@@ -5280,25 +5280,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K81" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L81" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M81" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3630049419-MemeGoddess.DualWield.md</x:v>
       </x:c>
       <x:c r="N81" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O81" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional dual-wield behavior; keep CE and old RunAndGun packages outside any supported profile.</x:v>
       </x:c>
       <x:c r="P81" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package MemeGoddess.DualWield; metadata support 1.0-1.6 and load folders 1.1-1.6; About.xml SHA-256 B6D26EDF546218F9AC026BB8216BEC1E91E45BA94C48F632122C0ACDFB543AA2</x:v>
       </x:c>
       <x:c r="Q81" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify weapon pairings, command behavior, and selected RunAndGun continuation interaction.</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="45" customHeight="1">
@@ -5333,25 +5333,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K82" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L82" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-FAC;RR-GATE;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M82" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1446523594-Dubwise.DubsMintMenus.md</x:v>
       </x:c>
       <x:c r="N82" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O82" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional menu/UI layer; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P82" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q82" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; Harmony declaration mismatch and removal notice retained; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="45" customHeight="1">
@@ -5386,25 +5386,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K83" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L83" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-EXP;RR-OUT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M83" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1662119905-dubwise.dubsmintminimap.md</x:v>
       </x:c>
       <x:c r="N83" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O83" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional map UI; not authoritative for coordinates, discovery, or RWT pings.</x:v>
       </x:c>
       <x:c r="P83" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.3.800'; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 A96E6D9C659E89141074ED31C0FC02FA39E189095EF28CD701B33BEC0BE5A58A</x:v>
       </x:c>
       <x:c r="Q83" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify maps, markers, fog, comms gating, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="45" customHeight="1">
@@ -5430,34 +5430,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H84" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Use Rimatomics nuclear power, security, and safety systems as optional late facility infrastructure. The gate must also start through a Core-only power route.</x:v>
       </x:c>
       <x:c r="I84" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>Keep Rimatomics research and power native; do not require its weapons, reactor, or resources for the basic gate loop.</x:v>
       </x:c>
       <x:c r="J84" s="24" t="str">
-        <x:v>Medium: use as optional power/industry sources; price gate operating cost consistently and do not require one source for basic gate operation.</x:v>
+        <x:v>Test research priorities, reactor safety, defenses, material costs, and interaction with Rimefeller and the selected power mods.</x:v>
       </x:c>
       <x:c r="K84" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L84" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M84" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1127530465-Dubwise.Rimatomics.md</x:v>
       </x:c>
       <x:c r="N84" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O84" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native power/security features; do not require for the gate.</x:v>
       </x:c>
       <x:c r="P84" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.7.3551; About SHA-256 E5054EDE7290B443CA82427EEA94A0583519EBC9DE70CD940269A3428813ACB</x:v>
       </x:c>
       <x:c r="Q84" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify power, safety, research, defenses, and research-priority interaction.</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="45" customHeight="1">
@@ -5492,25 +5492,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K85" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L85" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M85" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/832333531-Dubwise.DubsRimkit.md</x:v>
       </x:c>
       <x:c r="N85" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O85" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native staff-care and repair tools; no adapter planned.</x:v>
       </x:c>
       <x:c r="P85" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.5.2023; About SHA-256 C073521ED5427D1C71E6EB1E8E77C085D675ABDA2DE06F9893D946FCFA072AF8</x:v>
       </x:c>
       <x:c r="Q85" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify kit use, repair, Common Sense, Smart Medicine, Prison Labor, and RWT interactions.</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="45" customHeight="1">
@@ -5545,25 +5545,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K86" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L86" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M86" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/735106432-EdB.PrepareCarefully.md</x:v>
       </x:c>
       <x:c r="N86" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O86" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional scenario setup utility; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P86" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q86" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page/repository and local metadata recorded; dependency ID mismatch noted; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="45" customHeight="1">
@@ -5589,34 +5589,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H87" s="24" t="str">
-        <x:v>Use battery efficiency and lightning protection as optional ways to keep the headquarters and gate reserve stable. Preserve the selected profile's own weather and power settings.</x:v>
+        <x:v>Use its advertised battery tiers and efficiency as optional storage choices for the facility and gate reserve; keep the Core power route viable without it.</x:v>
       </x:c>
       <x:c r="I87" s="24" t="str">
-        <x:v>Low to medium: balance gate reserve costs with battery changes. Lightning and power events must not be assumed when the profile suppresses related events.</x:v>
+        <x:v>Preserve the mod battery behavior and express gate costs in a way that does not assume these efficiencies or capacities.</x:v>
       </x:c>
       <x:c r="J87" s="24" t="str">
-        <x:v>Medium: use as optional power/industry sources; price gate operating cost consistently and do not require one source for basic gate operation.</x:v>
+        <x:v>Confirm installed recipes, research, capacity, and efficiency; test the reserve with Rimatomics, Rimefeller, and the Core-only fallback.</x:v>
       </x:c>
       <x:c r="K87" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L87" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M87" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/865497369-efficient.batteries.md</x:v>
       </x:c>
       <x:c r="N87" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O87" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native storage; gate must work with Core power alone.</x:v>
       </x:c>
       <x:c r="P87" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 3D803E91E0C22735EF979E9D1BA52CFC35546655394B55F2A3C6BE7574AB6A03</x:v>
       </x:c>
       <x:c r="Q87" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; review page details and test tiers, power network, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="45" customHeight="1">
@@ -5651,25 +5651,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K88" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L88" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M88" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2505566813-Mlie.EggIncubator.md</x:v>
       </x:c>
       <x:c r="N88" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O88" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal/facility furnishing; no required reproduction system.</x:v>
       </x:c>
       <x:c r="P88" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.0 and publisher/repository sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q88" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT repo and separate art credit noted. Temperature, powered incubation, modded eggs, and save behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="45" customHeight="1">
@@ -5704,25 +5704,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K89" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L89" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M89" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1649368867-Cocaine.ElectricStonecuttingTable.md</x:v>
       </x:c>
       <x:c r="N89" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O89" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional production furniture; not required for materials/progression.</x:v>
       </x:c>
       <x:c r="P89" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 65D19F1A518BDC6531C4F5311342E0B41B43EDED7F1AB4297EC6E4953AD40758</x:v>
       </x:c>
       <x:c r="Q89" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify power shortage, research settings, vanilla and Stonecutting Extended recipes, output, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="45" customHeight="1">
@@ -5757,25 +5757,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K90" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L90" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M90" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2162909284-Mlie.ExplosiveImplant.md</x:v>
       </x:c>
       <x:c r="N90" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O90" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional pawn-threat content; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P90" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q90" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher description and local metadata recorded; development/delist caveat and user report retained; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="45" customHeight="1">
@@ -5810,25 +5810,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K91" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L91" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M91" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2845980214-Aelanna.FistNerf.md</x:v>
       </x:c>
       <x:c r="N91" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O91" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional balance behavior; does not provide prisoner containment or escape prevention.</x:v>
       </x:c>
       <x:c r="P91" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Aelanna.FistNerf; support 1.3-1.6; About.xml SHA-256 41B9307991D4D51B666993A97DC50ECFEC65727D824932861E2419E2B32D5BB2</x:v>
       </x:c>
       <x:c r="Q91" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; distinguish unarmed building damage from mining, weapons, animals, and other escape routes.</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="45" customHeight="1">
@@ -5863,25 +5863,25 @@
         <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
       </x:c>
       <x:c r="K92" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L92" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M92" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2497907804-Mlie.FlickableStorage.md</x:v>
       </x:c>
       <x:c r="N92" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O92" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional storage configuration; never use for security or ownership enforcement.</x:v>
       </x:c>
       <x:c r="P92" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.2'; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 D8E29D09E7FA18945A604BC221DDC10B6739A6FCC77A1A3F0E08505823290A37</x:v>
       </x:c>
       <x:c r="Q92" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify four states, linked ASF storage, chunks, mental breaks, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="45" customHeight="1">
@@ -5916,25 +5916,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K93" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L93" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M93" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2960126462-Hawkwood.FloorsAreAlmostWorthless.md</x:v>
       </x:c>
       <x:c r="N93" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O93" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional floor-wealth balance patch; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P93" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q93" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Existing source note plus available publisher text reviewed; direct page limitation retained; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="45" customHeight="1">
@@ -5969,25 +5969,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K94" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L94" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M94" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2843483188-Mlie.FoodPoisoningStackFix.md</x:v>
       </x:c>
       <x:c r="N94" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O94" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional food-handling correction; maintain care without it.</x:v>
       </x:c>
       <x:c r="P94" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and publisher/repository sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q94" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT continued repo noted. Mixed-stack behavior, row48 care, cafeteria, guest/animal feeding, and RWT transfer remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="45" customHeight="1">
@@ -6022,25 +6022,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K95" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L95" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M95" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2958300354-zed.0xff.ForceXenogermImplantation.md</x:v>
       </x:c>
       <x:c r="N95" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O95" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional captive-genetics control; no Rimrooms custody or staffing dependency.</x:v>
       </x:c>
       <x:c r="P95" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local selected package metadata and exact Workshop/source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q95" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Selected package is Zed item 2958300354; separate continuation 3261498531 excluded from claims. Source license and surgery behavior remain unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="45" customHeight="1">
@@ -6075,25 +6075,25 @@
         <x:v>Low to medium: no hard dependency planned. Verify the selected 1.6 behavior before writing a direct compatibility patch.</x:v>
       </x:c>
       <x:c r="K96" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L96" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M96" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1591142767-notfood.FrameRateControl.md</x:v>
       </x:c>
       <x:c r="N96" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O96" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional client performance utility; no gameplay adapter.</x:v>
       </x:c>
       <x:c r="P96" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q96" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and existing repository note reviewed; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="45" customHeight="1">
@@ -6128,25 +6128,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K97" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source review incomplete; direct publisher-source check pending.</x:v>
       </x:c>
       <x:c r="L97" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M97" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3286907608-Xercaine.FueledCrematorium.md</x:v>
       </x:c>
       <x:c r="N97" s="28" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="O97" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Pending primary-source review; provisional optional disposal furniture, never an evidence workflow.</x:v>
       </x:c>
       <x:c r="P97" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.5, 1.6; About.xml SHA-256 3E2AF3B20B59F94757902F691179A88D94B23CC7961CA4EC62549D2CA010E87E</x:v>
       </x:c>
       <x:c r="Q97" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Wave 11 exact and English-page retries still rate-limited; no publisher-linked source/license verified. Existing indexed description remains unconfirmed; no runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="45" customHeight="1">
@@ -6166,40 +6166,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2000801414</x:v>
       </x:c>
       <x:c r="F98" s="24" t="str">
-        <x:v>Research and staff development</x:v>
+        <x:v>Gemstones and mineral economy</x:v>
       </x:c>
       <x:c r="G98" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H98" s="24" t="str">
-        <x:v>Use the mod's native research or skill workflow as part of the company lab and training plan. The Backrooms tree should own gate, mapping, containment, and spatial-analysis milestones and should not overwrite other research trees.</x:v>
+        <x:v>Treat gems as optional resource/trade content; keep Rimrooms currency and research independent.</x:v>
       </x:c>
       <x:c r="I98" s="24" t="str">
-        <x:v>Medium: check research tab replacements, prerequisite edits, and project speed changes. Backrooms milestones need stable definitions and an independent route when optional trees are absent.</x:v>
+        <x:v>Use native item behavior only; do not require gems or reuse content.</x:v>
       </x:c>
       <x:c r="J98" s="24" t="str">
-        <x:v>Medium: preserve native research progression and add Backrooms milestones as a separate, optional chain.</x:v>
+        <x:v>Verify mining/trade/tribute and item definitions with Jewelry; duplicate-Ruby report is unverified.</x:v>
       </x:c>
       <x:c r="K98" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L98" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-FAC;RR-EVD;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M98" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2000801414-zylle.Gemstones.md</x:v>
       </x:c>
       <x:c r="N98" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O98" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional materials/economy content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P98" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q98" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and existing source note reviewed; license unresolved and interaction report unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="45" customHeight="1">
@@ -6234,25 +6234,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K99" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L99" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-STA;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M99" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3674332861-MemeGoddess.GiddyUp.md</x:v>
       </x:c>
       <x:c r="N99" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O99" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional mount behavior; expeditions must work without it.</x:v>
       </x:c>
       <x:c r="P99" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '2.2.5'; local support 1.4, 1.5, 1.6; About.xml SHA-256 8483B32882CB44654CC0AEB985668DF872E1969EEEC7DF6448D9152947FD2848</x:v>
       </x:c>
       <x:c r="Q99" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify caravans, combat, exits, save/load, and two-client RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="45" customHeight="1">
@@ -6287,25 +6287,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K100" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L100" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M100" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1541794953-amunra.gmc.md</x:v>
       </x:c>
       <x:c r="N100" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O100" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional medicine recipe; not required for care or progression.</x:v>
       </x:c>
       <x:c r="P100" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 5800979EA3D61DC773CF9CA5A8535301B7F72687D17088605EF2770D26C3ED72</x:v>
       </x:c>
       <x:c r="Q100" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify research, bench, ingredients, output, time, placement, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="45" customHeight="1">
@@ -6331,34 +6331,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H101" s="24" t="str">
-        <x:v>Use world events, factions, comms, traders, and saleable goods to support company contracts, procurement, outposts, and revenue. Add company jobs through a dedicated Operations interface while honoring the profile's comms and quest settings.</x:v>
+        <x:v>Use its optional exploration events as a separate source of world stories. Do not make it the Backrooms coordinate, room, or mission generator.</x:v>
       </x:c>
       <x:c r="I101" s="24" t="str">
-        <x:v>Medium to high: world objects, quests, traders, and site creation require exact RimWorld Together synchronization review. Keep the company ledger distinct from vanilla silver and other mods' transaction state.</x:v>
+        <x:v>Leave its event flow native and keep company contracts and Backrooms site identity in their own systems.</x:v>
       </x:c>
       <x:c r="J101" s="24" t="str">
-        <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
+        <x:v>Test event frequency and duplication with faction/quest mods, comms settings, world-map changes, and RWT branch ownership.</x:v>
       </x:c>
       <x:c r="K101" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L101" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-MSN;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M101" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1814100216-Albion.GoExplore.md</x:v>
       </x:c>
       <x:c r="N101" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O101" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: separate optional native exploration content; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P101" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 C231AEA51F5738D9D95E1F7F852DD950110C3442928389AB2DE7FAA4347E2EC0</x:v>
       </x:c>
       <x:c r="Q101" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify events, site entry/exit, rewards, quest filters, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="45" customHeight="1">
@@ -6393,25 +6393,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K102" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L102" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M102" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2527544142-kongkim.GSingots.md</x:v>
       </x:c>
       <x:c r="N102" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O102" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional Royalty-linked economy flavor; never a required input.</x:v>
       </x:c>
       <x:c r="P102" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 D223D77B8D4EAA05270661E1AB8C17CE251FDCAFEC6D054A102F7A7732517E19</x:v>
       </x:c>
       <x:c r="Q102" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify recipes, market/tribute values, and Core-only absence path.</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="45" customHeight="1">
@@ -6446,25 +6446,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K103" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L103" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STYLE;RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M103" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2807132773-Arkymn.AgingVisuals.md</x:v>
       </x:c>
       <x:c r="N103" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O103" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional staff appearance; no adapter.</x:v>
       </x:c>
       <x:c r="P103" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q103" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>No source/license verified. Birthday, gene, age, and optional DLC effects remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="45" customHeight="1">
@@ -6499,25 +6499,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K104" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L104" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M104" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2018947066-Mlie.GreyerMorals.md</x:v>
       </x:c>
       <x:c r="N104" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O104" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional pawn-reaction balance; Rimrooms policies and evidence-sale outcomes remain independent.</x:v>
       </x:c>
       <x:c r="P104" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and publisher page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q104" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact source/license unverified. Trait/Ideology/custody thoughts and ledger boundaries remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="45" customHeight="1">
@@ -6552,25 +6552,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K105" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L105" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M105" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3515052580-Sirprook.HardenedArmor.md</x:v>
       </x:c>
       <x:c r="N105" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O105" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional combat-balance settings; do not make this mod own Rimrooms injury state.</x:v>
       </x:c>
       <x:c r="P105" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Sirprook.HardenedArmor; support 1.5-1.6; About.xml SHA-256 B9B963C5F94C4479CF1B95D7C47806420A1DB24ECEFCB45198575911AC4CC19A</x:v>
       </x:c>
       <x:c r="Q105" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; test armor/penetration and threat balance; Combat Extended behavior is theoretical and unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="45" customHeight="1">
@@ -6605,25 +6605,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K106" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L106" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M106" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1204502413-Smuffle.HarvestOrgansPostMortem.md</x:v>
       </x:c>
       <x:c r="N106" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O106" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional corpse processing; do not make Rimrooms evidence or income depend on organs.</x:v>
       </x:c>
       <x:c r="P106" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 05B30AAC47D60475C12F50187196A98AE5151CAD3CAE3E2DB1E2CCCF0AD62DBE</x:v>
       </x:c>
       <x:c r="Q106" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare 1.6 with/without HugsLib, corpse windows/freezing/yields, and row274 patch in solo.</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="45" customHeight="1">
@@ -6643,40 +6643,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2898826891</x:v>
       </x:c>
       <x:c r="F107" s="24" t="str">
-        <x:v>Materials, cargo, and recovered resources</x:v>
+        <x:v>Animal butchering and resource yields</x:v>
       </x:c>
       <x:c r="G107" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H107" s="24" t="str">
-        <x:v>Use carrying, item handling, harvest, and salvage rules to shape expedition kit limits and recovered-cargo value. Preserve each mod's normal material and weight behavior; add only a Backrooms cargo manifest and appraisal layer.</x:v>
+        <x:v>Use its normal butchering yields if selected; do not duplicate resource harvesting in Rimrooms.</x:v>
       </x:c>
       <x:c r="I107" s="24" t="str">
-        <x:v>Medium: weight, stack, yield, and destruction rules affect mission capacity and valuation. Reconcile cargo accounting with item transfers and avoid duplicate salvage or recipe patches.</x:v>
+        <x:v>No adapter; preserve Core-only butchering and animal-resource paths.</x:v>
       </x:c>
       <x:c r="J107" s="24" t="str">
-        <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
+        <x:v>Check yields, wild-animal setting, explosive animals, Harmony absence and save/load.</x:v>
       </x:c>
       <x:c r="K107" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L107" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-ECO;RR-EXP;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M107" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2898826891-Mlie.HarvestWhenButchering.md</x:v>
       </x:c>
       <x:c r="N107" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O107" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional butchering-yield behavior; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P107" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q107" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="45" customHeight="1">
@@ -6711,25 +6711,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K108" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L108" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EXP;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M108" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/949498803-jkluch.HaulToStack.md</x:v>
       </x:c>
       <x:c r="N108" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O108" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional hauling QoL; do not build supply loops around it.</x:v>
       </x:c>
       <x:c r="P108" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 287296991AB7C83747DC95AF1CB82B67822B561BF067716A49551E5176134E2D</x:v>
       </x:c>
       <x:c r="Q108" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare partial stacks/jobs with Pick Up And Haul row164 on/off.</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="45" customHeight="1">
@@ -6764,25 +6764,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K109" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L109" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M109" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2714095848-Syrus.HMSChoice.md</x:v>
       </x:c>
       <x:c r="N109" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O109" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional serum-selection QoL; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P109" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 4189F33496658A7D3F6D399964CB7F4D3F5B7A707332AEC5D726510DA2C2DA5A</x:v>
       </x:c>
       <x:c r="Q109" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check choose/cancel/consume, animals, save/load, and Core/DLC profiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="45" customHeight="1">
@@ -6817,25 +6817,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K110" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L110" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-MSN;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M110" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2992224079-Adamas.Hospital.md</x:v>
       </x:c>
       <x:c r="N110" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O110" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native hospital/economy scenario; no Rimrooms dependency or adapter.</x:v>
       </x:c>
       <x:c r="P110" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4-1.6; Harmony required; no version/license declared; About SHA-256 A85F70D3A6D9D8DB57D62059BBFDE3BFBD960BF8BE85D6AD93E6027967D78828</x:v>
       </x:c>
       <x:c r="Q110" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify patient arrivals, care/surgery, fees/goodwill, QEE, and RWT only if supported.</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="45" customHeight="1">
@@ -6861,34 +6861,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H111" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Use pawn-powered cycling as optional exercise or emergency generation; never require labor-powered startup or a Prison Labor job for the gate.</x:v>
       </x:c>
       <x:c r="I111" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>Keep its Cycle work and power output native. Do not replace the selected profile work or generator systems.</x:v>
       </x:c>
       <x:c r="J111" s="24" t="str">
-        <x:v>Medium: use as optional power/industry sources; price gate operating cost consistently and do not require one source for basic gate operation.</x:v>
+        <x:v>Check output, movement scaling, work priorities, Prison Labor settings, and synchronized pawn/generator state in RWT.</x:v>
       </x:c>
       <x:c r="K111" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L111" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M111" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1706030487-FLASHPOINT55.HumanPowerGeneratorMod.md</x:v>
       </x:c>
       <x:c r="N111" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O111" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native emergency power/exercise; do not require labor-powered startup.</x:v>
       </x:c>
       <x:c r="P111" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 D1268B0BA80CCC886B8FBBED6E59902E4ED9D19057C00DB8079CE6A0E02F89BA</x:v>
       </x:c>
       <x:c r="Q111" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Cycle jobs, power output, Prison Labor setting, and gate operation without the mod.</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="45" customHeight="1">
@@ -6923,25 +6923,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K112" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L112" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M112" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2023661266-Mlie.IClearlyHaveEnough.md</x:v>
       </x:c>
       <x:c r="N112" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O112" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional construction UI; not procurement/cargo accounting.</x:v>
       </x:c>
       <x:c r="P112" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.3 and publisher/continued-source repo checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q112" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT continuation repo noted. Resource totals, blueprint display, MapComponent removal, and map-transfer behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="45" customHeight="1">
@@ -6976,25 +6976,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K113" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L113" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M113" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2918091446-Zaf.InjectGene.md</x:v>
       </x:c>
       <x:c r="N113" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O113" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech genepack treatment; keep gene packs separate from company evidence.</x:v>
       </x:c>
       <x:c r="P113" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID Workshop text checked 2026-09-27; direct page rate-limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q113" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>No source/license found. Biotech need, settings, coma, item consumption, and gene-bank accounting remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="45" customHeight="1">
@@ -7029,25 +7029,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K114" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L114" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M114" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2413690575-Haecriver.InjuredCarry.md</x:v>
       </x:c>
       <x:c r="N114" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O114" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional manual rescue behavior; not automatic extraction or treatment.</x:v>
       </x:c>
       <x:c r="P114" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 3F2908C1F241A27A9AB5BE771AA974E70E82F4DEEA6C0AEFDF9A9693F43FDB90</x:v>
       </x:c>
       <x:c r="Q114" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check injured pawns/animals, bleeding, guest departure, Vehicle Framework, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="45" customHeight="1">
@@ -7082,25 +7082,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K115" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L115" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M115" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2884115974-Turnovus.Biotech.IntegratedGenes.md</x:v>
       </x:c>
       <x:c r="N115" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O115" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech gene content; Rimrooms staff loop remains Core-compatible.</x:v>
       </x:c>
       <x:c r="P115" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.8.0 and Workshop/changelog sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q115" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Public source/license not verified; Workshop source was removed. DLC-conditioned gene availability and pawn effects remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="45" customHeight="1">
@@ -7135,25 +7135,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K116" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L116" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M116" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3682304832-kazepsi.irbm.md</x:v>
       </x:c>
       <x:c r="N116" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O116" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional global missile/threat reference; no reuse or co-op support claim.</x:v>
       </x:c>
       <x:c r="P116" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.6; About.xml SHA-256 AEAC3838D6DF83A1757C1B74A11DDB844683B0162E98D9466495E5FF637CBD7E</x:v>
       </x:c>
       <x:c r="Q116" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify dependency mismatch, events/launches/world state, branch ownership, save/reconnect.</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="45" customHeight="1">
@@ -7188,25 +7188,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K117" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L117" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-FAC;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M117" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2856471776-Mlie.JustPutItOverThere.md</x:v>
       </x:c>
       <x:c r="N117" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O117" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional delivery convenience; ground-drop fallback must stay visible; avoid duplicate/lost paid goods.</x:v>
       </x:c>
       <x:c r="P117" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.1'; local support 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 C9F45B4321DA906E590B8C9E9A7256C470967FC895D9EAC882FA95532BA2336A</x:v>
       </x:c>
       <x:c r="Q117" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify reachable/unavailable storage, guests/trades, Common Sense option, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="45" customHeight="1">
@@ -7241,25 +7241,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K118" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L118" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M118" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3461478214-Linnun.KeepConverting.md</x:v>
       </x:c>
       <x:c r="N118" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O118" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Ideology conversion automation; no Rimrooms onboarding dependency.</x:v>
       </x:c>
       <x:c r="P118" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q118" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>No source/license verified. Reported errors, conversion stop conditions, load order and Integrated Genes interaction remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="45" customHeight="1">
@@ -7294,25 +7294,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K119" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L119" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M119" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3559816908-Mlie.LadiesCanFlirtToo.md</x:v>
       </x:c>
       <x:c r="N119" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O119" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional staff relationship behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P119" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and publisher/continued-source repo checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q119" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT continuation repo noted; separate source assets not covered. Romance behavior with rows119/197/238 remains untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="45" customHeight="1">
@@ -7347,25 +7347,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K120" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L120" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M120" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2014603702-Mlie.LessStupidRomanceAttempt.md</x:v>
       </x:c>
       <x:c r="N120" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O120" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional relationship behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P120" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.2 and publisher/continued-source repo checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q120" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT continuation repo noted. Original asset/source rights and row118/197/238 interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="45" customHeight="1">
@@ -7400,25 +7400,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K121" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L121" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M121" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2659985388-Mlie.LiveWithThePain.md</x:v>
       </x:c>
       <x:c r="N121" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O121" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional injury-recovery tuning; no dependency.</x:v>
       </x:c>
       <x:c r="P121" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.2'; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 1B1D302BE16DD3FA87B32883730D5F780CB54C012F88A2D842A1ABEDF597D8F2</x:v>
       </x:c>
       <x:c r="Q121" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify pain-reduction stages/modifiers, pawn scope, long save, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="45" customHeight="1">
@@ -7453,25 +7453,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K122" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L122" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M122" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1541795146-amunra.lc.md</x:v>
       </x:c>
       <x:c r="N122" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O122" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional drug-manufacturing economy content; not an essential staff-care path.</x:v>
       </x:c>
       <x:c r="P122" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and current publisher page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q122" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher recipe differs from older third-party translation; current recipe recorded. Work, market, and selected medicine/trade interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="45" customHeight="1">
@@ -7506,25 +7506,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K123" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L123" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-ECO;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M123" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3373064575-ASF.DeepStorage.md</x:v>
       </x:c>
       <x:c r="N123" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O123" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional storage content; keep vanilla storage fallback.</x:v>
       </x:c>
       <x:c r="P123" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 3F6B3E84997358D345126E4EE3D390FE2CE26277F6C9E9A3D19820D94AEC98F5</x:v>
       </x:c>
       <x:c r="Q123" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify construction, hauling, limits, DLC-absent mode, and gravship cargo.</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="45" customHeight="1">
@@ -7559,25 +7559,25 @@
         <x:v>Medium: preserve native research progression and add Backrooms milestones as a separate, optional chain.</x:v>
       </x:c>
       <x:c r="K124" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L124" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M124" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/731111514-ratys.madskills.md</x:v>
       </x:c>
       <x:c r="N124" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O124" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional skill balance; no Rimrooms training dependency.</x:v>
       </x:c>
       <x:c r="P124" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata includes v1.6 folder; Workshop/source repo checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q124" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>GPLv3 source noted. Decay/settings and selected training/work interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="45" customHeight="1">
@@ -7612,25 +7612,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K125" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L125" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-OUT;RR-SPACE;RR-UI;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M125" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2800857642-m00nl1ght.MapPreview.md</x:v>
       </x:c>
       <x:c r="N125" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O125" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional/no-touch map-preview utility; no Backrooms-generation adapter planned.</x:v>
       </x:c>
       <x:c r="P125" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.12.26; supports 1.3-1.6; About SHA-256 04BC5687850597CCACEBCE213BD04FEB5C867AD040FA0AB7D058E9971E03B90B</x:v>
       </x:c>
       <x:c r="Q125" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify world-gen preview/seed accuracy and RWT separately; publisher multiplayer warning is not an RWT result.</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="45" customHeight="1">
@@ -7665,25 +7665,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K126" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L126" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M126" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3538082807-Memegoddess.MealsOnWheels.md</x:v>
       </x:c>
       <x:c r="N126" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O126" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional meal access; do not rely on it for ration accounting.</x:v>
       </x:c>
       <x:c r="P126" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 B049AD3E1ACCED39F656BEB203E03AA97EA7AE7680974974E6D5F5675A7D67C0</x:v>
       </x:c>
       <x:c r="Q126" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check animal/pawn/caravan meals and Pick Up And Haul row164 job loops/save.</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="45" customHeight="1">
@@ -7718,25 +7718,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K127" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L127" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M127" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3480177412-cantaloupetheclown.MedicalIVsFork.md</x:v>
       </x:c>
       <x:c r="N127" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O127" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional medical IV equipment; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P127" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.5, 1.6; About.xml SHA-256 01FC47BDE1CB804EA06B33A8F52F4FB9C8791F4FE86CC3A127CC47F247CDA388</x:v>
       </x:c>
       <x:c r="Q127" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Biotech on/off, IV behavior, medicine use, beds, jobs, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="45" customHeight="1">
@@ -7756,40 +7756,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3769804600</x:v>
       </x:c>
       <x:c r="F128" s="24" t="str">
-        <x:v>Research and staff development</x:v>
+        <x:v>Mining and ore-vein designation UI</x:v>
       </x:c>
       <x:c r="G128" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H128" s="24" t="str">
-        <x:v>Use the mod's native research or skill workflow as part of the company lab and training plan. The Backrooms tree should own gate, mapping, containment, and spatial-analysis milestones and should not overwrite other research trees.</x:v>
+        <x:v>Use only as optional mining convenience; Rimrooms exploration, mining and return routes must not depend on this UI.</x:v>
       </x:c>
       <x:c r="I128" s="24" t="str">
-        <x:v>Medium: check research tab replacements, prerequisite edits, and project speed changes. Backrooms milestones need stable definitions and an independent route when optional trees are absent.</x:v>
+        <x:v>No Rimrooms adapter or dependency; preserve the vanilla Mine-designator path when absent.</x:v>
       </x:c>
       <x:c r="J128" s="24" t="str">
-        <x:v>Medium: preserve native research progression and add Backrooms milestones as a separate, optional chain.</x:v>
+        <x:v>Publisher confirms a Mine-designator overlay, configurable Shift-click vein designation and Harmony requirement; page status banners are not runtime findings.</x:v>
       </x:c>
       <x:c r="K128" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L128" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-FAC;RR-OUT;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M128" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3769804600-rabiosus.minesight.md</x:v>
       </x:c>
       <x:c r="N128" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O128" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional mining and exploration UI convenience; no Rimrooms dependency or adapter.</x:v>
       </x:c>
       <x:c r="P128" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata snapshot dated 2026-09-27; publisher Workshop description and author comments reviewed.</x:v>
       </x:c>
       <x:c r="Q128" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher confirms Mine overlay, configurable Shift-click vein designation, Harmony requirement, and Mine-only tool scope. Page notices are not runtime findings; no license or runtime/profile test.</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="45" customHeight="1">
@@ -7824,25 +7824,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K129" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L129" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M129" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/872762753-erdelf.MinifyEverything.md</x:v>
       </x:c>
       <x:c r="N129" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O129" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional experimental construction utility; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P129" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 C274605B58EE5915845A17CFD692D674C7786F9BDA961151B349BDB455800407</x:v>
       </x:c>
       <x:c r="Q129" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check minify/transport/reinstall, contents/power restoration, defense portability, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="45" customHeight="1">
@@ -7877,25 +7877,25 @@
         <x:v>Medium: preserve native research progression and add Backrooms milestones as a separate, optional chain.</x:v>
       </x:c>
       <x:c r="K130" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L130" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M130" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/717575199-Haplo.Miscellaneous.Training.md</x:v>
       </x:c>
       <x:c r="N130" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O130" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional training furniture; never the sole staff-development route.</x:v>
       </x:c>
       <x:c r="P130" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.6 and author source collection checked 2026-09-27; Steam fetch 429; no runtime test.</x:v>
       </x:c>
       <x:c r="Q130" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>CC BY-SA 4.0 source collection noted; Workshop-page details partly corroborated via source/third parties. Training effects and selected weapon/work interactions untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="45" customHeight="1">
@@ -7930,25 +7930,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K131" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L131" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STYLE;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M131" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3341372760-Burpee.MoreBeautifulBodies.md</x:v>
       </x:c>
       <x:c r="N131" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O131" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech-dependent appearance support; Core-only profile must omit it.</x:v>
       </x:c>
       <x:c r="P131" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and exact-ID indexed Workshop text checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q131" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Texture reuse permission is limited/asset scope unverified; no code license/source. Row268/order and DLC-absent behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="45" customHeight="1">
@@ -7983,25 +7983,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K132" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L132" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M132" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1638467041-AtamanDolinskaja.MoreCrashedShipParts.md</x:v>
       </x:c>
       <x:c r="N132" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O132" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native ship-threat content; no Rimrooms incident patch planned.</x:v>
       </x:c>
       <x:c r="P132" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; Harmony required; About SHA-256 9AD7E3FF50E8EDF12F970CA05DF970035B85C9C146795A83FBFDD3D8F94E8D60</x:v>
       </x:c>
       <x:c r="Q132" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify incident frequency, map scope, paired ship-part content, cleanup, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="45" customHeight="1">
@@ -8036,25 +8036,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K133" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L133" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-MSN;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M133" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2379076640-Mlie.MoreFactionInteraction.md</x:v>
       </x:c>
       <x:c r="N133" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O133" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native faction/event features; keep Rimrooms ledger and sites independent.</x:v>
       </x:c>
       <x:c r="P133" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.8; About SHA-256 A3EA0B9A4D68AAE28E648D1D096D47C97BD1292311AD1FA931017E3169F33B0F</x:v>
       </x:c>
       <x:c r="Q133" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check selected load order, event/trader cadence, quest pawns, save/load, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="45" customHeight="1">
@@ -8089,25 +8089,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K134" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L134" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M134" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2558978295-arl85.AnimalsAgeFilter.md</x:v>
       </x:c>
       <x:c r="N134" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O134" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal-management QoL; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P134" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q134" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="45" customHeight="1">
@@ -8142,25 +8142,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K135" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L135" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M135" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1103809207-4loris4.MoreLinkables.md</x:v>
       </x:c>
       <x:c r="N135" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O135" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional facility furniture/linking; do not balance Rimrooms around claimed speed bonuses.</x:v>
       </x:c>
       <x:c r="P135" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q135" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="45" customHeight="1">
@@ -8195,25 +8195,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K136" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L136" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-ECO;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M136" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3453878341-KobeRiddle.MilkAndWoolPatches.md</x:v>
       </x:c>
       <x:c r="N136" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O136" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal-resource variety; not a Rimrooms economy requirement.</x:v>
       </x:c>
       <x:c r="P136" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q136" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="45" customHeight="1">
@@ -8248,25 +8248,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K137" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L137" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-SPACE;RR-OUT;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M137" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1931453053-zylle.MoreVanillaBiomes.md</x:v>
       </x:c>
       <x:c r="N137" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O137" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional RimWorld world-generation content; Rimrooms space generation remains independent.</x:v>
       </x:c>
       <x:c r="P137" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q137" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="45" customHeight="1">
@@ -8301,25 +8301,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K138" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L138" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M138" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1729446857-hobtook.mortaraccuracy.md</x:v>
       </x:c>
       <x:c r="N138" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O138" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional artillery balance feature; Combat Extended is explicitly incompatible.</x:v>
       </x:c>
       <x:c r="P138" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package hobtook.mortaraccuracy; support 1.0-1.6; About.xml SHA-256 C5CD2382C803ECB5A7247245D153C8B4036E2CABDB7546D9DA37D70139CD71A</x:v>
       </x:c>
       <x:c r="Q138" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check predictions, weather, skill, target movement, artillery variants, and any RWT claim.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="45" customHeight="1">
@@ -8354,25 +8354,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K139" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L139" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M139" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3221480525-ferny.moveyourmonolith.md</x:v>
       </x:c>
       <x:c r="N139" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O139" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Anomaly layout utility; not a Rimrooms gate or navigation system.</x:v>
       </x:c>
       <x:c r="P139" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher page/change notes checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q139" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher warns to move before monolith activation. Quest, attunement, and Core-only absence remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="45" customHeight="1">
@@ -8407,25 +8407,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K140" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L140" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M140" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2917732219-IssacZhuang.MuzzleFlash.md</x:v>
       </x:c>
       <x:c r="N140" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O140" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional visual effect; threat cues must remain readable without it; do not reuse assets without permission.</x:v>
       </x:c>
       <x:c r="P140" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package IssacZhuang.MuzzleFlash; support 1.4-1.6; About.xml SHA-256 760AE11964BEB0DCB1E82ED19CB168F6D6BEC6D28BB87E29CEDD1CE3DFA873CA</x:v>
       </x:c>
       <x:c r="Q140" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check selected weapons, retextures, DLC, logs, and Blood Animations overlap.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="45" customHeight="1">
@@ -8460,25 +8460,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K141" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L141" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-EVD;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M141" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3229905841-ferny.NameYourEntities.md</x:v>
       </x:c>
       <x:c r="N141" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O141" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional captured-threat display naming; stable Rimrooms IDs remain separate.</x:v>
       </x:c>
       <x:c r="P141" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and current Workshop page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q141" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Workshop requires Anomaly but local metadata omits hard requirement. Exact installed revision, persistence, and Core-only behavior remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="45" customHeight="1">
@@ -8513,25 +8513,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K142" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L142" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M142" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3263018536-zal.namesgalore.md</x:v>
       </x:c>
       <x:c r="N142" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O142" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional pawn naming; never use generated names as identity keys or lore canon.</x:v>
       </x:c>
       <x:c r="P142" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.0.1 and Workshop/original repo checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q142" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT mod code noted; separate name-data corpus license/provenance unresolved. Reported naming/faction issues and transfer persistence remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="45" customHeight="1">
@@ -8566,25 +8566,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K143" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L143" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M143" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2566316158-AmCh.NeedBarOverflow.md</x:v>
       </x:c>
       <x:c r="N143" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O143" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional need-bar behavior; Rimrooms care/cafeteria routes stay independent.</x:v>
       </x:c>
       <x:c r="P143" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.4.7 and publisher page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q143" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>GPLv3 stated. Row75 idle-recreation interaction and alpha-books report remain unverified; profile behavior pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="45" customHeight="1">
@@ -8619,25 +8619,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K144" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L144" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M144" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1541795281-amunra.nc.md</x:v>
       </x:c>
       <x:c r="N144" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O144" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional neutroamine recipe; keep medicine/production usable without it.</x:v>
       </x:c>
       <x:c r="P144" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 2A4CADFEA02B45DC5B6976C3B386809277A69A86036870A6758E4754D2836392</x:v>
       </x:c>
       <x:c r="Q144" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify research, ingredients, yield, price, trade, save/load, and rows99/121.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="45" customHeight="1">
@@ -8672,25 +8672,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K145" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L145" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M145" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1923990111-Unon.NoBurnMetal.md</x:v>
       </x:c>
       <x:c r="N145" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O145" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional fire-rule patch; keep Rimrooms fire/material rules self-contained.</x:v>
       </x:c>
       <x:c r="P145" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 46E44D82DF6C05C11E8CBB58564F352B81C2F24932B46AAF9403A3F71B0FD55C</x:v>
       </x:c>
       <x:c r="Q145" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify vanilla/custom metal flammability, spread, XML errors, and safe add/remove.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="45" customHeight="1">
@@ -8725,25 +8725,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K146" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L146" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M146" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/914638336-cucumpear.cooties.md</x:v>
       </x:c>
       <x:c r="N146" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O146" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional apparel-thought adjustment; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P146" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q146" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="45" customHeight="1">
@@ -8778,25 +8778,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K147" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L147" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M147" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2887053053-Dark.NoHemogenFarmMedicalAlert.md</x:v>
       </x:c>
       <x:c r="N147" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O147" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional alert filter only; not treatment or containment.</x:v>
       </x:c>
       <x:c r="P147" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 17513522D94E61ECB85CCF4EAAC04EDD267E08600FEB2BF87E1E806D80FC9B46</x:v>
       </x:c>
       <x:c r="Q147" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify intended hemogen alert case, unrelated emergencies, arrest edge case, and row 292.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="45" customHeight="1">
@@ -8831,25 +8831,25 @@
         <x:v>High: profile suppresses vanilla infestations. Backrooms threats need their own incident and entity systems; do not reuse an infestation incident.</x:v>
       </x:c>
       <x:c r="K148" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L148" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M148" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2890080496-walkingproblem.noinfestation.md</x:v>
       </x:c>
       <x:c r="N148" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O148" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional event-removal preference; Rimrooms threats and quests must not depend on infestations.</x:v>
       </x:c>
       <x:c r="P148" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q148" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="45" customHeight="1">
@@ -8884,25 +8884,25 @@
         <x:v>Medium: company contracts must respect the profile's comms rule or use a clearly separate Operations contract board.</x:v>
       </x:c>
       <x:c r="K149" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L149" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-MSN;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M149" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2557302879-eBae.NoQuestsWithoutComms.md</x:v>
       </x:c>
       <x:c r="N149" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O149" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration only; Rimrooms objectives must not depend on this quest filter.</x:v>
       </x:c>
       <x:c r="P149" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4-1.6; no modVersion; About SHA-256 0144929D49F5648B1421344AC0F2998F63E8FFA03D8968B0F0A59B44D64E14D2</x:v>
       </x:c>
       <x:c r="Q149" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare quest behavior before/after comms and with custom objectives.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="45" customHeight="1">
@@ -8922,40 +8922,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2558797536</x:v>
       </x:c>
       <x:c r="F150" s="24" t="str">
-        <x:v>Furniture, clothing, and visual content</x:v>
+        <x:v>Royalty clothing-demand setting</x:v>
       </x:c>
       <x:c r="G150" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H150" s="24" t="str">
-        <x:v>Use these items to furnish laboratories, cafeterias, dormitories, security rooms, and company uniforms. Treat mod assets as user-installed content; create original Backrooms assets for any new distributed material.</x:v>
+        <x:v>Keep royalty clothing demands optional; Rimrooms uniforms and staff progression remain independent.</x:v>
       </x:c>
       <x:c r="I150" s="24" t="str">
-        <x:v>Low: prefer no code hooks. Check room roles and apparel restrictions only where company roles need them; avoid hard dependencies on optional aesthetics or furniture.</x:v>
+        <x:v>No adapter; require Royalty only when the player selects this mod/DLC path.</x:v>
       </x:c>
       <x:c r="J150" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>Workshop lists Royalty required while local metadata has no hard DLC requirement.</x:v>
       </x:c>
       <x:c r="K150" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L150" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M150" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2558797536-No.Royal.Clothing.Reqs.md</x:v>
       </x:c>
       <x:c r="N150" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O150" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Royalty-only configuration; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P150" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q150" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; DLC requirement mismatch noted; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="45" customHeight="1">
@@ -8990,25 +8990,25 @@
         <x:v>High: profile suppresses vanilla solar flares. Gate power pressure must come from Backrooms machine states or incidents, not an assumed solar-flare event.</x:v>
       </x:c>
       <x:c r="K151" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L151" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M151" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2879659174-laura7z.noflares.md</x:v>
       </x:c>
       <x:c r="N151" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O151" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: no integration until the installed package effect is identified; do not infer behavior from title/comments.</x:v>
       </x:c>
       <x:c r="P151" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q151" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="45" customHeight="1">
@@ -9043,25 +9043,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K152" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L152" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M152" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3533769253-sk.noprisonersympathy.md</x:v>
       </x:c>
       <x:c r="N152" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O152" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration-only; no Rimrooms integration planned.</x:v>
       </x:c>
       <x:c r="P152" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.5.0; About SHA-256 5A72B6B7E01D9B9D085CD5697D27485A1B37C01DA6C75F62447A79824E3968AE</x:v>
       </x:c>
       <x:c r="Q152" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare prisoner-action thoughts with Ideology and harvesting mods.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="45" customHeight="1">
@@ -9096,25 +9096,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K153" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L153" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-EVD;RR-THREAT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M153" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1778821244-avilmask.NonUnoPinata.md</x:v>
       </x:c>
       <x:c r="N153" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O153" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional corpse/inventory behavior; not Rimrooms evidence ledger.</x:v>
       </x:c>
       <x:c r="P153" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 5C96642877F0D2A396E9C66D69954CC527DAD71952C7F6E5349AD313B14360EF</x:v>
       </x:c>
       <x:c r="Q153" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check downed/dead pawns, prisoner/guest stripping, cremation/butchering, transfer, and removal.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="45" customHeight="1">
@@ -9149,25 +9149,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K154" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L154" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-OUT;RR-ECO;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M154" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2870045856-Vesper.NotMyFault.md</x:v>
       </x:c>
       <x:c r="N154" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O154" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional relationship-balance patch; Rimrooms reputation and contracts remain independent.</x:v>
       </x:c>
       <x:c r="P154" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q154" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="45" customHeight="1">
@@ -9202,25 +9202,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K155" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L155" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M155" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3465476199-io.github.cvrunmin.OrbitTradeNotOnlyGeneBank.md</x:v>
       </x:c>
       <x:c r="N155" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O155" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native gene-pack trade behavior; no contract payout dependency or adapter.</x:v>
       </x:c>
       <x:c r="P155" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.0.0; supports 1.5-1.6; Biotech and Harmony required; About SHA-256 0B291B9472E88B0AB66142D27A6A3C3634CFDC5AA9B0C27B19BE49871F2EAA9D</x:v>
       </x:c>
       <x:c r="Q155" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Oops All Gene Banks visibleToTraders setting, beacon patch, trade counts, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="45" customHeight="1">
@@ -9255,25 +9255,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K156" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L156" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M156" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1414302321-Mehni.Numbers.md</x:v>
       </x:c>
       <x:c r="N156" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O156" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional workforce dashboard; no Rimrooms data ownership.</x:v>
       </x:c>
       <x:c r="P156" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata and publisher/source checked 2026-09-27; no runtime test.</x:v>
       </x:c>
       <x:c r="Q156" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Local package/dependency snapshot and stated publisher/source findings recorded in linked note; no isolated or combined-profile runtime test; compatibility remains unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="45" customHeight="1">
@@ -9308,25 +9308,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K157" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L157" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M157" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3266000468-Mlie.OffspringInheritXenogenes.md</x:v>
       </x:c>
       <x:c r="N157" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O157" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech offspring genetics; no staff/recruitment dependency.</x:v>
       </x:c>
       <x:c r="P157" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.0 and publisher/continued-repo sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q157" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT continuation repo noted. Inheritance with other selected gene mods, save/load, and RWT pawn transfer remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="45" customHeight="1">
@@ -9361,25 +9361,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K158" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L158" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-EVD;RR-EXP;RR-OUT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M158" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1447140290-Ogre.OgreStack.md</x:v>
       </x:c>
       <x:c r="N158" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O158" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional stack-size configuration; keep vanilla stack limits supported.</x:v>
       </x:c>
       <x:c r="P158" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 37B9C6686DB208B3F67DB1ED86898DBC4E9CD745D69B170A3B06D6184EAE66CA</x:v>
       </x:c>
       <x:c r="Q158" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify configuration/save warning, storage/cargo display, caravans, and RWT item exchange.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="45" customHeight="1">
@@ -9414,25 +9414,25 @@
         <x:v>Medium: preserve native research progression and add Backrooms milestones as a separate, optional chain.</x:v>
       </x:c>
       <x:c r="K159" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L159" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-ECO;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M159" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2883683444-redundant.oopsallgenepacks.md</x:v>
       </x:c>
       <x:c r="N159" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O159" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech lab/storage; do not require it or treat genes as Rimrooms evidence.</x:v>
       </x:c>
       <x:c r="P159" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/source pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q159" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>No reuse license found. Gene bank capacity, trader setting, row154 relationship, and RWT custom-content transfer remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="45" customHeight="1">
@@ -9467,25 +9467,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K160" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L160" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-STA;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M160" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1501052499-PackMulesExtended.Standard.md</x:v>
       </x:c>
       <x:c r="N160" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O160" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional caravan pack species; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P160" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 F08CD9F6CB13A8657BD7AE2C9D091419334059BB9FB9E3A73B8165E50B16D55A</x:v>
       </x:c>
       <x:c r="Q160" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify capacity, caravan travel/return, species, row46/98 interactions, and safe removal.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="45" customHeight="1">
@@ -9520,25 +9520,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K161" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L161" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-SPACEFLIGHT;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M161" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2509511179-turnovus.submod.backpacksarenotbelts.md</x:v>
       </x:c>
       <x:c r="N161" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O161" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional equipment-layer patch; DLC remain optional.</x:v>
       </x:c>
       <x:c r="P161" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '2.5.0'; local support 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 9C3B6363836A633FACB074EE7696CA9EEAFEFA950540062DB69DBA546BBB1C11</x:v>
       </x:c>
       <x:c r="Q161" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify belts+packs, VAE/VGE gear, DLC combinations, settings/restart, and save/reload.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="45" customHeight="1">
@@ -9573,25 +9573,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K162" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L162" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M162" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3583129312-Mlie.PassItThroughTheWindow.md</x:v>
       </x:c>
       <x:c r="N162" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O162" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional room-to-room item transfer; not a secure containment barrier.</x:v>
       </x:c>
       <x:c r="P162" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Mlie.PassItThroughTheWindow; version 1.6.1; support 1.5-1.6; About.xml SHA-256 A0A86367B927B4814F6ECD881A7E5D3C8947A615A900CC91B4804AF9A61488F4</x:v>
       </x:c>
       <x:c r="Q162" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check item eligibility, perishables, research, LWM storage, controlled rooms, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="45" customHeight="1">
@@ -9626,25 +9626,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K163" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L163" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M163" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2014789938-fed1sPlay.PawnTargetFix.md</x:v>
       </x:c>
       <x:c r="N163" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O163" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional pawn-targeting behavior; not a turret patch and no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P163" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package fed1sPlay.PawnTargetFix; support 1.1-1.6; About.xml SHA-256 5A616ED3C213EBE318C27EE0E5818C71D035C377DEECBB29C8FEFAD37C006A13</x:v>
       </x:c>
       <x:c r="Q163" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check manual targets, friendly fire, downed targets, and row198 moving-fire interaction.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="45" customHeight="1">
@@ -9679,25 +9679,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K164" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L164" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M164" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3261312042-Owlchemist.PermeableTerrain.md</x:v>
       </x:c>
       <x:c r="N164" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O164" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional/configuration-only; consider a narrow XML adapter only if generated surfaces need its filth decay.</x:v>
       </x:c>
       <x:c r="P164" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.3-1.6; Harmony required; About SHA-256 FB92F7EE8276E80DBF1C72F51D654A9E29DB5E59E2CC41B5214092A5BF3199DE</x:v>
       </x:c>
       <x:c r="Q164" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify spawned filth expiry, XML extensions, generated terrain, and optional ReGrowth ordering.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="45" customHeight="1">
@@ -9732,25 +9732,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K165" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L165" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EXP;RR-OUT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M165" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1279012058-Mehni.PickUpAndHaul.md</x:v>
       </x:c>
       <x:c r="N165" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O165" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional hauling QoL; Rimrooms cargo records and vanilla hauling remain independent.</x:v>
       </x:c>
       <x:c r="P165" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q165" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT upstream noted. Publisher limitations, row107/125 hauling interactions, item accounting, and RWT transfer remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="45" customHeight="1">
@@ -9785,25 +9785,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K166" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L166" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M166" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2807616911-Mlie.PlantGrowthSync.md</x:v>
       </x:c>
       <x:c r="N166" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O166" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional harvest scheduling; do not base supply contracts on fixed timing.</x:v>
       </x:c>
       <x:c r="P166" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q166" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Workshop broad MIT claim and upstream LGPL-3.0 do not resolve selected continuation license. Crop/hauling effects untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="45" customHeight="1">
@@ -9838,25 +9838,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K167" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L167" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M167" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2018276375-Mlie.PlasteelSurgery.md</x:v>
       </x:c>
       <x:c r="N167" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O167" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional surgery/research content; not needed for care or progression.</x:v>
       </x:c>
       <x:c r="P167" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.1'; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 8D8916B2B374F80F054D8A9A9BDA5C8A04CC731D61CC47145BF114E252A99C9E</x:v>
       </x:c>
       <x:c r="Q167" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check recipes, body/voice/trait outcomes, relationships, save/load, and removal.</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="45" customHeight="1">
@@ -9882,34 +9882,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H168" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Use manual or grouped power-pole wiring as an optional facility layout control for keeping gate circuits organized.</x:v>
       </x:c>
       <x:c r="I168" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>Leave its wiring controls native; build the machine as ordinary power consumers unless a later verified extension is needed.</x:v>
       </x:c>
       <x:c r="J168" s="24" t="str">
-        <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
+        <x:v>Test construction/removal, circuit flow, group controls, and save/load beside the selected power and industrial mods.</x:v>
       </x:c>
       <x:c r="K168" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L168" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M168" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2507086460-co.uk.epicguru.rimforgepoles.md</x:v>
       </x:c>
       <x:c r="N168" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O168" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: use native wiring controls; no Rimrooms patch planned.</x:v>
       </x:c>
       <x:c r="P168" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4-1.6; no modVersion; About SHA-256 E989E88E52444BD14FC634A3198FD9D6C7EE80DAE0E5144CB9D8BA70FAE71478</x:v>
       </x:c>
       <x:c r="Q168" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify construction/removal and power flow with the selected power systems.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="45" customHeight="1">
@@ -9944,25 +9944,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K169" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L169" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M169" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3009738919-tk421storm.PriorityTreatmentRessurected.md</x:v>
       </x:c>
       <x:c r="N169" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O169" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional emergency-care QoL; not a Rimrooms medical system.</x:v>
       </x:c>
       <x:c r="P169" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 1F45A053BC08073FA07E1AFCAA0B04A14E256F0E508D57D230808429B8D5B376</x:v>
       </x:c>
       <x:c r="Q169" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check priorities/needs/surgery, row209 medicine behavior, and stalled jobs.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="45" customHeight="1">
@@ -9997,25 +9997,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K170" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L170" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M170" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2898000489-Mlie.PrisonCommons.md</x:v>
       </x:c>
       <x:c r="N170" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O170" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native prisoner-room behavior; no adapter planned.</x:v>
       </x:c>
       <x:c r="P170" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.3; About SHA-256 2217441ADF9196BB16B54D5A58835CE0F00627FBF28B9A92BC860B6F9994206E</x:v>
       </x:c>
       <x:c r="Q170" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify doors, feeding, warden jobs, Prisoners Dont Have Keys, and Prison Labor.</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="45" customHeight="1">
@@ -10050,25 +10050,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K171" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L171" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M171" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2022581505-Mlie.PrisonerArena.md</x:v>
       </x:c>
       <x:c r="N171" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O171" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native prisoner content; no Rimrooms arena or adapter.</x:v>
       </x:c>
       <x:c r="P171" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.1; About SHA-256 2D51638525D96782CD667540F7214AF517075CDC513403401DD35B870E212C35</x:v>
       </x:c>
       <x:c r="Q171" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify warden hauling, fights, release/death, interruption, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="45" customHeight="1">
@@ -10103,25 +10103,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K172" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L172" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M172" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3347850851-Extracting.Organs.1.5.md</x:v>
       </x:c>
       <x:c r="N172" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O172" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: no direct integration; do not depend on or redistribute its thought definitions.</x:v>
       </x:c>
       <x:c r="P172" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.5/1.6; no modVersion; About SHA-256 3743990839D497543490C66BE6937D1E5D0F298E370E18628CF09DDC59C9EB41</x:v>
       </x:c>
       <x:c r="Q172" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare thoughts with No Sympathy For Prisoners, Ideology, and Biotech.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="45" customHeight="1">
@@ -10156,25 +10156,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K173" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L173" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M173" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3402467889-ocarina.prisonerjumpsuits.md</x:v>
       </x:c>
       <x:c r="N173" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O173" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional apparel; no Rimrooms clothing requirement or asset reuse planned.</x:v>
       </x:c>
       <x:c r="P173" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no hard dependency or version; local hash 851E12197D1ADDDC94F5F54606CAA18D4F841973D8CB9E621B7245EAAC0FEDFA; upstream repo lists MIT</x:v>
       </x:c>
       <x:c r="Q173" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify apparel policies, forced wear, Prison Labor, and artwork/license boundaries.</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="45" customHeight="1">
@@ -10209,25 +10209,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K174" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L174" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M174" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/794038005-erdelf.PrisonerRansom.md</x:v>
       </x:c>
       <x:c r="N174" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O174" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native ransom behavior; no Rimrooms ledger integration planned.</x:v>
       </x:c>
       <x:c r="P174" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 5A725B8D8458954A8D989DE0DC4134DB4B89BD6650BA8BD1017D6552B9DEBFE0</x:v>
       </x:c>
       <x:c r="Q174" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify comms, accept/reject, raid, repeat transaction, and save/load outcomes.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="45" customHeight="1">
@@ -10262,25 +10262,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K175" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L175" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M175" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3409290110-divineDerivative.PrisonerReading.md</x:v>
       </x:c>
       <x:c r="N175" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O175" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional recreation QoL; no direct integration; validate framework metadata discrepancy.</x:v>
       </x:c>
       <x:c r="P175" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.5-1.6; Harmony required; no version; upstream repo lists MIT; About SHA-256 74655884BC0FDD75E6D0A4A0AEF6FCBF3A10E48E4BA0A7DD8411EB586FA91D79</x:v>
       </x:c>
       <x:c r="Q175" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify books/recreation with Commons, TVForPrison, Prison Labor, and DivineFramework presence.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="45" customHeight="1">
@@ -10315,25 +10315,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K176" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L176" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M176" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2595360307-Mlie.PrisonersDontHaveKeys.md</x:v>
       </x:c>
       <x:c r="N176" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O176" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native/config behavior; no Rimrooms door patch planned.</x:v>
       </x:c>
       <x:c r="P176" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.1; About SHA-256 AA1372440435E53ACAA3C1FD51FD1E513872E2FA57DFC76D5AB638B64375E22E</x:v>
       </x:c>
       <x:c r="Q176" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify commons/cell doors, escape, Doors Expanded, slaves, and Anomaly entities.</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="45" customHeight="1">
@@ -10368,25 +10368,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K177" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L177" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M177" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2076235181-MadaraUchiha.PrisonersNeedRecruiting.md</x:v>
       </x:c>
       <x:c r="N177" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O177" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: leave native reminder optional; no adapter planned.</x:v>
       </x:c>
       <x:c r="P177" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.1-1.6; no modVersion; About SHA-256 6D486C4E3AA8DE6BBF6BB6AD046E3877C94D2F692FCC07BB448488DD04DFDAD3</x:v>
       </x:c>
       <x:c r="Q177" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify reminder/dismissal with prisoner settings, custom interactions, and Hemogen maintain mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="45" customHeight="1">
@@ -10421,25 +10421,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K178" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L178" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M178" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2602436826-Mlie.PrisonersShouldFearTurrets.md</x:v>
       </x:c>
       <x:c r="N178" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O178" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration-only; no Rimrooms turret patch planned.</x:v>
       </x:c>
       <x:c r="P178" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.6.0; supports 1.1-1.6; Harmony required; upstream repo lists MIT; About SHA-256 6D21A9B98D2AF72C0C7034258B4174C6978630E84B0EF837CB3EDBD1808FAC28</x:v>
       </x:c>
       <x:c r="Q178" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify prisoner escape/door/arena/restraint and turret-mod interactions.</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="45" customHeight="1">
@@ -10474,25 +10474,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K179" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L179" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M179" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2012507402-Mlie.ProstheticDidgets.md</x:v>
       </x:c>
       <x:c r="N179" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O179" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional prosthetic digits; vanilla recovery remains available.</x:v>
       </x:c>
       <x:c r="P179" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.1'; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 497AD0E1305AA7997BFE297CDF8D15C1573BCBEC4856D0D03A51A744AAE7291B</x:v>
       </x:c>
       <x:c r="Q179" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify recipes/research, installation, effects, row179 apparel, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="45" customHeight="1">
@@ -10527,25 +10527,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K180" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L180" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M180" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2739055353-Mlie.ProstheticNoMissingBodyParts.md</x:v>
       </x:c>
       <x:c r="N180" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O180" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional apparel compatibility; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P180" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.1'; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 005D9883B87885869E6377335FAE88C72F767A5E481864D784D275153B043F51</x:v>
       </x:c>
       <x:c r="Q180" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify final ordering, prosthetic clothing/armor, row178, and patch overlap.</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="45" customHeight="1">
@@ -10580,25 +10580,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K181" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L181" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-ECO;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M181" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3513846773-DawnsGlow.qualcolor.md</x:v>
       </x:c>
       <x:c r="N181" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O181" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional quality display; retain text labels and non-color cues.</x:v>
       </x:c>
       <x:c r="P181" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID Workshop text checked 2026-09-27; direct fetch rate-limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q181" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Reuse rights/source ownership are unverified. UI surfaces, palettes, and accessibility/readability remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="45" customHeight="1">
@@ -10633,25 +10633,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K182" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L182" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-UI;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M182" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3512466087-hatti.qualitybuilder.md</x:v>
       </x:c>
       <x:c r="N182" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O182" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional construction QoL; do not require quality thresholds or promise resource-neutral retries.</x:v>
       </x:c>
       <x:c r="P182" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.013 and indexed exact-ID Workshop text checked 2026-09-27; direct fetch rate-limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q182" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Fork license not found. Material consumption, work assignment, overlapping builds, and Ideology fallback remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="45" customHeight="1">
@@ -10686,25 +10686,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K183" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L183" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-THREAT;RR-DLC;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M183" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2850854272-Mlie.QuestionableEthicsEnhanced.md</x:v>
       </x:c>
       <x:c r="N183" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O183" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: solo-only optional pending Gate 0 choice; publisher says multiplayer will not work properly.</x:v>
       </x:c>
       <x:c r="P183" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.6.5; supports 1.0-1.6; Harmony required; upstream repository lists MIT; About SHA-256 07A3C667B6B6729378D4EEDD5CACDBCC5F87A74B72546875D8ACD112CF982033</x:v>
       </x:c>
       <x:c r="Q183" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Hospitality vat performance, medical/prisoner overlap, and exact RWT profile before support.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="45" customHeight="1">
@@ -10739,25 +10739,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K184" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L184" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M184" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2886929245-Mlie.RealFactionGuest.md</x:v>
       </x:c>
       <x:c r="N184" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O184" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native faction-pawn support; no Rimrooms adapter planned.</x:v>
       </x:c>
       <x:c r="P184" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.1; About SHA-256 B40C72B4707FC6A637535D1378E3BDFAFF1D0EE3DA7EC220F790381570B19AC9</x:v>
       </x:c>
       <x:c r="Q184" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check quest/event visitors, faction identity, save/load, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="45" customHeight="1">
@@ -10792,25 +10792,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K185" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L185" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M185" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2558042766-Lucifer.RealisticRooms.md</x:v>
       </x:c>
       <x:c r="N185" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O185" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional room-score QoL; never use room-size thresholds as Rimrooms progression gates.</x:v>
       </x:c>
       <x:c r="P185" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package snapshot and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q185" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Source facts and GPL-3.0 repository note recorded. Room/mood behavior in this profile and optional absence remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="45" customHeight="1">
@@ -10845,25 +10845,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K186" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L186" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-THREAT;RR-SPACEFLIGHT;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M186" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3262718980-ReBuild.COTR.DoorsAndCorners.md</x:v>
       </x:c>
       <x:c r="N186" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O186" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional architecture reference; do not reuse code/assets under CC BY-NC-ND.</x:v>
       </x:c>
       <x:c r="P186" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.5-Miller-rev1'; local support 1.5, 1.6; About.xml SHA-256 AE26EFD376A1BD5DD6203C4A6E304F81026BC762EB55DE534B765D8505D57265</x:v>
       </x:c>
       <x:c r="Q186" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify patch logs, construction, pathing, retextures, rows 77/187/201/252/265, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="45" customHeight="1">
@@ -10898,25 +10898,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K187" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L187" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-FAC;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M187" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2904906618-Mlie.RecipeIcons.md</x:v>
       </x:c>
       <x:c r="N187" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O187" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional recipe/UI convenience; every operation must remain readable without icons.</x:v>
       </x:c>
       <x:c r="P187" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q187" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Source facts recorded. Continued-package asset/license coverage and selected-bill UI behavior remain unresolved/unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="45" customHeight="1">
@@ -10951,25 +10951,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K188" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L188" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M188" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2243274070-Mlie.RemoteDoors.md</x:v>
       </x:c>
       <x:c r="N188" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O188" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional remote-control reference; no Rimrooms adapter/dependency.</x:v>
       </x:c>
       <x:c r="P188" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.1'; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 07FB4C65A5F7FD51D95BB5B599932E01DFCD99C2C43FCA2AE0EA5A4B27930DD6</x:v>
       </x:c>
       <x:c r="Q188" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify each controller, power loss/restore, embrasure pathing/combat, row 77, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="45" customHeight="1">
@@ -11004,25 +11004,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K189" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L189" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACE;RR-THREAT;RR-COMPAT;RR-DLC</x:v>
       </x:c>
       <x:c r="M189" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1541438898-Proxyer.RemovableMtRockRoofPatche.md</x:v>
       </x:c>
       <x:c r="N189" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O189" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional roof/map utility with security tradeoffs; no bundled content or dependency.</x:v>
       </x:c>
       <x:c r="P189" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q189" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher roof/impact/infestation claims recorded; license, profile interactions, and save behavior remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="45" customHeight="1">
@@ -11057,25 +11057,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K190" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L190" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M190" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3526354009-Memegoddess.ReplaceStuff.md</x:v>
       </x:c>
       <x:c r="N190" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O190" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional construction utility; selected package license/source not verified; row 278 declares a dependency on it.</x:v>
       </x:c>
       <x:c r="P190" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package snapshot and indexed exact-ID source checked 2026-09-27; Workshop fetch rate-limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q190" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Source limitation and row278 dependency recorded. Selected package behavior/license and exact-profile construction interaction remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="45" customHeight="1">
@@ -11110,25 +11110,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K191" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L191" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-DLC;RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M191" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3503586725-Spuffy.AnimaReplant.md</x:v>
       </x:c>
       <x:c r="N191" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O191" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Royalty-adjacent landscaping; never require Anima Tree access for facility function.</x:v>
       </x:c>
       <x:c r="P191" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package snapshot and continuation/original publisher pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q191" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Continuation behavior and license unresolved; original-mod claim clearly separated. Job/save behavior remains untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="45" customHeight="1">
@@ -11163,25 +11163,25 @@
         <x:v>Medium: the profile changes research presentation or flow. Keep company milestones on a stable separate research chain and avoid replacing the selected research interface blindly.</x:v>
       </x:c>
       <x:c r="K192" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L192" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M192" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3569150345-eheieh.researchtree.md</x:v>
       </x:c>
       <x:c r="N192" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O192" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional research presentation/planning layer; no progression dependency.</x:v>
       </x:c>
       <x:c r="P192" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.2'; local support 1.6; About.xml SHA-256 D8F817E00063EDEF8C5AAF51B821ED25D79646A9CF4FA97D1335831105088FF5</x:v>
       </x:c>
       <x:c r="Q192" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify tree/cache, filters, queues, Anomaly/Gravtech, rows 76/83/279, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="45" customHeight="1">
@@ -11216,25 +11216,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K193" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L193" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M193" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1578234826-BDew.Restraints.md</x:v>
       </x:c>
       <x:c r="N193" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O193" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native restraint tool; never make it the only custody path.</x:v>
       </x:c>
       <x:c r="P193" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 D3C1AD084603C817A51280EA4166F7E5153C0FCE4F23160A61CD64F78B61726C</x:v>
       </x:c>
       <x:c r="Q193" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; resolve 1.6 HugsLib dependency and test pawn types, jobs, mood, and release.</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="45" customHeight="1">
@@ -11269,25 +11269,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K194" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L194" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M194" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3523724230-temmie3754.retend.1.md</x:v>
       </x:c>
       <x:c r="N194" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O194" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional medical-work QoL; no adapter/dependency.</x:v>
       </x:c>
       <x:c r="P194" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 A5E5E96CDD762D319271E060DAF6958E152E9FB1D3BBB979401BCF805FBD0311</x:v>
       </x:c>
       <x:c r="Q194" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; test re-tending, infection/self-tending, quality, medicine use, repeated jobs, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="45" customHeight="1">
@@ -11313,34 +11313,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H195" s="24" t="str">
-        <x:v>Use existing generation, switching, storage, and industrial production to build the headquarters power grid and gate reserve. Backrooms progression should add clear gate-specific operating costs and failure states without replacing the profile's power systems.</x:v>
+        <x:v>Use Rimefeller oil processing, fuel production, power, and industrial recipes as optional company infrastructure and saleable output.</x:v>
       </x:c>
       <x:c r="I195" s="24" t="str">
-        <x:v>Medium: balance and component changes can affect gate uptime. Respect profile choices that suppress vanilla events; add Backrooms-specific pressure only through its own incidents and machine state.</x:v>
+        <x:v>Keep its refinery and production chain native; do not require Rimefeller fuel, power, or research to start the gate.</x:v>
       </x:c>
       <x:c r="J195" s="24" t="str">
-        <x:v>Medium: use as optional power/industry sources; price gate operating cost consistently and do not require one source for basic gate operation.</x:v>
+        <x:v>Check oil/fuel balances, research, incidents, save/load, and interaction with Rimatomics and the selected power systems.</x:v>
       </x:c>
       <x:c r="K195" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L195" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-ECO;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M195" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1321849735-Dubwise.Rimefeller.md</x:v>
       </x:c>
       <x:c r="N195" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O195" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native industry and power; do not require its economy or power for the gate.</x:v>
       </x:c>
       <x:c r="P195" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.2.2061; About SHA-256 AFF16453ACB0B7C21FC229C7FA13BC39DEC8B134A327FAA89659F78B9BC964C8</x:v>
       </x:c>
       <x:c r="Q195" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; reconcile Harmony metadata and verify refinery, power, incidents, saves, and Rimatomics interactions.</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="45" customHeight="1">
@@ -11375,25 +11375,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K196" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L196" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-EVD;RR-ECO;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M196" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2898411376-rimfridge.kv.rw.md</x:v>
       </x:c>
       <x:c r="N196" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O196" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional refrigeration/storage; two-sided access means it is not a custody/security barrier.</x:v>
       </x:c>
       <x:c r="P196" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 2.0.7 and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q196" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Source facts and MIT upstream noted. Deep-storage capacity, factory hopper, and gravship airtightness interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="78" hidden="0" customHeight="1">
@@ -11428,7 +11428,7 @@
         <x:v>Official docs list offline visits/raids and item/pawn exchange. The local activity settings and exact results remain untested; the server does not enforce mod order/settings.</x:v>
       </x:c>
       <x:c r="K197" s="24" t="str">
-        <x:v>Workshop/wiki/release info, local metadata, profile config, and release tree reviewed; two-player compatibility and any client extension remain unconfirmed.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L197" s="28" t="str">
         <x:v>RR-MP;RR-ECO;RR-COMPAT</x:v>
@@ -11481,25 +11481,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K198" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L198" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-DLC;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M198" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2654432921-telardo.RomanceOnTheRim.md</x:v>
       </x:c>
       <x:c r="N198" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O198" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional relationship/need content; MP ID marks branch-ownership check only, not RWT support.</x:v>
       </x:c>
       <x:c r="P198" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1.0 and publisher page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q198" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>No source/license found. Removal, danger/boarding cancellation, DLC rituals, and rows118/119/238/RWT interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="45" customHeight="1">
@@ -11534,25 +11534,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K199" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L199" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M199" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3562365100-MemeGoddess.RunAndGun.md</x:v>
       </x:c>
       <x:c r="N199" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O199" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional move-and-shoot control; Workshop Harmony requirement differs from local metadata and needs verification before pinning.</x:v>
       </x:c>
       <x:c r="P199" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package MemeGoddess.RunAndGun; support 1.0-1.6; About.xml SHA-256 A1020E848EA46A28CAC98523F7B927D105E7AAF3111ABD285BACE0BBE2A43D6F</x:v>
       </x:c>
       <x:c r="Q199" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify dependency, target selection, reported neutral-target behavior, and row80/162 interactions.</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="45" customHeight="1">
@@ -11587,25 +11587,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K200" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L200" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-OUT;RR-MSN;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M200" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3546378186-Mlie.SafelyHiddenAway.md</x:v>
       </x:c>
       <x:c r="N200" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O200" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional world-event pacing; Rimrooms owns outpost threat schedules.</x:v>
       </x:c>
       <x:c r="P200" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.1 and publisher/original/archived-fork sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q200" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Archived upstream MIT does not settle current continuation rights. Remote-site timing, wealth, visitors, and save removal remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="45" customHeight="1">
@@ -11640,25 +11640,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K201" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L201" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-EXP;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M201" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3232242247-MemeGoddess.SearchAndDestroy.md</x:v>
       </x:c>
       <x:c r="N201" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O201" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional combat automation; no authored threat depends on it.</x:v>
       </x:c>
       <x:c r="P201" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop/GitHub source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q201" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher copy restrictions recorded. Targeting, retreat, performance, gravship user report, and RWT remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="45" customHeight="1">
@@ -11693,25 +11693,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K202" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L202" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M202" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2412682633-Mlie.SecretPassageDoors.md</x:v>
       </x:c>
       <x:c r="N202" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O202" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional visual furnishing; concealment is not secure containment.</x:v>
       </x:c>
       <x:c r="P202" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version '1.6.3'; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 9E0A1E4E1AE6394CE4B0D45A2C96D65538A2119379589788F8E49EA4D74FDECD</x:v>
       </x:c>
       <x:c r="Q202" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify hidden-door access, hostile bashing, prisoner/visitor/animal pathing, Giddy-Up, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="45" customHeight="1">
@@ -11731,40 +11731,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3525790312</x:v>
       </x:c>
       <x:c r="F203" s="24" t="str">
-        <x:v>Emergency care and containment response</x:v>
+        <x:v>Odyssey animal-filth setting</x:v>
       </x:c>
       <x:c r="G203" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H203" s="24" t="str">
-        <x:v>Use recovery, fire response, mental-state support, and mechanoid treatment as native emergency procedures for facility incidents and returning crews.</x:v>
+        <x:v>Leave Sentience Catalyst cleanup and alert options to this optional mod; do not treat them as emergency care.</x:v>
       </x:c>
       <x:c r="I203" s="24" t="str">
-        <x:v>Medium: these alter pawn recovery or entity handling. Keep Backrooms exposure and treatment state explicit and do not bypass the installed medicine or recovery rules.</x:v>
+        <x:v>No adapter; keep Rimrooms sanitation and incident tracking independent.</x:v>
       </x:c>
       <x:c r="J203" s="24" t="str">
-        <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
+        <x:v>Odyssey requirement and direct-page access limitation; verify filth/alert behavior in game.</x:v>
       </x:c>
       <x:c r="K203" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L203" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-THREAT;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M203" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3525790312-FlyingSloth.SCFilthReducer.md</x:v>
       </x:c>
       <x:c r="N203" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O203" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Odyssey-specific animal cleanliness setting; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P203" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q203" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact-item indexed publisher text and local metadata recorded with access limitation; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="45" customHeight="1">
@@ -11784,40 +11784,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3374039039</x:v>
       </x:c>
       <x:c r="F204" s="24" t="str">
-        <x:v>World, environment, and evidence</x:v>
+        <x:v>Loading-screen quote utility</x:v>
       </x:c>
       <x:c r="G204" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H204" s="24" t="str">
-        <x:v>Use world and environmental content as sources for coordinates, supply opportunities, clues, and recovery missions. Build the Backrooms generator from deterministic room recipes, not from global random map edits.</x:v>
+        <x:v>Leave loading quotes/tips to the mod; do not use its community quotes as Rimrooms lore or evidence.</x:v>
       </x:c>
       <x:c r="I204" s="24" t="str">
-        <x:v>Medium: map generation and world-site state are multiplayer-sensitive. Confirm map/quest ownership, generation hooks, and event interactions before adding compatibility patches.</x:v>
+        <x:v>No Rimrooms content integration; preserve a normal loading screen if it is absent.</x:v>
       </x:c>
       <x:c r="J204" s="24" t="str">
-        <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
+        <x:v>Row 3 Loading Progress reports are unverified; quote and contribution licenses vary.</x:v>
       </x:c>
       <x:c r="K204" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L204" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M204" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3374039039-Mlie.ShitRimworldSays.md</x:v>
       </x:c>
       <x:c r="N204" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O204" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional loading-screen utility; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P204" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q204" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact publisher page and local metadata reviewed; comment-based interaction remains unverified. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="45" customHeight="1">
@@ -11852,25 +11852,25 @@
         <x:v>Low: avoid overriding hotkeys, scenario controls, or unrelated vanilla tabs.</x:v>
       </x:c>
       <x:c r="K205" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L205" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STYLE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M205" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2475965842-Mlie.ShowMeYourHands.md</x:v>
       </x:c>
       <x:c r="N205" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O205" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: visual-only weapon presentation; no gameplay adapter.</x:v>
       </x:c>
       <x:c r="P205" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.10 and publisher/continued-repo sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q205" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT continuation source noted. Hand/weapon visuals with selected Simple Sidearms/Dual Wield and absent-conflict check remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="45" customHeight="1">
@@ -11905,25 +11905,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K206" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L206" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M206" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/927155256-PeteTimesSix.SimpleSidearms.md</x:v>
       </x:c>
       <x:c r="N206" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O206" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional weapon management; Rimrooms equipment works through standard controls.</x:v>
       </x:c>
       <x:c r="P206" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and available Workshop/repository listing checked 2026-09-27; Steam/forum fetch limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q206" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>License and detailed feature/source scope unresolved. Carry limits, auto-switch, row164/200/204 interactions, and RWT remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="45" customHeight="1">
@@ -11958,25 +11958,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K207" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L207" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M207" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2926945131-NightKosh.SlaveOutfitFix.md</x:v>
       </x:c>
       <x:c r="N207" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O207" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional apparel-layer fix; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P207" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q207" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Retained publisher description and local metadata; source repository unavailable; comments unverified. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="45" customHeight="1">
@@ -12011,25 +12011,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K208" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L208" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M208" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3696700829-Xercaine.Furniture.Small.md</x:v>
       </x:c>
       <x:c r="N208" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O208" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional furniture variants; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P208" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q208" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Indexed publisher text and local metadata recorded with WIP/removal caveats; reports unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="45" customHeight="1">
@@ -12049,40 +12049,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2812513517</x:v>
       </x:c>
       <x:c r="F209" s="24" t="str">
-        <x:v>World, environment, and evidence</x:v>
+        <x:v>Anima-tree and shrine spacing tweak</x:v>
       </x:c>
       <x:c r="G209" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H209" s="24" t="str">
-        <x:v>Use world and environmental content as sources for coordinates, supply opportunities, clues, and recovery missions. Build the Backrooms generator from deterministic room recipes, not from global random map edits.</x:v>
+        <x:v>Treat object radius as optional base-layout behavior; do not use it for Backrooms coordinate or room generation.</x:v>
       </x:c>
       <x:c r="I209" s="24" t="str">
-        <x:v>Medium: map generation and world-site state are multiplayer-sensitive. Confirm map/quest ownership, generation hooks, and event interactions before adding compatibility patches.</x:v>
+        <x:v>No Rimrooms adapter; keep generated rooms independent of Royalty layout edits.</x:v>
       </x:c>
       <x:c r="J209" s="24" t="str">
-        <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
+        <x:v>Publisher DLC wording is unclear; check relevant DLC presence and construction restrictions.</x:v>
       </x:c>
       <x:c r="K209" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L209" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M209" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2812513517-Longman.SmallerRadiusForAnimaTreesAndShrines.md</x:v>
       </x:c>
       <x:c r="N209" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O209" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Royalty-area spacing tweak; no Rimrooms integration.</x:v>
       </x:c>
       <x:c r="P209" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q209" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Indexed publisher description and local metadata recorded; DLC scope unresolved; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="45" customHeight="1">
@@ -12117,25 +12117,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K210" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L210" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M210" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3526251680-Memegoddess.SmartMedicine.md</x:v>
       </x:c>
       <x:c r="N210" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O210" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional medical-care QoL; maintain vanilla care path.</x:v>
       </x:c>
       <x:c r="P210" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 C365FCD3B65CCAA923D6778D078E9D0B5A9671AB119C53949BFA4EAFB3014044</x:v>
       </x:c>
       <x:c r="Q210" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify medicine selection, stock-up, field tending, surgery, prisoner care, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="45" customHeight="1">
@@ -12170,25 +12170,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K211" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L211" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M211" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2800676538-PureMJ.MjRimMods.SmartMeditation.md</x:v>
       </x:c>
       <x:c r="N211" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O211" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional staff-welfare behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P211" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q211" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact-item indexed publisher text and local metadata recorded with access limitation; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="45" customHeight="1">
@@ -12223,25 +12223,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K212" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L212" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M212" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2636621800-denev.SmartTurretCovering.md</x:v>
       </x:c>
       <x:c r="N212" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O212" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional turret cover calculation; do not base security on it.</x:v>
       </x:c>
       <x:c r="P212" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 92F0942F34F8E16AEE32D0E76F813C7AA6ABCA25C1701F5615C2E6A8EBE8D6B1</x:v>
       </x:c>
       <x:c r="Q212" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify turret sizes/angles, optional setting, Rimatomics turrets, and target patches.</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="45" customHeight="1">
@@ -12276,25 +12276,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K213" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L213" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M213" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2202185773-dhultgren.smarterconstruction.md</x:v>
       </x:c>
       <x:c r="N213" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O213" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional construction-job QoL; no direct Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P213" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package snapshot and indexed exact-ID Workshop/upstream repository checked 2026-09-27; direct Workshop fetch rate-limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q213" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher claims and license gap recorded. Selected blueprints/materials and construction behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="45" customHeight="1">
@@ -12329,25 +12329,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K214" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L214" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M214" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3012491521-Mlie.SmarterVisitors.md</x:v>
       </x:c>
       <x:c r="N214" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O214" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional visitor behavior; no RWT company-visit adapter.</x:v>
       </x:c>
       <x:c r="P214" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.2 and upstream source checked 2026-09-27; direct Workshop fetch rate-limited; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q214" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT upstream/source note recorded. Visitor/Hospitality behavior and separate RWT visits remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="45" customHeight="1">
@@ -12382,25 +12382,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K215" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L215" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT;RR-MP</x:v>
       </x:c>
       <x:c r="M215" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1319782555-weilbyte.snapout.md</x:v>
       </x:c>
       <x:c r="N215" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O215" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional mental-break aid; do not make it the required crisis or custody system.</x:v>
       </x:c>
       <x:c r="P215" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/upstream pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q215" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT repository and historical generic multiplayer note recorded. Current gameplay and RWT synchronization remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="45" customHeight="1">
@@ -12435,25 +12435,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K216" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L216" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-COMPAT;RR-MP</x:v>
       </x:c>
       <x:c r="M216" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3400608063-Krelinos.SocialEXPFromTrade.md</x:v>
       </x:c>
       <x:c r="N216" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O216" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional staff-skill progression; no Rimrooms ledger bridge.</x:v>
       </x:c>
       <x:c r="P216" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q216" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT upstream/source note recorded. Skill payout, pricing edge cases, and branch-local RWT behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="45" customHeight="1">
@@ -12473,40 +12473,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=1123043922</x:v>
       </x:c>
       <x:c r="F217" s="24" t="str">
-        <x:v>World, environment, and evidence</x:v>
+        <x:v>Independent technology, trade and event expansion</x:v>
       </x:c>
       <x:c r="G217" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H217" s="24" t="str">
-        <x:v>Use world and environmental content as sources for coordinates, supply opportunities, clues, and recovery missions. Build the Backrooms generator from deterministic room recipes, not from global random map edits.</x:v>
+        <x:v>Keep its Glittertech research, traders, and events separate from the Rimrooms gate and progression.</x:v>
       </x:c>
       <x:c r="I217" s="24" t="str">
-        <x:v>Medium: map generation and world-site state are multiplayer-sensitive. Confirm map/quest ownership, generation hooks, and event interactions before adding compatibility patches.</x:v>
+        <x:v>No integration or shared research dependency; retain the Core-only campaign route.</x:v>
       </x:c>
       <x:c r="J217" s="24" t="str">
-        <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
+        <x:v>Publisher names CE incompatibility; Odyssey/shuttle reports are unverified; full page was not retrievable.</x:v>
       </x:c>
       <x:c r="K217" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L217" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-MSN;RR-ECO;RR-EXP;RR-THREAT;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M217" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1123043922-Albion.SparklingWorlds.Full.md</x:v>
       </x:c>
       <x:c r="N217" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O217" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional expansion content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P217" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q217" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact-ID indexed publisher text and local metadata recorded with fetch limitation; user reports unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="45" customHeight="1">
@@ -12532,34 +12532,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H218" s="24" t="str">
-        <x:v>Use battery efficiency and lightning protection as optional ways to keep the headquarters and gate reserve stable. Preserve the selected profile's own weather and power settings.</x:v>
+        <x:v>Use lightning rods as optional storm protection for facility power infrastructure; do not tie gate progression to lightning events.</x:v>
       </x:c>
       <x:c r="I218" s="24" t="str">
-        <x:v>Low to medium: balance gate reserve costs with battery changes. Lightning and power events must not be assumed when the profile suppresses related events.</x:v>
+        <x:v>Leave its interception and power behavior native; keep gate status and any machine damage in Rimrooms-owned state.</x:v>
       </x:c>
       <x:c r="J218" s="24" t="str">
-        <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
+        <x:v>Test the rod modes, overload/repair behavior, incident settings, and interaction with the selected power mods.</x:v>
       </x:c>
       <x:c r="K218" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L218" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M218" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2358261479-Mlie.SSLightningRod.md</x:v>
       </x:c>
       <x:c r="N218" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O218" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native storm defense; gate progression cannot rely on lightning.</x:v>
       </x:c>
       <x:c r="P218" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml modVersion 1.6.0; About SHA-256 B2A76DDDDEE0654586B268A075FCA99543B383CCDC9A7A55FB4FCC698F4EFC46</x:v>
       </x:c>
       <x:c r="Q218" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify modes, overload, repair, and interaction with selected power mods.</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="45" customHeight="1">
@@ -12594,25 +12594,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K219" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L219" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-GATE;RR-EXP;RR-OUT;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M219" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2831698056-ccyt.stargatesmod.md</x:v>
       </x:c>
       <x:c r="N219" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O219" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: exclude as gameplay dependency/direct integration; high-level mechanics reference only.</x:v>
       </x:c>
       <x:c r="P219" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.3-1.6; Harmony and Vanilla Expanded Framework required; GPL-3.0; About SHA-256 CD5D5E5830FB02209F2A5D7732F77D3922E0CD493030C96770D17AE40BF9D883</x:v>
       </x:c>
       <x:c r="Q219" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; gate/site/cargo/pawn transfer, persistence, combat, save/load, and RWT are not certified.</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="45" customHeight="1">
@@ -12647,25 +12647,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K220" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L220" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M220" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2571676542-Scherub.StonecuttingExtended.md</x:v>
       </x:c>
       <x:c r="N220" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O220" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional material-processing recipes; vanilla stonecutting remains available.</x:v>
       </x:c>
       <x:c r="P220" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.13.0 and publisher/upstream sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q220" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>MIT upstream and row88 interaction lead recorded. Recipe/work/XP behavior in selected profile remains untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="45" customHeight="1">
@@ -12685,40 +12685,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2362707956</x:v>
       </x:c>
       <x:c r="F221" s="24" t="str">
-        <x:v>Emergency care and containment response</x:v>
+        <x:v>Fire-response behavior</x:v>
       </x:c>
       <x:c r="G221" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H221" s="24" t="str">
-        <x:v>Use recovery, fire response, mental-state support, and mechanoid treatment as native emergency procedures for facility incidents and returning crews.</x:v>
+        <x:v>Treat self-extinguishing behavior as optional pawn response, not Rimrooms fire safety.</x:v>
       </x:c>
       <x:c r="I221" s="24" t="str">
-        <x:v>Medium: these alter pawn recovery or entity handling. Keep Backrooms exposure and treatment state explicit and do not bypass the installed medicine or recovery rules.</x:v>
+        <x:v>No adapter; preserve player control and vanilla response if absent.</x:v>
       </x:c>
       <x:c r="J221" s="24" t="str">
-        <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
+        <x:v>Multiplayer desync is a user report only; test determinism if selected for RWT.</x:v>
       </x:c>
       <x:c r="K221" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L221" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M221" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2362707956-balistafreak.StopDropAndRoll.md</x:v>
       </x:c>
       <x:c r="N221" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O221" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional fire-response behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P221" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q221" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher description and local metadata recorded; multiplayer comment unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="45" customHeight="1">
@@ -12753,25 +12753,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K222" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L222" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M222" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2787438435-Mlie.StuffMassMatters.md</x:v>
       </x:c>
       <x:c r="N222" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O222" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional item-mass behavior; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P222" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q222" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="45" customHeight="1">
@@ -12806,25 +12806,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K223" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L223" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M223" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3289533061-moistestWhale.stuffOnTablesForked.md</x:v>
       </x:c>
       <x:c r="N223" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O223" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional decoration/placement feature; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P223" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q223" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; license unresolved; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="45" customHeight="1">
@@ -12859,25 +12859,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K224" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L224" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M224" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3246748490-sov.det.surrogatemech.md</x:v>
       </x:c>
       <x:c r="N224" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O224" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional Biotech automation; no Rimrooms bridge or Core dependency.</x:v>
       </x:c>
       <x:c r="P224" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.5, 1.6; About.xml SHA-256 A349E47519DA5C2A04BD3B45BAE84AA070D1373F98A967DA03C4A6032E1B86C3</x:v>
       </x:c>
       <x:c r="Q224" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify research, Gestator, feeding/play, fire response, rescue jobs, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="45" customHeight="1">
@@ -12912,25 +12912,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K225" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L225" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M225" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3749200746-rabiosus.TakeCover.md</x:v>
       </x:c>
       <x:c r="N225" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O225" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional combat command; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P225" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q225" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; comment disagreement not resolved; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="45" customHeight="1">
@@ -12965,25 +12965,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K226" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L226" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M226" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3476618866-msd.tendyourself.md</x:v>
       </x:c>
       <x:c r="N226" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O226" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional self-tending recovery aid; not guaranteed recovery or secure capture.</x:v>
       </x:c>
       <x:c r="P226" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop page checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q226" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher claims and generic multiplayer statement recorded. Medical behavior and RWT pawn-state handling remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="45" customHeight="1">
@@ -13018,25 +13018,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K227" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L227" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M227" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3221592105-GodlyAnnihilator.TheLowCooler.md</x:v>
       </x:c>
       <x:c r="N227" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O227" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional cooling furniture; selected-package behavior and relation to original remain unresolved.</x:v>
       </x:c>
       <x:c r="P227" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; selected local package metadata and selected/original Workshop pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q227" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Selected-versus-original boundary and rights uncertainty recorded. Exact selected payload and cooling behavior must be verified before reliance.</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="45" customHeight="1">
@@ -13071,25 +13071,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K228" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L228" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-SPACEFLIGHT;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M228" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3523427789-santa.titantreatment.md</x:v>
       </x:c>
       <x:c r="N228" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O228" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Odyssey-gated treatment; no Core crew life-support dependency.</x:v>
       </x:c>
       <x:c r="P228" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q228" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher effects/cost and Odyssey requirement recorded. Surgery/vacuum effects and selected assets rights remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="45" customHeight="1">
@@ -13124,25 +13124,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K229" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L229" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M229" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1499848654-Jaxe.ToggleHarvest.md</x:v>
       </x:c>
       <x:c r="N229" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O229" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional farm/outpost QoL; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P229" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q229" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; reports unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="45" customHeight="1">
@@ -13177,25 +13177,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K230" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L230" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M230" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1506931205-Meow.TradableMeals.md</x:v>
       </x:c>
       <x:c r="N230" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O230" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native cafeteria-surplus sales; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P230" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 4A4DED935A42839D33712B3AFA68D1300AA5358732AABDAAC89950A5C8E236DE</x:v>
       </x:c>
       <x:c r="Q230" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify trade meal coverage with all DLC and the selected food profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="45" customHeight="1">
@@ -13230,25 +13230,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K231" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L231" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-OUT;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M231" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1522257424-Meow.TradableStoneBlocks.md</x:v>
       </x:c>
       <x:c r="N231" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O231" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional trade-list behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P231" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q231" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and author comment reviewed; exact trade behavior untested. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="45" customHeight="1">
@@ -13283,25 +13283,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K232" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L232" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M232" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1969732297-smashphil.dropspot.md</x:v>
       </x:c>
       <x:c r="N232" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O232" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native supply receiving-zone control; no Rimrooms adapter.</x:v>
       </x:c>
       <x:c r="P232" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.0-1.6; no modVersion; About SHA-256 7417CA47F1A508847E2BB81DD1294C3E031F2B165283203C86AF30440B19E1EF</x:v>
       </x:c>
       <x:c r="Q232" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify marker restrictions, quest/orbital cargo, and trade-call cluster.</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="45" customHeight="1">
@@ -13336,25 +13336,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K233" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L233" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M233" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2296557502-WindowsXP.TradeShipsNoMatterWhat.md</x:v>
       </x:c>
       <x:c r="N233" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O233" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: configuration only; do not assume guaranteed trader supply or sales.</x:v>
       </x:c>
       <x:c r="P233" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.2-1.6; no modVersion; About SHA-256 8CA8E17F573297C3E859030C7C05C160652823424D12F38E66693B9B053B77A3</x:v>
       </x:c>
       <x:c r="Q233" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify intervals/types, duplicate calls, drop spots, event cadence, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="45" customHeight="1">
@@ -13389,25 +13389,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K234" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L234" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M234" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1751884355-CarnySenpai.TraitRarityColors.md</x:v>
       </x:c>
       <x:c r="N234" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O234" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional roster/readability aid; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P234" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q234" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page/repository and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="45" customHeight="1">
@@ -13442,25 +13442,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K235" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L235" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M235" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3221646589-archie.turrettargetpatch.md</x:v>
       </x:c>
       <x:c r="N235" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O235" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional predator targeting; preserve only after Animals Logic option test.</x:v>
       </x:c>
       <x:c r="P235" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 61F1F956B913213AB93B721A95A3073EDA128906E610DE7E4B7472AEBBA8C94F</x:v>
       </x:c>
       <x:c r="Q235" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; compare Animals Logic option on/off, visibility, ideology, target patches, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="45" customHeight="1">
@@ -13480,40 +13480,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2921021769</x:v>
       </x:c>
       <x:c r="F236" s="24" t="str">
-        <x:v>Food service and staff welfare</x:v>
+        <x:v>Child education from powered TVs/radios</x:v>
       </x:c>
       <x:c r="G236" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H236" s="24" t="str">
-        <x:v>Use installed food, recreation, and hospitality objects to operate cafeterias, dorms, break rooms, and visitor services. Connect room assignments and supply orders to staff schedules without forcing a new needs system.</x:v>
+        <x:v>Use only as optional Biotech education/recreation; do not classify it as general cafeteria or company welfare support.</x:v>
       </x:c>
       <x:c r="I236" s="24" t="str">
-        <x:v>Low to medium: keep food safety, storage, and recreation rules intact; verify performance with guest and prisoner content active.</x:v>
+        <x:v>No adapter; preserve Core-only staff recreation and education fallback.</x:v>
       </x:c>
       <x:c r="J236" s="24" t="str">
-        <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
+        <x:v>Hard Biotech requirement; pair with rows 236 and 256 only after runtime checks.</x:v>
       </x:c>
       <x:c r="K236" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L236" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M236" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2921021769-Mlie.TVIsEducational.md</x:v>
       </x:c>
       <x:c r="N236" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O236" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Biotech education/recreation feature; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P236" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q236" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; named interactions are test leads only. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="45" customHeight="1">
@@ -13548,25 +13548,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K237" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L237" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M237" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2194535018-Mlie.TVForPrison.md</x:v>
       </x:c>
       <x:c r="N237" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O237" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional/no-touch recreation; no Rimrooms TV or resistance patch planned.</x:v>
       </x:c>
       <x:c r="P237" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.6.0; supports 1.1-1.6; no hard dependency; CC BY-NC-SA and repo MIT indications conflict; About SHA-256 6C88E6582AE7AAECC12D362EE09D1D57E0D3713908D2A7D3309D13B99694CBE0</x:v>
       </x:c>
       <x:c r="Q237" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify mood/resistance/range with prisoner rooms, books, and ideology/thought mods.</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="45" customHeight="1">
@@ -13601,25 +13601,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K238" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source review incomplete; direct publisher-source check pending.</x:v>
       </x:c>
       <x:c r="L238" s="28" t="str">
         <x:v>Pending mapping</x:v>
       </x:c>
       <x:c r="M238" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1542424705-marvinkosh.ughyougotme.md</x:v>
       </x:c>
       <x:c r="N238" s="28" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="O238" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Pending: direct publisher behavior and license not verified; no integration.</x:v>
       </x:c>
       <x:c r="P238" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>Local metadata snapshot dated 2026-09-27; Version blank; local support 1.0–1.6; Harmony required and ordered after Harmony; no runtime check.</x:v>
       </x:c>
       <x:c r="Q238" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Wave 11 exact and English-page retries returned HTTP 429; old publisher site inaccessible and no linked source/license verified. Secondary references insufficient; no runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="45" customHeight="1">
@@ -13654,25 +13654,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K239" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L239" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M239" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2884233923-uglytogether.leeh.md</x:v>
       </x:c>
       <x:c r="N239" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O239" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional social behavior; no Rimrooms recruitment/romance dependency.</x:v>
       </x:c>
       <x:c r="P239" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata plus exact-ID indexed Workshop and source listing checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q239" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Workshop Harmony requirement differs from local About.xml; source license not found. Interactions with rows118/119/197 remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="45" customHeight="1">
@@ -13707,25 +13707,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K240" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L240" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M240" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2157495459-madarauchiha.undraftaftertucking.md</x:v>
       </x:c>
       <x:c r="N240" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O240" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional care-flow QoL; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P240" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q240" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page, source repository and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="45" customHeight="1">
@@ -13760,25 +13760,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K241" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L241" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M241" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2895378449-BlackFranky.UnsterilizeAnimals.md</x:v>
       </x:c>
       <x:c r="N241" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O241" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal breeding feature; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P241" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q241" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="45" customHeight="1">
@@ -13813,25 +13813,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K242" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L242" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M242" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3229291869-dd.useyourgun.md</x:v>
       </x:c>
       <x:c r="N242" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O242" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional combat behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P242" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q242" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; dependency mismatch noted; reports unverified. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="45" customHeight="1">
@@ -13851,40 +13851,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=1814987817</x:v>
       </x:c>
       <x:c r="F243" s="24" t="str">
-        <x:v>Furniture, clothing, and visual content</x:v>
+        <x:v>Apparel and work clothing</x:v>
       </x:c>
       <x:c r="G243" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H243" s="24" t="str">
-        <x:v>Use these items to furnish laboratories, cafeterias, dormitories, security rooms, and company uniforms. Treat mod assets as user-installed content; create original Backrooms assets for any new distributed material.</x:v>
+        <x:v>Use player-installed apparel as optional uniforms/equipment; retain Core gear fallbacks.</x:v>
       </x:c>
       <x:c r="I243" s="24" t="str">
-        <x:v>Low: prefer no code hooks. Check room roles and apparel restrictions only where company roles need them; avoid hard dependencies on optional aesthetics or furniture.</x:v>
+        <x:v>No asset copying or dependency; consume the mod through normal installed content only.</x:v>
       </x:c>
       <x:c r="J243" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>Publisher lists CC BY-NC-ND 4.0; verify VEF/Harmony dependencies and gear behavior.</x:v>
       </x:c>
       <x:c r="K243" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L243" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M243" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1814987817-VanillaExpanded.VAPPE.md</x:v>
       </x:c>
       <x:c r="N243" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O243" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional apparel/equipment content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P243" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q243" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="45" customHeight="1">
@@ -13904,40 +13904,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2521176396</x:v>
       </x:c>
       <x:c r="F244" s="24" t="str">
-        <x:v>Furniture, clothing, and visual content</x:v>
+        <x:v>Apparel accessories and equipment layers</x:v>
       </x:c>
       <x:c r="G244" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H244" s="24" t="str">
-        <x:v>Use these items to furnish laboratories, cafeterias, dormitories, security rooms, and company uniforms. Treat mod assets as user-installed content; create original Backrooms assets for any new distributed material.</x:v>
+        <x:v>Use as an optional accessory layer; no mission or job should require its items.</x:v>
       </x:c>
       <x:c r="I244" s="24" t="str">
-        <x:v>Low: prefer no code hooks. Check room roles and apparel restrictions only where company roles need them; avoid hard dependencies on optional aesthetics or furniture.</x:v>
+        <x:v>No asset copying or dependency; consume installed content through normal item behavior.</x:v>
       </x:c>
       <x:c r="J244" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>Publisher lists CC BY-NC-ND 4.0; check row 160 and VGE equipment layers.</x:v>
       </x:c>
       <x:c r="K244" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L244" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M244" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2521176396-VanillaExpanded.VAEAccessories.md</x:v>
       </x:c>
       <x:c r="N244" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O244" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional accessories; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P244" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q244" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact-item indexed publisher text and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="45" customHeight="1">
@@ -13972,25 +13972,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K245" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L245" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M245" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1814988282-VanillaExpanded.VARME.md</x:v>
       </x:c>
       <x:c r="N245" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O245" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional armor/equipment content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P245" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q245" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="45" customHeight="1">
@@ -14025,25 +14025,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K246" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L246" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M246" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2801452324-PureMJ.MjRimMods.VanillaFixHaulAfterSlaughter.md</x:v>
       </x:c>
       <x:c r="N246" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O246" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal corpse-hauling QoL; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P246" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q246" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact-item indexed publisher text and local metadata recorded; user report unverified. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="45" customHeight="1">
@@ -14078,25 +14078,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K247" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L247" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-OUT;RR-DLC;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M247" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3686924415-VanillaExpanded.VFEFactory.md</x:v>
       </x:c>
       <x:c r="N247" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O247" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional production expansion; CC BY-NC-ND content is not to be bundled or adapted.</x:v>
       </x:c>
       <x:c r="P247" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and publisher/changelog sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q247" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>License, dependency discrepancy, and gravship interaction leads recorded. Production, performance, and cargo behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="78" customHeight="1">
@@ -14131,7 +14131,7 @@
         <x:v>Publisher warns gravship-changing mods may conflict. Test Chapter 2, the selected vehicle/space mods, RWT, and save/load before claiming support.</x:v>
       </x:c>
       <x:c r="K248" s="24" t="str">
-        <x:v>Workshop page/FAQ and local About.xml/LoadFolders.xml reviewed; 1.6, dependencies, incompatibility declaration, and license recorded; runtime pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L248" s="28" t="str">
         <x:v>RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
@@ -14169,40 +14169,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=1888705256</x:v>
       </x:c>
       <x:c r="F249" s="24" t="str">
-        <x:v>Furniture, clothing, and visual content</x:v>
+        <x:v>Pawn hair and appearance</x:v>
       </x:c>
       <x:c r="G249" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H249" s="24" t="str">
-        <x:v>Use these items to furnish laboratories, cafeterias, dormitories, security rooms, and company uniforms. Treat mod assets as user-installed content; create original Backrooms assets for any new distributed material.</x:v>
+        <x:v>Treat as optional appearance editing; do not make recruiting or staff value depend on hairstyle.</x:v>
       </x:c>
       <x:c r="I249" s="24" t="str">
-        <x:v>Low: prefer no code hooks. Check room roles and apparel restrictions only where company roles need them; avoid hard dependencies on optional aesthetics or furniture.</x:v>
+        <x:v>No asset copying or dependency; retain normal appearance if absent.</x:v>
       </x:c>
       <x:c r="J249" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>Publisher lists CC BY-NC-ND 4.0 and requires Harmony; test EdB beard-editor limitations.</x:v>
       </x:c>
       <x:c r="K249" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L249" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-UI;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M249" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1888705256-VanillaExpanded.VHE.md</x:v>
       </x:c>
       <x:c r="N249" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O249" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional appearance layer; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P249" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q249" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; Harmony declaration mismatch noted; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="45" customHeight="1">
@@ -14237,25 +14237,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K250" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L250" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M250" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3014906877-OskarPotocki.VanillaVehiclesExpanded.md</x:v>
       </x:c>
       <x:c r="N250" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O250" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native travel/logistics; no vehicle dependency for gate use or expedition entry.</x:v>
       </x:c>
       <x:c r="P250" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4-1.6; Harmony, Vehicle Framework, VEF required; CC BY-NC-ND 4.0; About SHA-256 53F97862719662845DBA0985903D8F4ED8C597A5BBF44F2EE782AB6995E212B7</x:v>
       </x:c>
       <x:c r="Q250" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify vehicle production, caravans, cargo ownership, map travel, VGE coexistence, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="45" customHeight="1">
@@ -14290,25 +14290,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K251" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L251" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M251" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2454918354-VanillaExpanded.VWENL.md</x:v>
       </x:c>
       <x:c r="N251" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O251" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional nonlethal equipment; retain a Core security/restraint path.</x:v>
       </x:c>
       <x:c r="P251" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 0E485B36FEEED9EE7085CC5DF6CE865F139BB2179CA9C9ED2616AF5D54FCEFDA</x:v>
       </x:c>
       <x:c r="Q251" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify recipes, wounds, incapacitation, targeting, capture, Combat Extended variants, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="45" customHeight="1">
@@ -14343,25 +14343,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K252" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L252" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EVD;RR-MSN;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M252" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2014616487-Mlie.VariousSpaceShipChunk.md</x:v>
       </x:c>
       <x:c r="N252" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O252" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native salvage/event content; no direct integration planned.</x:v>
       </x:c>
       <x:c r="P252" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.6.2; supports 1.0-1.6; Harmony required; MIT license in installed package; About SHA-256 787806915436FAED642024A2DA98FE8AC2C110999A964DABDD90B3368CA08423</x:v>
       </x:c>
       <x:c r="Q252" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; pair with row131 for event content, map generation, cleanup, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="45" customHeight="1">
@@ -14396,25 +14396,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K253" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L253" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M253" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2000708343-SickBoyWi.Vault.OnePointOne.md</x:v>
       </x:c>
       <x:c r="N253" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O253" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional building content; not baseline defense balance or required containment.</x:v>
       </x:c>
       <x:c r="P253" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 B08590227722B1380118C59ECE32A7CDA7E363D29F39556ECAAF0632E16A6EB7</x:v>
       </x:c>
       <x:c r="Q253" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; check damage sources, pathing, openings, encounter counterplay, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="45" customHeight="1">
@@ -14449,25 +14449,25 @@
         <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
       </x:c>
       <x:c r="K254" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L254" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M254" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2511096015-Mlie.WalkableSolarPanels.md</x:v>
       </x:c>
       <x:c r="N254" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O254" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional compact power furniture; not the required gate-power route.</x:v>
       </x:c>
       <x:c r="P254" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.6.0 and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q254" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher output/cost claims recorded. License and power/pathing behavior remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="45" customHeight="1">
@@ -14502,25 +14502,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K255" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L255" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-SPACE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M255" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3286518227-Xercaine.WallHeater.md</x:v>
       </x:c>
       <x:c r="N255" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O255" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional room-temperature furniture; Core climate operation stays independent.</x:v>
       </x:c>
       <x:c r="P255" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q255" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher wall-placement/patch claims recorded. Output and selected cooler patch behavior remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="45" customHeight="1">
@@ -14555,25 +14555,25 @@
         <x:v>Medium to high: inspect world-object, quest, site, and RWT state ownership before adding patches.</x:v>
       </x:c>
       <x:c r="K256" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L256" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M256" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3655704055-Xercaine.WallOrbitalTradeBeacon.md</x:v>
       </x:c>
       <x:c r="N256" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O256" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native orbital-trade building; keep eligibility separate from cargo drop zones.</x:v>
       </x:c>
       <x:c r="P256" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.6; no dependency or modVersion; About SHA-256 A163787ED2135586F8427A7FC4F61083F424B818D351432DE7EC4D5163602968</x:v>
       </x:c>
       <x:c r="Q256" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify indoor/powered beacon radius, sale eligibility, orbital cargo drops, and trader-call cluster.</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="45" customHeight="1">
@@ -14608,25 +14608,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K257" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L257" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M257" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3582096423-Xercaine.WallTelevisions.md</x:v>
       </x:c>
       <x:c r="N257" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O257" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional recreation furniture; never required for staff recovery or campaign progression.</x:v>
       </x:c>
       <x:c r="P257" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q257" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher claims and selected TVForPrison interaction recorded. License, placement, and gravship behavior remain unverified.</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="45" customHeight="1">
@@ -14661,25 +14661,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K258" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L258" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M258" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3655382525-Xercaine.WallVitalsMonitor.md</x:v>
       </x:c>
       <x:c r="N258" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O258" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional compact medical furniture; treatment remains usable without it.</x:v>
       </x:c>
       <x:c r="P258" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q258" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher claims and stacking comment recorded. Exact hospital/IV interaction remains untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="45" customHeight="1">
@@ -14714,25 +14714,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K259" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L259" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-EXP;RR-COMPAT;RR-DLC</x:v>
       </x:c>
       <x:c r="M259" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3032870787-Mersid.WCE2Updated.Core.md</x:v>
       </x:c>
       <x:c r="N259" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O259" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional surgery/custody/experimentation content; no Rimrooms system depends on it.</x:v>
       </x:c>
       <x:c r="P259" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop publisher text checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q259" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Fork ownership/license boundary and Ideology behavior recorded. Surgery, recovery, worldgen and RWT behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="45" customHeight="1">
@@ -14767,25 +14767,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K260" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L260" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-EVD;RR-ECO;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M260" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3519963835-vin.warehouse.storage.md</x:v>
       </x:c>
       <x:c r="N260" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O260" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional ASF storage; do not make it a required Rimrooms path.</x:v>
       </x:c>
       <x:c r="P260" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 0B8E1449BE1A07E90FF86EE46F1523EA3E01E207A664FD7D3E3B6DD270745938</x:v>
       </x:c>
       <x:c r="Q260" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; prioritize gravship rotation/launch, cargo, nearby structures, filters, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="45" customHeight="1">
@@ -14820,25 +14820,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K261" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L261" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M261" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2784585275-PureMJ.MjRimMods.WhileYouAreNearby.md</x:v>
       </x:c>
       <x:c r="N261" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O261" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional work-flow QoL; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P261" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q261" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; user comments unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="45" customHeight="1">
@@ -14873,25 +14873,25 @@
         <x:v>Low to medium: no hard dependency planned. Verify the selected 1.6 behavior before writing a direct compatibility patch.</x:v>
       </x:c>
       <x:c r="K262" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L262" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M262" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3491552121-Tixiv.WhoShotMyLegOff.md</x:v>
       </x:c>
       <x:c r="N262" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O262" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional injury-history UI; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P262" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q262" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher description and local metadata recorded; limitation not independently reproduced. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="45" customHeight="1">
@@ -14911,40 +14911,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3108763487</x:v>
       </x:c>
       <x:c r="F263" s="24" t="str">
-        <x:v>Staff jobs, policies, and social systems</x:v>
+        <x:v>Prisoner conversion and recruitment</x:v>
       </x:c>
       <x:c r="G263" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H263" s="24" t="str">
-        <x:v>Use work priorities, schedules, skills, beliefs, and relationships to express company roles and long-running staff histories. Add company credentials and training records while leaving pawn skills, needs, and existing work assignment tools authoritative.</x:v>
+        <x:v>Treat conversion and recruitment behavior as optional Ideology content; do not make Core hiring depend on it.</x:v>
       </x:c>
       <x:c r="I263" s="24" t="str">
-        <x:v>Low to medium: check work-type ordering, schedules, and social interactions. Do not create a duplicate work tab or overwrite another mod's assignments.</x:v>
+        <x:v>No Rimrooms adapter or dependency; keep the Core-only hiring and custody paths independent.</x:v>
       </x:c>
       <x:c r="J263" s="24" t="str">
-        <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
+        <x:v>English publisher page confirms the Ideology requirement and certainty/resistance rules; local metadata also requires Harmony. Status banners are not runtime evidence and no license was verified.</x:v>
       </x:c>
       <x:c r="K263" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L263" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M263" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3108763487-RedMattis.BetterConversion.md</x:v>
       </x:c>
       <x:c r="N263" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O263" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Ideology conversion/recruitment behavior; no Core-only hiring or custody dependency.</x:v>
       </x:c>
       <x:c r="P263" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local snapshot dated 2026-09-27; Workshop English page directly reviewed.</x:v>
       </x:c>
       <x:c r="Q263" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>English-language publisher page confirms Ideology requirement and conversion/certainty rules; local metadata also requires Harmony. Removal/incompatibility banners noted but not treated as runtime evidence. No license grant or profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="45" customHeight="1">
@@ -14964,40 +14964,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3324430833</x:v>
       </x:c>
       <x:c r="F264" s="24" t="str">
-        <x:v>Medical, biological, and recovery systems</x:v>
+        <x:v>Vehicle passenger sleep and travel</x:v>
       </x:c>
       <x:c r="G264" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H264" s="24" t="str">
-        <x:v>Use installed health, gene, prosthetic, and medical content for staff injuries, exposure treatment, recovery, and optional research. Keep Backrooms exposure and entity biology as separately documented hediffs or evidence so they remain legible across the profile.</x:v>
+        <x:v>Leave sleep/rest behavior to selected vehicle content; keep a normal vehicle-free gate route.</x:v>
       </x:c>
       <x:c r="I264" s="24" t="str">
-        <x:v>Medium: check body-part definitions, treatment selection, gene changes, and synchronization. The core expedition loop must not require one medical or Biotech mod to treat a pawn.</x:v>
+        <x:v>No adapter; Rimrooms expedition and arrival state remain independent.</x:v>
       </x:c>
       <x:c r="J264" s="24" t="str">
-        <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
+        <x:v>Check gunners, rest stops, prisoners/animals and Vehicle Framework version; user reports are unverified.</x:v>
       </x:c>
       <x:c r="K264" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L264" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-SPACEFLIGHT;RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M264" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3324430833-Spacemoth.YouDriveISleep.md</x:v>
       </x:c>
       <x:c r="N264" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O264" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional vehicle travel behavior; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P264" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q264" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; user reports unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="45" customHeight="1">
@@ -15032,25 +15032,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K265" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L265" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-OUT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M265" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2436086611-Mlie.ZoneToSchedule.md</x:v>
       </x:c>
       <x:c r="N265" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O265" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional area/schedule convenience; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P265" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q265" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="45" customHeight="1">
@@ -15085,25 +15085,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K266" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L266" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-SPACEFLIGHT;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M266" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3534740420-Endy.Airtightgarage.md</x:v>
       </x:c>
       <x:c r="N266" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O266" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional Odyssey/VVE gravship utility; not a Core requirement.</x:v>
       </x:c>
       <x:c r="P266" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.6; About.xml SHA-256 B0CB577BBA31139323337745104048A80726427C53050E1637D096E3550225D8</x:v>
       </x:c>
       <x:c r="Q266" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify airtight behavior, logs, save/load, and row 185 in the exact gravship profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="45" customHeight="1">
@@ -15138,25 +15138,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K267" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L267" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M267" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3177395100-sarg.alphavehiclesageofsail.md</x:v>
       </x:c>
       <x:c r="N267" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O267" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional Vehicle Framework ship content; no sea-travel prerequisite.</x:v>
       </x:c>
       <x:c r="P267" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.6, 1.5; About.xml SHA-256 26A07EC102B3814BED703E46F89146BFC082A01B03CD556D6DD2FC4F5CE582B1</x:v>
       </x:c>
       <x:c r="Q267" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify local load order, research/build, water travel, cargo, DLC-off, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="45" customHeight="1">
@@ -15191,25 +15191,25 @@
         <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
       </x:c>
       <x:c r="K268" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L268" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EXP;RR-OUT;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M268" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3513849448-Ingendum.AnimalArmorBasic.md</x:v>
       </x:c>
       <x:c r="N268" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O268" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional animal equipment; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P268" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q268" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="45" customHeight="1">
@@ -15229,40 +15229,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2068281501</x:v>
       </x:c>
       <x:c r="F269" s="24" t="str">
-        <x:v>Furniture, clothing, and visual content</x:v>
+        <x:v>Pawn appearance textures</x:v>
       </x:c>
       <x:c r="G269" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H269" s="24" t="str">
-        <x:v>Use these items to furnish laboratories, cafeterias, dormitories, security rooms, and company uniforms. Treat mod assets as user-installed content; create original Backrooms assets for any new distributed material.</x:v>
+        <x:v>Treat as optional appearance content; staff value, hiring and gameplay state must not depend on body texture.</x:v>
       </x:c>
       <x:c r="I269" s="24" t="str">
-        <x:v>Low: prefer no code hooks. Check room roles and apparel restrictions only where company roles need them; avoid hard dependencies on optional aesthetics or furniture.</x:v>
+        <x:v>No adapter. Reuse only the publisher-permitted textures with credit after confirming the exact files; no code permission is implied.</x:v>
       </x:c>
       <x:c r="J269" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>Publisher says the textures are designed for vanilla clothing and permits reuse with credit. Removed-item notice is not a runtime finding; combined texture order is untested.</x:v>
       </x:c>
       <x:c r="K269" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L269" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M269" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2068281501-mireia.bodies.md</x:v>
       </x:c>
       <x:c r="N269" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O269" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional pawn-appearance content; publisher permits reuse of its textures with credit, but no gameplay dependency.</x:v>
       </x:c>
       <x:c r="P269" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata snapshot dated 2026-09-27; publisher Steam Workshop description reviewed.</x:v>
       </x:c>
       <x:c r="Q269" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher describes body-texture replacement, vanilla-clothing intent, and reuse of those textures with credit. No code/license grant or runtime/profile compatibility test; removed-page notice is not a runtime finding.</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="45" customHeight="1">
@@ -15297,25 +15297,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K270" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L270" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-ECO;RR-COMPAT;RR-MP</x:v>
       </x:c>
       <x:c r="M270" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3509488152-Orion.Gastronomy.md</x:v>
       </x:c>
       <x:c r="N270" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O270" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional cafeteria layer; no direct Rimrooms ledger adapter; continuation license remains unresolved.</x:v>
       </x:c>
       <x:c r="P270" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package 1.0.4 and publisher/repository sources checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q270" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Conflicting license statements preserved. Register, Hospitality, Animal Controls, custody, and RWT interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="45" customHeight="1">
@@ -15350,25 +15350,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K271" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L271" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-STA;RR-ECO;RR-MSN;RR-OUT;RR-SPACEFLIGHT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M271" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3509486825-Orion.Hospitality.md</x:v>
       </x:c>
       <x:c r="N271" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O271" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native guest economy; not a cross-company visit system or shared campaign dependency.</x:v>
       </x:c>
       <x:c r="P271" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.1.4; supports 1.5-1.6; Harmony required; code GPL-3.0 and art CC BY-SA 4.0; About SHA-256 DDE45358A4AE0E95669B07DA75F1B5C67E849ADE0C6D3694F4062634F6BBC6F7</x:v>
       </x:c>
       <x:c r="Q271" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Invite to Stay, Cash Register/Storefront, Real Faction Guest, RWT visits, and gravship transfer.</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="45" customHeight="1">
@@ -15388,40 +15388,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3203280763</x:v>
       </x:c>
       <x:c r="F272" s="24" t="str">
-        <x:v>Furniture, clothing, and visual content</x:v>
+        <x:v>Jewelry, gems and Royalty clothing demands</x:v>
       </x:c>
       <x:c r="G272" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H272" s="24" t="str">
-        <x:v>Use these items to furnish laboratories, cafeterias, dormitories, security rooms, and company uniforms. Treat mod assets as user-installed content; create original Backrooms assets for any new distributed material.</x:v>
+        <x:v>Treat jewelry as optional craft/trade/staff content; company currency and progression stay independent.</x:v>
       </x:c>
       <x:c r="I272" s="24" t="str">
-        <x:v>Low: prefer no code hooks. Check room roles and apparel restrictions only where company roles need them; avoid hard dependencies on optional aesthetics or furniture.</x:v>
+        <x:v>No asset copying or dependency; use installed items and native recipes only.</x:v>
       </x:c>
       <x:c r="J272" s="24" t="str">
-        <x:v>Low to medium: no hard dependency planned; confirm the native content works on expedition maps and stays transferable.</x:v>
+        <x:v>Workshop displays CC BY-NC-SA 4.0; test Gemstones and royalty demands; duplicate-Ruby report is unverified.</x:v>
       </x:c>
       <x:c r="K272" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L272" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-STA;RR-FAC;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M272" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3203280763-kikohi.jewelry.md</x:v>
       </x:c>
       <x:c r="N272" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O272" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional crafting/economy content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P272" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q272" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; reported duplicate item is unverified; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="45" customHeight="1">
@@ -15456,25 +15456,25 @@
         <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
       </x:c>
       <x:c r="K273" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L273" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-FAC;RR-EXP;RR-COMPAT;RR-SPACEFLIGHT</x:v>
       </x:c>
       <x:c r="M273" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2937012139-Troopersmith1.LifeSupport.md</x:v>
       </x:c>
       <x:c r="N273" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O273" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional medical organ-support feature; not environmental air or general gate life support.</x:v>
       </x:c>
       <x:c r="P273" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and updated Workshop/linked source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q273" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Selected 1.6 fork/license correspondence remains unresolved. Bed/gravship and RWT pawn behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="45" customHeight="1">
@@ -15509,25 +15509,25 @@
         <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
       </x:c>
       <x:c r="K274" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L274" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-THREAT;RR-STA;RR-COMPAT;RR-MP</x:v>
       </x:c>
       <x:c r="M274" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1157085076-avius.locks.md</x:v>
       </x:c>
       <x:c r="N274" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O274" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional access-control complement; no Rimrooms security outcome depends on it.</x:v>
       </x:c>
       <x:c r="P274" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop/GitHub pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q274" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Version mismatch and license/source status recorded. Door, custody, save-removal, and RWT interactions remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="45" customHeight="1">
@@ -15562,25 +15562,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K275" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L275" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-EVD;RR-THREAT;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M275" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1328216966-Heremeus.MedicalDissection.md</x:v>
       </x:c>
       <x:c r="N275" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O275" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: solo-only optional recommended; RWT co-op scope awaits owner input.</x:v>
       </x:c>
       <x:c r="P275" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 2462E577F12FC4ED84B1CEC0118A258883194A5468C74143302B571F5A4F427E</x:v>
       </x:c>
       <x:c r="Q275" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher multiplayer/desync warning; no RWT test run. Owner scope requested 2026-09-27; keep outside RWT support claim pending answer and evidence.</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="45" customHeight="1">
@@ -15615,25 +15615,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K276" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L276" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-THREAT;RR-STA;RR-MSN;RR-COMPAT;RR-MP</x:v>
       </x:c>
       <x:c r="M276" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3455926746-Smxrez.nonlethalreexamined.md</x:v>
       </x:c>
       <x:c r="N276" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O276" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional non-lethal weapon/custody aid; do not promise guaranteed stuns or capture.</x:v>
       </x:c>
       <x:c r="P276" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata and Workshop source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q276" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Explicit Combat Extended incompatibility and exact add-on rights gap recorded. Weapon, custody, and RWT behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="45" customHeight="1">
@@ -15668,25 +15668,25 @@
         <x:v>Medium: reconcile gate reserves and running costs with this mod's power rules; don't assume disabled vanilla events.</x:v>
       </x:c>
       <x:c r="K277" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L277" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M277" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3339142899-gy.ppextend.md</x:v>
       </x:c>
       <x:c r="N277" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O277" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional pole variant/visual add-on; not a new power system.</x:v>
       </x:c>
       <x:c r="P277" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 ABD36B959D4E02F938EDE9A1DCFD105A1DAFCBD1BE10C9684FA780F61710CE4D</x:v>
       </x:c>
       <x:c r="Q277" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify base row 167, power/lighting, optional Fortification patches, order, logs, and save/load.</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="45" customHeight="1">
@@ -15721,25 +15721,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K278" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L278" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-OUT;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M278" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3500482839-Rebuild.Embrasures.md</x:v>
       </x:c>
       <x:c r="N278" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O278" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional fortification content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P278" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q278" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; implementation and user reports unverified. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="45" customHeight="1">
@@ -15759,40 +15759,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3093303048</x:v>
       </x:c>
       <x:c r="F279" s="24" t="str">
-        <x:v>Facilities and spatial construction</x:v>
+        <x:v>Unverified package scope — title only</x:v>
       </x:c>
       <x:c r="G279" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H279" s="24" t="str">
-        <x:v>Use the construction and layout tools to create gate control, labs, secure storage, accommodation, service corridors, and outposts. Build Backrooms maps from its own reusable room templates and coordinate seeds.</x:v>
+        <x:v>Do not plan a feature integration from the title or local load-order metadata alone.</x:v>
       </x:c>
       <x:c r="I279" s="24" t="str">
-        <x:v>Medium: construction, door, terrain, and map-size changes can alter room validation or pathfinding. Keep generated room validation independent and test blueprints after updates.</x:v>
+        <x:v>No integration decision until publisher feature scope and license are accessible.</x:v>
       </x:c>
       <x:c r="J279" s="24" t="str">
-        <x:v>Medium: test pathing, room reachability, doors, and map generation with the profile's construction tools.</x:v>
+        <x:v>Publisher page retries were rate-limited. Local metadata declares hard dependencies on Harmony and Replace Stuff Continued, and a LoadAfter target for Replace Stuff Compatibility; that target is not declared as a hard dependency.</x:v>
       </x:c>
       <x:c r="K279" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source review incomplete; direct publisher-source check pending.</x:v>
       </x:c>
       <x:c r="L279" s="28" t="str">
         <x:v>Pending mapping</x:v>
       </x:c>
       <x:c r="M279" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3093303048-Deadmano.ReplaceStuffCoolerVentPlacementFix.md</x:v>
       </x:c>
       <x:c r="N279" s="28" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="O279" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Pending: no verified feature description or license; no integration.</x:v>
       </x:c>
       <x:c r="P279" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>Local metadata snapshot dated 2026-09-27; v1.6.0; support 1.4–1.6; hard deps Harmony and Replace Stuff Continued (Memegoddess.ReplaceStuff); after Garethp.ReplaceStuffCompatibility, absent.</x:v>
       </x:c>
       <x:c r="Q279" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Exact page and alternate URL returned HTTP 429; no publisher text, linked repository, or license verified. Local metadata only; no runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="45" customHeight="1">
@@ -15827,25 +15827,25 @@
         <x:v>Medium: the profile changes research presentation or flow. Keep company milestones on a stable separate research chain and avoid replacing the selected research interface blindly.</x:v>
       </x:c>
       <x:c r="K280" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L280" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-GATE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M280" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2552092060-avilmask.ResearchWhatever.md</x:v>
       </x:c>
       <x:c r="N280" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O280" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional automatic research selection; never take over critical gate research.</x:v>
       </x:c>
       <x:c r="P280" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 089DAA121D5800B083439E5253BCED46626B76BFB32556601FA2F82A44A0C03F</x:v>
       </x:c>
       <x:c r="Q280" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify manual/automatic priorities, Anomaly resume, Gravtech, row 191/76, Rimatomics, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="45" customHeight="1">
@@ -15865,40 +15865,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=2848956469</x:v>
       </x:c>
       <x:c r="F281" s="24" t="str">
-        <x:v>Research and staff development</x:v>
+        <x:v>Misc. Training texture companion</x:v>
       </x:c>
       <x:c r="G281" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H281" s="24" t="str">
-        <x:v>Use the mod's native research or skill workflow as part of the company lab and training plan. The Backrooms tree should own gate, mapping, containment, and spatial-analysis milestones and should not overwrite other research trees.</x:v>
+        <x:v>Treat as optional visual content; retain vanilla training and Rimrooms training routes without it.</x:v>
       </x:c>
       <x:c r="I281" s="24" t="str">
-        <x:v>Medium: check research tab replacements, prerequisite edits, and project speed changes. Backrooms milestones need stable definitions and an independent route when optional trees are absent.</x:v>
+        <x:v>No adapter or gameplay dependency; do not reuse assets while no reuse grant is recorded.</x:v>
       </x:c>
       <x:c r="J281" s="24" t="str">
-        <x:v>Medium: preserve native research progression and add Backrooms milestones as a separate, optional chain.</x:v>
+        <x:v>Publisher describes replacement sprites for Misc. Training and identifies its three target definitions in an author comment; no reuse terms or combined runtime result verified.</x:v>
       </x:c>
       <x:c r="K281" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L281" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M281" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2848956469-SirVan.MiscTrainingRetexture.md</x:v>
       </x:c>
       <x:c r="N281" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O281" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional visual companion to Misc. Training; not a training-mechanics provider or required Rimrooms feature.</x:v>
       </x:c>
       <x:c r="P281" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local metadata snapshot dated 2026-09-27; publisher Steam Workshop description and author comment reviewed.</x:v>
       </x:c>
       <x:c r="Q281" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher describes replacement sprites for Misc. Training and says a reported missing-target patch error indicates the original mod is needed; local order is recorded. No reuse terms or runtime/profile compatibility test; page notices are not runtime findings.</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="78" customHeight="1">
@@ -15933,7 +15933,7 @@
         <x:v>Publisher warns other gravship-changing mods may conflict. Test Chapter 1, selected vehicle/space mods, RWT, and save/load; local declared incompatibility target is outside profile.</x:v>
       </x:c>
       <x:c r="K282" s="24" t="str">
-        <x:v>Workshop page/FAQ and local About.xml/LoadFolders.xml reviewed; 1.6, dependencies, incompatibility declaration, and license recorded; runtime pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L282" s="28" t="str">
         <x:v>RR-OUT;RR-SPACEFLIGHT;RR-THREAT;RR-COMPAT</x:v>
@@ -15986,25 +15986,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K283" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L283" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-MSN;RR-OUT;RR-SPACEFLIGHT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M283" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3047892432-OskarPotocki.VanillaVehiclesExpandedTier3.md</x:v>
       </x:c>
       <x:c r="N283" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O283" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native late vehicle recovery; no Rimrooms vehicle definitions.</x:v>
       </x:c>
       <x:c r="P283" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.4-1.6; Harmony, Vehicle Framework, base VVE required; CC BY-NC-ND 4.0; About SHA-256 DA480FE4FD4DD939160B34E59DC19EF35FE303D1B9FFC4AA7BC0544313E65EAB</x:v>
       </x:c>
       <x:c r="Q283" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify vehicle wreck spawn/repair, research, map scope, RWT, and no unsupported Tier 3 upgrades.</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="45" customHeight="1">
@@ -16039,25 +16039,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K284" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L284" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-ECO;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M284" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3302208420-OskarPotocki.VanillaVehiclesExpandedUpgrades.md</x:v>
       </x:c>
       <x:c r="N284" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O284" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native vehicle progression; preserve its upgrade system and costs.</x:v>
       </x:c>
       <x:c r="P284" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.5-1.6; Harmony, Vehicle Framework, VVE required; CC BY-NC-ND 4.0; About SHA-256 DA8B6DB24CF957982923207BFE798517BB452836A41B220B554CCEE2FF9916B8</x:v>
       </x:c>
       <x:c r="Q284" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify upgrade work, costs, cargo, save/load, RWT, and Tier 3 exclusion.</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="45" customHeight="1">
@@ -16092,25 +16092,25 @@
         <x:v>High: verify patch order and source mods covered before adding any Backrooms patch.</x:v>
       </x:c>
       <x:c r="K285" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L285" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M285" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2893432492-FrozenSnowFox.FrozenSnowFoxTweaks.md</x:v>
       </x:c>
       <x:c r="N285" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O285" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional configurable tweaks; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P285" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q285" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata recorded; disabled-by-default is a publisher claim; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="45" customHeight="1">
@@ -16145,25 +16145,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K286" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L286" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-ECO;RR-MSN;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M286" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3783522506-gatoviejo.hospitality.invitetostay.md</x:v>
       </x:c>
       <x:c r="N286" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O286" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Hospitality extension; no Rimrooms integration; publisher page/license needs primary-source check.</x:v>
       </x:c>
       <x:c r="P286" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.1.0; Harmony and Orion.Hospitality required; local supports 1.6; About SHA-256 C8071C9C9BC22995074DC8149BAA891E372A86507DE93C60C9165EF28008C98B</x:v>
       </x:c>
       <x:c r="Q286" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify publisher page, invite/price behavior, Real Faction Guest, and RWT/gravship persistence.</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="45" customHeight="1">
@@ -16198,25 +16198,25 @@
         <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
       </x:c>
       <x:c r="K287" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L287" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-SCEN;RR-ECO;RR-STA;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M287" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2952321484-Adamas.Storefront.md</x:v>
       </x:c>
       <x:c r="N287" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O287" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional shop scenario flavor; not required for Rimrooms economy/selling loop.</x:v>
       </x:c>
       <x:c r="P287" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.4, 1.5, 1.6; About.xml SHA-256 4C568C1AB193952550FD88CCE99F645D0653C13505B6D073DC24D51480D25718</x:v>
       </x:c>
       <x:c r="Q287" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify storefront modes, customer accounting, prices, sales, Hospitality/caravan customers, and RWT separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="45" customHeight="1">
@@ -16251,25 +16251,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K288" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L288" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-STA;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M288" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3358620558-AgentBlac.MakePawnsPrisoners.md</x:v>
       </x:c>
       <x:c r="N288" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O288" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional bedless capture route; no required Rimrooms custody path.</x:v>
       </x:c>
       <x:c r="P288" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.3-1.6; Harmony required; loads after Locks; CC BY-NC-SA 4.0; About SHA-256 00EF1B884B5B6B978C6E4E19F6AD4EFA0FF4CB97FED5A86F076FC8F2452267A7</x:v>
       </x:c>
       <x:c r="Q288" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify capture, tend/feed, recovery, restraints, doors, turret safety, and map transfer.</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="78" customHeight="1">
@@ -16304,7 +16304,7 @@
         <x:v>Missing 1.6/Biotech conditional path; prisoner UI/work assignments may conflict with other prisoner and UI mods. Exact interaction and RWT transfer untested.</x:v>
       </x:c>
       <x:c r="K289" s="24" t="str">
-        <x:v>Workshop page, 1.6 upstream tree, About.xml, and LoadFolders.xml reviewed; runtime pending.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L289" s="28" t="str">
         <x:v>RR-STA;RR-EVD;RR-COMPAT</x:v>
@@ -16342,40 +16342,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=1724270693</x:v>
       </x:c>
       <x:c r="F290" s="24" t="str">
-        <x:v>Medical, biological, and recovery systems</x:v>
+        <x:v>Ivory material and crafting — fork source pending</x:v>
       </x:c>
       <x:c r="G290" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H290" s="24" t="str">
-        <x:v>Use installed health, gene, prosthetic, and medical content for staff injuries, exposure treatment, recovery, and optional research. Keep Backrooms exposure and entity biology as separately documented hediffs or evidence so they remain legible across the profile.</x:v>
+        <x:v>Treat ivory as optional material content, never as required Rimrooms currency.</x:v>
       </x:c>
       <x:c r="I290" s="24" t="str">
-        <x:v>Medium: check body-part definitions, treatment selection, gene changes, and synchronization. The core expedition loop must not require one medical or Biotech mod to treat a pawn.</x:v>
+        <x:v>No integration until the selected local fork provenance and license are established.</x:v>
       </x:c>
       <x:c r="J290" s="24" t="str">
-        <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
+        <x:v>Workshop publisher differs from selected fork; do not carry original-page claims across packages.</x:v>
       </x:c>
       <x:c r="K290" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L290" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-ECO;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M290" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/1724270693-LegendaryMinuteman.SimpleIvory.fork.md</x:v>
       </x:c>
       <x:c r="N290" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O290" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional resource content; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P290" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q290" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local fork metadata kept distinct; selected-fork provenance/license unresolved; no runtime test. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="45" customHeight="1">
@@ -16410,25 +16410,25 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K291" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L291" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EVD;RR-MSN;RR-OUT;RR-EXP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M291" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3299034372-Explorern11.VehiclesWrecksExpanded.md</x:v>
       </x:c>
       <x:c r="N291" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O291" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional native vehicle-wreck salvage; do not add custom wrecks without bounded spawn tests.</x:v>
       </x:c>
       <x:c r="P291" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.5-1.6; Vehicle Framework, VVE, and VVE Tier 3 required; About SHA-256 A9D5AE973543FF571C3F634D09E9E5B3BC4BFBF7CFDF5E14A08E123384BEBFA7</x:v>
       </x:c>
       <x:c r="Q291" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify patch logs, wreck spawn scope/density, repair, and optional no-natural-spawn behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="45" customHeight="1">
@@ -16463,25 +16463,25 @@
         <x:v>Medium: check targeting, drafted orders, downing, and threat counterplay; preserve player control of irreversible combat choices.</x:v>
       </x:c>
       <x:c r="K292" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L292" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-THREAT;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M292" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3459650108-tgbm.vve.secondary.weapons.md</x:v>
       </x:c>
       <x:c r="N292" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O292" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Optional VVE vehicle combat content; no Rimrooms adapter or bundled content.</x:v>
       </x:c>
       <x:c r="P292" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 'Release 3.2.2'; local support 1.5, 1.6; About.xml SHA-256 8EBD6E996FC3DBAE0ED5E0453E4A4581BAE739AC3AA130C36FB3B80A86FF5712</x:v>
       </x:c>
       <x:c r="Q292" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; resolve Vehicle Framework dependency difference and test loadouts/ammo/upgrades, saves, cargo, and RWT.</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="45" customHeight="1">
@@ -16516,25 +16516,25 @@
         <x:v>Medium to high: several prisoner/capture/custody systems are active. Validate custody, transfer, case data, and interaction overlap with every selected mod.</x:v>
       </x:c>
       <x:c r="K293" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L293" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-THREAT;RR-ECO;RR-MP;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M293" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2841231775-Mlie.CustomPrisonerInteractions.md</x:v>
       </x:c>
       <x:c r="N293" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O293" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional/no override; preserve prisoner ownership and saved action state.</x:v>
       </x:c>
       <x:c r="P293" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local version 1.6.2; supports 1.3-1.6; Harmony required; MIT repo; About SHA-256 5E05F1D4523914EC5A9AD78EC1C2883246B6FD8468416A6193350F6DD4F3E4A1</x:v>
       </x:c>
       <x:c r="Q293" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify Prison Labor saved modes, travel/map transfer, recruitment alert, ransom, and QEE interactions.</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="45" customHeight="1">
@@ -16569,25 +16569,25 @@
         <x:v>Medium: check overlap with ancient-site and wreck patches; prevent duplicate salvage and loot.</x:v>
       </x:c>
       <x:c r="K294" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L294" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-EXP;RR-OUT;RR-ECO;RR-SPACE;RR-DLC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M294" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/2871064871-proxyer.dismantleancientjunk.md</x:v>
       </x:c>
       <x:c r="N294" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O294" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional Ideology salvage feature; no Rimrooms dependency.</x:v>
       </x:c>
       <x:c r="P294" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package metadata snapshot dated 2026-09-27; package-specific facts in linked note.</x:v>
       </x:c>
       <x:c r="Q294" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Publisher page and local metadata facts recorded; no combined behavior tested. No runtime/profile compatibility test.</x:v>
       </x:c>
     </x:row>
     <x:row r="295" ht="45" customHeight="1">
@@ -16622,31 +16622,31 @@
         <x:v>Medium: verify stack, weight, ownership, caravan, and RWT transfer behavior for mission cargo.</x:v>
       </x:c>
       <x:c r="K295" s="24" t="str">
-        <x:v>Local name/ID record reviewed and mapped to a design family; exact Workshop page, dependency, source behavior, and compatibility remain pending unless separately cited.</x:v>
+        <x:v>Source facts recorded; runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L295" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STYLE;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M295" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>docs/research/reviews/mods/3348827283-VehiclesWrecksExpanded.Revisited.md</x:v>
       </x:c>
       <x:c r="N295" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O295" s="28" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Provisional: optional appearance-only support; do not bundle its textures.</x:v>
       </x:c>
       <x:c r="P295" s="28" t="str">
-        <x:v>Not pinned</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local About.xml supports 1.5-1.6; Vehicles Wrecks Expanded required; no license found; About SHA-256 59B45A39559C85824356760944F3FF2CD0E14B0A9682CF6901CC5D36F7F518BE</x:v>
       </x:c>
       <x:c r="Q295" s="28" t="str">
-        <x:v>Not runtime tested</x:v>
+        <x:v>Not runtime tested; verify texture precedence/readability and mechanics without this texture package.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ccbdd73add84f3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25c823537174157"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R4d15b45f42b84f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="Rc4587ff3a2054ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R92966c98affc4df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R0908af074b97493a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -481,7 +481,7 @@
         <x:v>Register evidence level</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>291 of 294 rows have accepted source-fact records; 3 remain pending. Partial source notes: rows 96, 237, and 278. No combined-profile compatibility is established by source review.</x:v>
+        <x:v>All 294 of 294 rows have accepted source-fact records with known limits recorded; no combined-profile runtime clearance has been established.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -505,7 +505,7 @@
         <x:v>Current RWT boundary</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>Local client/server IDs and order match, but the server does not enforce them. The server release and client artifact are pinned; separate starts, offline visits, supply/aid transfer, and reconnect checks remain pending.</x:v>
+        <x:v>Local client/server IDs and order match. The RWT 26.8.31.1 server archive matches the official release digest; the client artifact is pinned separately by hash. Server settings do not enforce the profile. Visits, custom cargo, differing scenarios, and reconnect behavior remain untested.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4020,7 +4020,7 @@
         <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O57" s="28" t="str">
-        <x:v>Provisional: optional profile QoL; no Rimrooms feature requires this mod. Keep native behavior untouched; 1.6 full-profile check pending.</x:v>
+        <x:v>Optional profile entry; preserve native milkable-animal behavior; no Rimrooms feature depends on it. Do not claim 1.6 compatibility from the local About.xml, which omits 1.6.</x:v>
       </x:c>
       <x:c r="P57" s="28" t="str">
         <x:v>RimWorld 1.6.4871 rev590; local About.xml omits 1.6; no modVersion; About.xml SHA256 2979A22559220FACF843F4E0600488958D1DC94CC8F6CE7B0329985E9E3B865E</x:v>
@@ -6119,16 +6119,16 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H97" s="24" t="str">
-        <x:v>Use fueled cremation as an optional company procedure for dangerous remains, contaminated waste, and post-incident cleanup; leave disposition to player policy.</x:v>
+        <x:v>Optional company procedure for ordinary remains and facility waste. Preserve Rimrooms evidence custody, sample analysis, and case disposition before any destruction.</x:v>
       </x:c>
       <x:c r="I97" s="24" t="str">
-        <x:v>Low to medium: verify corpse, prisoner, and evidence custody rules before offering a custom cleanup job.</x:v>
+        <x:v>No direct Rimrooms adapter or patch. Retain native cremation bills and recipes where present; use this as an optional facility example only.</x:v>
       </x:c>
       <x:c r="J97" s="24" t="str">
-        <x:v>Medium: check pawn health/custody state, treatment choice, and transfer; preserve a vanilla fallback.</x:v>
+        <x:v>Publisher lists RimWorld 1.5/1.6 and optional patches for Rim of Madness – Bones and Ashes. These are patch targets, not required dependencies. Check fuel, bills, corpse contents, destruction, and row 152 interactions before runtime claims.</x:v>
       </x:c>
       <x:c r="K97" s="24" t="str">
-        <x:v>Source review incomplete; direct publisher-source check pending.</x:v>
+        <x:v>Publisher and local source facts recorded; Rimrooms runtime compatibility pending.</x:v>
       </x:c>
       <x:c r="L97" s="28" t="str">
         <x:v>RR-FAC;RR-EVD;RR-THREAT;RR-COMPAT</x:v>
@@ -6137,16 +6137,16 @@
         <x:v>docs/research/reviews/mods/3286907608-Xercaine.FueledCrematorium.md</x:v>
       </x:c>
       <x:c r="N97" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O97" s="28" t="str">
-        <x:v>Pending primary-source review; provisional optional disposal furniture, never an evidence workflow.</x:v>
+        <x:v>Optional; no direct integration. Preserve evidence custody before destruction; profile and RWT coexistence are not runtime-verified.</x:v>
       </x:c>
       <x:c r="P97" s="28" t="str">
-        <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.5, 1.6; About.xml SHA-256 3E2AF3B20B59F94757902F691179A88D94B23CC7961CA4EC62549D2CA010E87E</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; local package Xercaine.FueledCrematorium; supports 1.5/1.6; no local modVersion; About.xml SHA-256 3E2AF3B20B59F94757902F691179A88D94B23CC7961CA4EC62549D2CA010E87E</x:v>
       </x:c>
       <x:c r="Q97" s="28" t="str">
-        <x:v>Wave 11 exact and English-page retries still rate-limited; no publisher-linked source/license verified. Existing indexed description remains unconfirmed; no runtime test.</x:v>
+        <x:v>Publisher page via alternate exact-ID route and author comments checked 2026-09-27; local 1.6 XML checked. No source repository/license found. Steam removal/generic incompatibility banners are page state, not runtime findings. No runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="45" customHeight="1">
@@ -10698,13 +10698,13 @@
         <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O183" s="28" t="str">
-        <x:v>Provisional: solo-only optional pending Gate 0 choice; publisher says multiplayer will not work properly.</x:v>
+        <x:v>Optional; include in the owner-selected RWT candidate test profile despite the publisher multiplayer warning; do not advertise co-op support before exact-profile results.</x:v>
       </x:c>
       <x:c r="P183" s="28" t="str">
         <x:v>RimWorld 1.6.4871 rev590; local version 1.6.5; supports 1.0-1.6; Harmony required; upstream repository lists MIT; About SHA-256 07A3C667B6B6729378D4EEDD5CACDBCC5F87A74B72546875D8ACD112CF982033</x:v>
       </x:c>
       <x:c r="Q183" s="28" t="str">
-        <x:v>Not runtime tested; verify Hospitality vat performance, medical/prisoner overlap, and exact RWT profile before support.</x:v>
+        <x:v>Publisher warns multiplayer may not work properly. Owner selected this row for RWT candidate testing on 2026-09-27; no runtime test or RWT support clearance yet. Verify Hospitality, medical/prisoner overlap, and desync behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="45" customHeight="1">
@@ -13592,34 +13592,34 @@
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H238" s="24" t="str">
-        <x:v>Use the active trait, memory, social-fight, relationship, conversion, and faction-reaction rules when generating applicants, workplace incidents, and crew histories. Keep the company's evaluation based on actual pawn traits, skills, and relationships.</x:v>
+        <x:v>Account for this optional change to vanilla social-fight stopping conditions when resolving staff injuries, relationship conflicts, and casualties. No Rimrooms-specific behavior is demonstrated.</x:v>
       </x:c>
       <x:c r="I238" s="24" t="str">
-        <x:v>Medium: these mods change the staff and visitor experience. Avoid replacing their thought, relation, or faction logic; check how hostility and guest incidents affect company reputation.</x:v>
+        <x:v>No direct integration; leave native social-fight logic intact and keep Rimrooms staff/case records separate.</x:v>
       </x:c>
       <x:c r="J238" s="24" t="str">
-        <x:v>Low to medium: preserve native jobs, needs, guest/faction ownership, and social behavior; test custom role suggestions around them.</x:v>
+        <x:v>Publisher describes pain/injury and relationship stop checks; Masochists ignore the pain check and Bloodlust pawns can continue until surrender, death, or downing. Steam also shows generic removal and incompatibility banners without a stated reason; do not treat those as a reproduced co-op conflict.</x:v>
       </x:c>
       <x:c r="K238" s="24" t="str">
-        <x:v>Source review incomplete; direct publisher-source check pending.</x:v>
+        <x:v>Publisher and local source facts recorded; social-fight, full-profile, and RWT behavior remain runtime-pending.</x:v>
       </x:c>
       <x:c r="L238" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-STA;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M238" s="28" t="str">
         <x:v>docs/research/reviews/mods/1542424705-marvinkosh.ughyougotme.md</x:v>
       </x:c>
       <x:c r="N238" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O238" s="28" t="str">
-        <x:v>Pending: direct publisher behavior and license not verified; no integration.</x:v>
+        <x:v>Optional; no direct integration. Social-fight and RWT coexistence are unverified; do not claim profile compatibility without testing.</x:v>
       </x:c>
       <x:c r="P238" s="28" t="str">
-        <x:v>Local metadata snapshot dated 2026-09-27; Version blank; local support 1.0–1.6; Harmony required and ordered after Harmony; no runtime check.</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; package marvinkosh.ughyougotme; local version blank; publisher lists 1.0.7 updated 2025-06-21 and support 1.0–1.6; Harmony required and loaded before mod.</x:v>
       </x:c>
       <x:c r="Q238" s="28" t="str">
-        <x:v>Wave 11 exact and English-page retries returned HTTP 429; old publisher site inaccessible and no linked source/license verified. Secondary references insufficient; no runtime test.</x:v>
+        <x:v>Exact publisher page, change notes, comments, and local metadata checked 2026-09-27. No source repository/license identified. Steam removal/incompatibility banners do not establish technical incompatibility. No runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="45" customHeight="1">
@@ -15574,13 +15574,13 @@
         <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O275" s="28" t="str">
-        <x:v>Provisional: solo-only optional recommended; RWT co-op scope awaits owner input.</x:v>
+        <x:v>Optional; include in the owner-selected RWT candidate test profile despite the publisher multiplayer/desync warning; do not advertise co-op support before exact-profile results.</x:v>
       </x:c>
       <x:c r="P275" s="28" t="str">
         <x:v>RimWorld 1.6.4871 rev590; local version ''; local support 1.0, 1.1, 1.2, 1.3, 1.4, 1.5, 1.6; About.xml SHA-256 2462E577F12FC4ED84B1CEC0118A258883194A5468C74143302B571F5A4F427E</x:v>
       </x:c>
       <x:c r="Q275" s="28" t="str">
-        <x:v>Publisher multiplayer/desync warning; no RWT test run. Owner scope requested 2026-09-27; keep outside RWT support claim pending answer and evidence.</x:v>
+        <x:v>Publisher warns multiplayer is unsupported and may desynchronize. Owner selected this row for RWT candidate testing on 2026-09-27; no runtime test or RWT support clearance yet. Test medical, custody, corpse and Harvest Organs interactions.</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="45" customHeight="1">
@@ -15759,40 +15759,40 @@
         <x:v>https://steamcommunity.com/sharedfiles/filedetails/?id=3093303048</x:v>
       </x:c>
       <x:c r="F279" s="24" t="str">
-        <x:v>Unverified package scope — title only</x:v>
+        <x:v>Facility construction and material access</x:v>
       </x:c>
       <x:c r="G279" s="24" t="str">
         <x:v>Included in the user-selected 294-entry profile; not a Backrooms core dependency.</x:v>
       </x:c>
       <x:c r="H279" s="24" t="str">
-        <x:v>Do not plan a feature integration from the title or local load-order metadata alone.</x:v>
+        <x:v>Optional placement fix for cooler and vent construction with Replace Stuff; it restores checks against blocked intakes/exhausts and over-wall placement.</x:v>
       </x:c>
       <x:c r="I279" s="24" t="str">
-        <x:v>No integration decision until publisher feature scope and license are accessible.</x:v>
+        <x:v>No direct Rimrooms integration. Let the optional patch preserve its native placement rules; do not replace cooler/vent geometry in Rimrooms.</x:v>
       </x:c>
       <x:c r="J279" s="24" t="str">
-        <x:v>Publisher page retries were rate-limited. Local metadata declares hard dependencies on Harmony and Replace Stuff Continued, and a LoadAfter target for Replace Stuff Compatibility; that target is not declared as a hard dependency.</x:v>
+        <x:v>Hard dependencies are Harmony and Replace Stuff Continued. Local metadata orders after Garethp.ReplaceStuffCompatibility, which is absent from the profile. Publisher comments contain an unresolved pawns-fire-through-coolers report; it was not reproduced.</x:v>
       </x:c>
       <x:c r="K279" s="24" t="str">
-        <x:v>Source review incomplete; direct publisher-source check pending.</x:v>
+        <x:v>Publisher and local source facts recorded; placement and line-of-fire behavior remain runtime-pending.</x:v>
       </x:c>
       <x:c r="L279" s="28" t="str">
-        <x:v>Pending mapping</x:v>
+        <x:v>RR-FAC;RR-COMPAT</x:v>
       </x:c>
       <x:c r="M279" s="28" t="str">
         <x:v>docs/research/reviews/mods/3093303048-Deadmano.ReplaceStuffCoolerVentPlacementFix.md</x:v>
       </x:c>
       <x:c r="N279" s="28" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Reviewed—source facts recorded</x:v>
       </x:c>
       <x:c r="O279" s="28" t="str">
-        <x:v>Pending: no verified feature description or license; no integration.</x:v>
+        <x:v>Optional; no direct integration. Do not claim profile/RWT coexistence until placement and the reported line-of-fire issue are checked.</x:v>
       </x:c>
       <x:c r="P279" s="28" t="str">
-        <x:v>Local metadata snapshot dated 2026-09-27; v1.6.0; support 1.4–1.6; hard deps Harmony and Replace Stuff Continued (Memegoddess.ReplaceStuff); after Garethp.ReplaceStuffCompatibility, absent.</x:v>
+        <x:v>RimWorld 1.6.4871 rev590; package Deadmano.ReplaceStuffCoolerVentPlacementFix v1.6.0; supports 1.4–1.6; requires Harmony and Memegoddess.ReplaceStuff; loads after Garethp.ReplaceStuffCompatibility per local metadata.</x:v>
       </x:c>
       <x:c r="Q279" s="28" t="str">
-        <x:v>Exact page and alternate URL returned HTTP 429; no publisher text, linked repository, or license verified. Local metadata only; no runtime test.</x:v>
+        <x:v>Exact publisher page, change notes, comments and local metadata checked 2026-09-27. No source repository/license found. Author's continuation preference is not a general license. Pawn-fire-through-coolers report is unverified. No runtime test.</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="45" customHeight="1">
@@ -16646,7 +16646,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25c823537174157"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8a5db6044d34198"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
+++ b/outputs/rimrooms-async-industries-register-2026-09-27/Rimrooms_Async_Industries_294_Mod_Integration_Register.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R92966c98affc4df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R0908af074b97493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rad5cc2ad2cae4118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mod Register" sheetId="2" r:id="R607367d691144eea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4980,7 +4980,7 @@
         <x:v>RimWorld 1.6.4871 rev590; local Mlie.DingOnGameLoaded 1.6.1 / support 1.1–1.6; exact-ID indexed Workshop text checked 2026-09-27; direct Steam fetch rate-limited; no runtime test.</x:v>
       </x:c>
       <x:c r="Q75" s="28" t="str">
-        <x:v>Linked note records the indexed publisher claims and local metadata. Direct page, client audio timing, and compatibility were not tested.</x:v>
+        <x:v>Not runtime tested. Linked note records the indexed publisher claims and local metadata. Direct page, client audio timing, and compatibility were not tested.</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="45" customHeight="1">
@@ -5192,7 +5192,7 @@
         <x:v>RimWorld 1.6.4871 rev590; local package metadata and indexed exact-ID publisher text checked 2026-09-27; direct page errored; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q79" s="28" t="str">
-        <x:v>Permission to update is not a license grant. Animal Weapon wording and full-profile command behavior remain uncertain.</x:v>
+        <x:v>Not runtime tested. Permission to update is not a license grant. Animal Weapon wording and full-profile command behavior remain uncertain.</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="45" customHeight="1">
@@ -6040,7 +6040,7 @@
         <x:v>RimWorld 1.6.4871 rev590; local selected package metadata and exact Workshop/source checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q95" s="28" t="str">
-        <x:v>Selected package is Zed item 2958300354; separate continuation 3261498531 excluded from claims. Source license and surgery behavior remain unresolved.</x:v>
+        <x:v>Not runtime tested. Selected package is Zed item 2958300354; separate continuation 3261498531 excluded from claims. Source license and surgery behavior remain unresolved.</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="45" customHeight="1">
@@ -13036,7 +13036,7 @@
         <x:v>RimWorld 1.6.4871 rev590; selected local package metadata and selected/original Workshop pages checked 2026-09-27; not runtime tested.</x:v>
       </x:c>
       <x:c r="Q227" s="28" t="str">
-        <x:v>Selected-versus-original boundary and rights uncertainty recorded. Exact selected payload and cooling behavior must be verified before reliance.</x:v>
+        <x:v>Not runtime tested. Selected-versus-original boundary and rights uncertainty recorded. Exact selected payload and cooling behavior must be verified before reliance.</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="45" customHeight="1">
@@ -16646,7 +16646,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8a5db6044d34198"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2579a00438a471e"/>
   </x:tableParts>
 </x:worksheet>
 </file>